--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I394"/>
+  <dimension ref="A1:I395"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -15979,7 +15979,33 @@
         </is>
       </c>
     </row>
-    <row r="395" ht="28.5" customHeight="1" s="22"/>
+    <row r="395" ht="28.5" customHeight="1" s="22">
+      <c r="A395" s="0" t="inlineStr">
+        <is>
+          <t>Cubicle</t>
+        </is>
+      </c>
+      <c r="B395" s="0" t="inlineStr">
+        <is>
+          <t>kiúbikel</t>
+        </is>
+      </c>
+      <c r="C395" s="0" t="inlineStr">
+        <is>
+          <t>Small enclosed space — Cubículo.</t>
+        </is>
+      </c>
+      <c r="D395" s="0" t="inlineStr">
+        <is>
+          <t>Lock the bathroom cubicle.</t>
+        </is>
+      </c>
+      <c r="I395" s="0" t="inlineStr">
+        <is>
+          <t>Common in British English for toilet stalls; also used for office partitions (open-plan cubicles).</t>
+        </is>
+      </c>
+    </row>
     <row r="396" ht="28.5" customHeight="1" s="22"/>
     <row r="397" ht="28.5" customHeight="1" s="22"/>
     <row r="398" ht="42.75" customHeight="1" s="22"/>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -33800,7 +33800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="2" min="1" max="1"/>
@@ -36538,7 +36538,43 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="57" customHeight="1" s="22"/>
+    <row r="67" ht="57" customHeight="1" s="22">
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t>estrip</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>Narrow piece of material — Tira.</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="inlineStr">
+        <is>
+          <t>She used strips of tape to hold the boxes closed.</t>
+        </is>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t>To remove clothing or a covering — Desnudar(se) / Quitar.</t>
+        </is>
+      </c>
+      <c r="F67" s="0" t="inlineStr">
+        <is>
+          <t>He stripped off his wet clothes before going inside.</t>
+        </is>
+      </c>
+      <c r="I67" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: strip — Present: strips — Past: stripped — Past participle: stripped. Note double 'p' in the -ing and past forms (stripping, stripped).</t>
+        </is>
+      </c>
+    </row>
     <row r="68" ht="28.5" customHeight="1" s="22"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36551,7 +36587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J475"/>
+  <dimension ref="A1:J476"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="5" min="1" max="1"/>
@@ -52950,7 +52986,53 @@
         </is>
       </c>
     </row>
-    <row r="476" ht="28.5" customHeight="1" s="22"/>
+    <row r="476" ht="28.5" customHeight="1" s="22">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Stall</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>stol</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Small enclosed cubicle, as in a bathroom or barn — Cubículo o compartimento.</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Lock the bathroom stall door.</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>A stand where goods are sold, as in a market — Puesto.</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>She bought fresh vegetables from a market stall.</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>To stop running suddenly, or to delay — Calarse (un motor) / dar largas.</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>The car stalled at the traffic light.</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>As a verb (meaning 3): Regular verb. Base: stall — Present: stalls — Past: stalled — Past participle: stalled. Can be used with 'for' as in 'stall for time', meaning to delay deliberately.</t>
+        </is>
+      </c>
+    </row>
     <row r="477" ht="28.5" customHeight="1" s="22"/>
     <row r="478" ht="28.5" customHeight="1" s="22"/>
     <row r="479" ht="28.5" customHeight="1" s="22"/>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -52987,47 +52987,47 @@
       </c>
     </row>
     <row r="476" ht="28.5" customHeight="1" s="22">
-      <c r="A476" t="inlineStr">
+      <c r="A476" s="0" t="inlineStr">
         <is>
           <t>Stall</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr">
+      <c r="B476" s="0" t="inlineStr">
         <is>
           <t>stol</t>
         </is>
       </c>
-      <c r="C476" t="inlineStr">
+      <c r="C476" s="0" t="inlineStr">
         <is>
           <t>Small enclosed cubicle, as in a bathroom or barn — Cubículo o compartimento.</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr">
+      <c r="D476" s="0" t="inlineStr">
         <is>
           <t>Lock the bathroom stall door.</t>
         </is>
       </c>
-      <c r="E476" t="inlineStr">
+      <c r="E476" s="0" t="inlineStr">
         <is>
           <t>A stand where goods are sold, as in a market — Puesto.</t>
         </is>
       </c>
-      <c r="F476" t="inlineStr">
+      <c r="F476" s="0" t="inlineStr">
         <is>
           <t>She bought fresh vegetables from a market stall.</t>
         </is>
       </c>
-      <c r="G476" t="inlineStr">
+      <c r="G476" s="0" t="inlineStr">
         <is>
           <t>To stop running suddenly, or to delay — Calarse (un motor) / dar largas.</t>
         </is>
       </c>
-      <c r="H476" t="inlineStr">
+      <c r="H476" s="0" t="inlineStr">
         <is>
           <t>The car stalled at the traffic light.</t>
         </is>
       </c>
-      <c r="I476" t="inlineStr">
+      <c r="I476" s="0" t="inlineStr">
         <is>
           <t>As a verb (meaning 3): Regular verb. Base: stall — Present: stalls — Past: stalled — Past participle: stalled. Can be used with 'for' as in 'stall for time', meaning to delay deliberately.</t>
         </is>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -36587,7 +36587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J476"/>
+  <dimension ref="A1:J479"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="5" min="1" max="1"/>
@@ -53033,9 +53033,107 @@
         </is>
       </c>
     </row>
-    <row r="477" ht="28.5" customHeight="1" s="22"/>
-    <row r="478" ht="28.5" customHeight="1" s="22"/>
-    <row r="479" ht="28.5" customHeight="1" s="22"/>
+    <row r="477" ht="28.5" customHeight="1" s="22">
+      <c r="A477" s="0" t="inlineStr">
+        <is>
+          <t>Mock</t>
+        </is>
+      </c>
+      <c r="B477" s="0" t="inlineStr">
+        <is>
+          <t>mok</t>
+        </is>
+      </c>
+      <c r="C477" s="0" t="inlineStr">
+        <is>
+          <t>To ridicule or make fun of — Burlarse de.</t>
+        </is>
+      </c>
+      <c r="D477" s="0" t="inlineStr">
+        <is>
+          <t>The other children mocked his accent.</t>
+        </is>
+      </c>
+      <c r="E477" s="0" t="inlineStr">
+        <is>
+          <t>Fake or imitation (adjective) — Simulado o fingido.</t>
+        </is>
+      </c>
+      <c r="F477" s="0" t="inlineStr">
+        <is>
+          <t>We did a mock exam before the real test.</t>
+        </is>
+      </c>
+      <c r="I477" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: mock — Present: mocks — Past: mocked — Past participle: mocked. Also used as an adjective before a noun, as in 'mock interview' or 'mock trial'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="28.5" customHeight="1" s="22">
+      <c r="A478" s="0" t="inlineStr">
+        <is>
+          <t>Unthinkable</t>
+        </is>
+      </c>
+      <c r="B478" s="0" t="inlineStr">
+        <is>
+          <t>anzínkabol</t>
+        </is>
+      </c>
+      <c r="C478" s="0" t="inlineStr">
+        <is>
+          <t>Impossible to accept or imagine — Impensable.</t>
+        </is>
+      </c>
+      <c r="D478" s="0" t="inlineStr">
+        <is>
+          <t>It was unthinkable that he would quit his job without notice.</t>
+        </is>
+      </c>
+      <c r="I478" s="0" t="inlineStr">
+        <is>
+          <t>Adjective, not a verb. Often used in the pattern 'it is unthinkable that...' or 'unthinkable to + verb'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479" ht="28.5" customHeight="1" s="22">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Whisper</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>wíspar</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>A soft, quiet voice — Susurro.</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>She spoke in a whisper.</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>To speak very quietly — Susurrar.</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>He whispered the answer to me.</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: whisper — Present: whispers — Past: whispered — Past participle: whispered.</t>
+        </is>
+      </c>
+    </row>
     <row r="480" ht="28.5" customHeight="1" s="22"/>
     <row r="481" ht="28.5" customHeight="1" s="22"/>
     <row r="482" ht="28.5" customHeight="1" s="22"/>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -19080,7 +19080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I391"/>
+  <dimension ref="A1:I394"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="18.140625" customWidth="1" style="7" min="1" max="1"/>
@@ -33771,9 +33771,117 @@
         </is>
       </c>
     </row>
-    <row r="392" ht="28.5" customHeight="1" s="22"/>
-    <row r="393" ht="28.5" customHeight="1" s="22"/>
-    <row r="394" ht="28.5" customHeight="1" s="22"/>
+    <row r="392" ht="28.5" customHeight="1" s="22">
+      <c r="A392" s="0" t="inlineStr">
+        <is>
+          <t>Dispute</t>
+        </is>
+      </c>
+      <c r="B392" s="0" t="inlineStr">
+        <is>
+          <t>dispiút</t>
+        </is>
+      </c>
+      <c r="C392" s="0" t="inlineStr">
+        <is>
+          <t>A disagreement or argument — Disputa.</t>
+        </is>
+      </c>
+      <c r="D392" s="0" t="inlineStr">
+        <is>
+          <t>He got mixed up in the dispute.</t>
+        </is>
+      </c>
+      <c r="E392" s="0" t="inlineStr">
+        <is>
+          <t>To question or argue against — Disputar, cuestionar.</t>
+        </is>
+      </c>
+      <c r="F392" s="0" t="inlineStr">
+        <is>
+          <t>She disputed the referee's decision.</t>
+        </is>
+      </c>
+      <c r="I392" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: dispute — Present: disputes — Past: disputed — Past participle: disputed. As a noun, stress falls on the second syllable, same as the verb; can be used with 'in' (in a dispute) or 'over' (a dispute over money).</t>
+        </is>
+      </c>
+    </row>
+    <row r="393" ht="28.5" customHeight="1" s="22">
+      <c r="A393" s="0" t="inlineStr">
+        <is>
+          <t>Backward</t>
+        </is>
+      </c>
+      <c r="B393" s="0" t="inlineStr">
+        <is>
+          <t>báquard</t>
+        </is>
+      </c>
+      <c r="C393" s="0" t="inlineStr">
+        <is>
+          <t>Toward the rear or in reverse — Hacia atrás.</t>
+        </is>
+      </c>
+      <c r="D393" s="0" t="inlineStr">
+        <is>
+          <t>He took a step backward.</t>
+        </is>
+      </c>
+      <c r="E393" s="0" t="inlineStr">
+        <is>
+          <t>Underdeveloped or old-fashioned — Atrasado.</t>
+        </is>
+      </c>
+      <c r="F393" s="0" t="inlineStr">
+        <is>
+          <t>The village was seen as backward and poor.</t>
+        </is>
+      </c>
+      <c r="I393" s="0" t="inlineStr">
+        <is>
+          <t>Adjective and adverb. In British English, 'backwards' is often used instead as the adverb form. Compare with 'forward'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="28.5" customHeight="1" s="22">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Shelter</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>shélter</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>A place that gives protection from danger or weather — Refugio.</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>They donated clothes to the shelter.</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>To protect someone from danger or weather — Proteger, resguardar.</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>The trees sheltered us from the rain.</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: shelter — Present: shelters — Past: sheltered — Past participle: sheltered. As a noun, often used with 'the' to refer to a specific building (e.g., homeless shelter, animal shelter).</t>
+        </is>
+      </c>
+    </row>
     <row r="395" ht="28.5" customHeight="1" s="22"/>
     <row r="396" ht="28.5" customHeight="1" s="22"/>
     <row r="397" ht="28.5" customHeight="1" s="22"/>
@@ -36587,7 +36695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J479"/>
+  <dimension ref="A1:J480"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="5" min="1" max="1"/>
@@ -53098,43 +53206,69 @@
       </c>
     </row>
     <row r="479" ht="28.5" customHeight="1" s="22">
-      <c r="A479" t="inlineStr">
+      <c r="A479" s="0" t="inlineStr">
         <is>
           <t>Whisper</t>
         </is>
       </c>
-      <c r="B479" t="inlineStr">
+      <c r="B479" s="0" t="inlineStr">
         <is>
           <t>wíspar</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr">
+      <c r="C479" s="0" t="inlineStr">
         <is>
           <t>A soft, quiet voice — Susurro.</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr">
+      <c r="D479" s="0" t="inlineStr">
         <is>
           <t>She spoke in a whisper.</t>
         </is>
       </c>
-      <c r="E479" t="inlineStr">
+      <c r="E479" s="0" t="inlineStr">
         <is>
           <t>To speak very quietly — Susurrar.</t>
         </is>
       </c>
-      <c r="F479" t="inlineStr">
+      <c r="F479" s="0" t="inlineStr">
         <is>
           <t>He whispered the answer to me.</t>
         </is>
       </c>
-      <c r="I479" t="inlineStr">
+      <c r="I479" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: whisper — Present: whispers — Past: whispered — Past participle: whispered.</t>
         </is>
       </c>
     </row>
-    <row r="480" ht="28.5" customHeight="1" s="22"/>
+    <row r="480" ht="28.5" customHeight="1" s="22">
+      <c r="A480" s="0" t="inlineStr">
+        <is>
+          <t>Sitter</t>
+        </is>
+      </c>
+      <c r="B480" s="0" t="inlineStr">
+        <is>
+          <t>síter</t>
+        </is>
+      </c>
+      <c r="C480" s="0" t="inlineStr">
+        <is>
+          <t>Person who looks after children, pets, or a house while the owner is away — Niñera o cuidador.</t>
+        </is>
+      </c>
+      <c r="D480" s="0" t="inlineStr">
+        <is>
+          <t>We booked a sitter for Saturday night.</t>
+        </is>
+      </c>
+      <c r="I480" s="0" t="inlineStr">
+        <is>
+          <t>Not a verb. Often short for babysitter, but also used for pet-sitter or house-sitter.</t>
+        </is>
+      </c>
+    </row>
     <row r="481" ht="28.5" customHeight="1" s="22"/>
     <row r="482" ht="28.5" customHeight="1" s="22"/>
     <row r="483" ht="28.5" customHeight="1" s="22"/>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -33846,37 +33846,37 @@
       </c>
     </row>
     <row r="394" ht="28.5" customHeight="1" s="22">
-      <c r="A394" t="inlineStr">
+      <c r="A394" s="0" t="inlineStr">
         <is>
           <t>Shelter</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
+      <c r="B394" s="0" t="inlineStr">
         <is>
           <t>shélter</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr">
+      <c r="C394" s="0" t="inlineStr">
         <is>
           <t>A place that gives protection from danger or weather — Refugio.</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr">
+      <c r="D394" s="0" t="inlineStr">
         <is>
           <t>They donated clothes to the shelter.</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr">
+      <c r="E394" s="0" t="inlineStr">
         <is>
           <t>To protect someone from danger or weather — Proteger, resguardar.</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr">
+      <c r="F394" s="0" t="inlineStr">
         <is>
           <t>The trees sheltered us from the rain.</t>
         </is>
       </c>
-      <c r="I394" t="inlineStr">
+      <c r="I394" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: shelter — Present: shelters — Past: sheltered — Past participle: sheltered. As a noun, often used with 'the' to refer to a specific building (e.g., homeless shelter, animal shelter).</t>
         </is>
@@ -36695,7 +36695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J480"/>
+  <dimension ref="A1:J481"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="5" min="1" max="1"/>
@@ -53269,7 +53269,33 @@
         </is>
       </c>
     </row>
-    <row r="481" ht="28.5" customHeight="1" s="22"/>
+    <row r="481" ht="28.5" customHeight="1" s="22">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Briefcase</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>brífqueis</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Case for carrying documents and papers — Maletín.</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>He packed his laptop in his briefcase before leaving for work.</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>Noun. Often associated with office work or business travel.</t>
+        </is>
+      </c>
+    </row>
     <row r="482" ht="28.5" customHeight="1" s="22"/>
     <row r="483" ht="28.5" customHeight="1" s="22"/>
     <row r="484" ht="28.5" customHeight="1" s="22"/>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -19080,7 +19080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I394"/>
+  <dimension ref="A1:I397"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="18.140625" customWidth="1" style="7" min="1" max="1"/>
@@ -33882,9 +33882,107 @@
         </is>
       </c>
     </row>
-    <row r="395" ht="28.5" customHeight="1" s="22"/>
-    <row r="396" ht="28.5" customHeight="1" s="22"/>
-    <row r="397" ht="28.5" customHeight="1" s="22"/>
+    <row r="395" ht="28.5" customHeight="1" s="22">
+      <c r="A395" s="0" t="inlineStr">
+        <is>
+          <t>Walk someone through</t>
+        </is>
+      </c>
+      <c r="B395" s="0" t="inlineStr">
+        <is>
+          <t>uok sámuan zrú</t>
+        </is>
+      </c>
+      <c r="C395" s="0" t="inlineStr">
+        <is>
+          <t>Explain or guide someone step by step through something — Explicarle o guiarle a alguien paso a paso.</t>
+        </is>
+      </c>
+      <c r="D395" s="0" t="inlineStr">
+        <is>
+          <t>Can you walk me through how the printer works?</t>
+        </is>
+      </c>
+      <c r="I395" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: walk — Present: walks — Past: walked — Past participle: walked. Separable phrasal verb: walk someone through something. Common in explanations, tutorials, or recounting events.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" ht="28.5" customHeight="1" s="22">
+      <c r="A396" s="0" t="inlineStr">
+        <is>
+          <t>Go straight</t>
+        </is>
+      </c>
+      <c r="B396" s="0" t="inlineStr">
+        <is>
+          <t>gou streit</t>
+        </is>
+      </c>
+      <c r="C396" s="0" t="inlineStr">
+        <is>
+          <t>To go directly to a place without stopping or delay — Ir directamente.</t>
+        </is>
+      </c>
+      <c r="D396" s="0" t="inlineStr">
+        <is>
+          <t>Did you go straight to the professor when you saw the mark?</t>
+        </is>
+      </c>
+      <c r="E396" s="0" t="inlineStr">
+        <is>
+          <t>To stop committing crimes and start living honestly — Enmendarse, dejar la vida delictiva.</t>
+        </is>
+      </c>
+      <c r="F396" s="0" t="inlineStr">
+        <is>
+          <t>After his release, he promised to go straight.</t>
+        </is>
+      </c>
+      <c r="I396" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb (based on go). Base: go straight — Present: goes straight — Past: went straight — Past participle: gone straight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="28.5" customHeight="1" s="22">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Back up</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>bak ap</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Support or confirm with evidence — Respaldar o confirmar con pruebas.</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Do you have any recordings or witnesses to back this up?</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Make a copy of data for safety — Hacer una copia de seguridad.</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Remember to back up your files before the update.</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: back up — Present: backs up — Past: backed up — Past participle: backed up. Separable: back something up / back up something.</t>
+        </is>
+      </c>
+    </row>
     <row r="398" ht="28.5" customHeight="1" s="22"/>
     <row r="399" ht="28.5" customHeight="1" s="22"/>
     <row r="400" ht="28.5" customHeight="1" s="22"/>
@@ -36695,7 +36793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J481"/>
+  <dimension ref="A1:J482"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="5" min="1" max="1"/>
@@ -53270,33 +53368,69 @@
       </c>
     </row>
     <row r="481" ht="28.5" customHeight="1" s="22">
-      <c r="A481" t="inlineStr">
+      <c r="A481" s="0" t="inlineStr">
         <is>
           <t>Briefcase</t>
         </is>
       </c>
-      <c r="B481" t="inlineStr">
+      <c r="B481" s="0" t="inlineStr">
         <is>
           <t>brífqueis</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr">
+      <c r="C481" s="0" t="inlineStr">
         <is>
           <t>Case for carrying documents and papers — Maletín.</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr">
+      <c r="D481" s="0" t="inlineStr">
         <is>
           <t>He packed his laptop in his briefcase before leaving for work.</t>
         </is>
       </c>
-      <c r="I481" t="inlineStr">
+      <c r="I481" s="0" t="inlineStr">
         <is>
           <t>Noun. Often associated with office work or business travel.</t>
         </is>
       </c>
     </row>
-    <row r="482" ht="28.5" customHeight="1" s="22"/>
+    <row r="482" ht="28.5" customHeight="1" s="22">
+      <c r="A482" s="0" t="inlineStr">
+        <is>
+          <t>Exchange</t>
+        </is>
+      </c>
+      <c r="B482" s="0" t="inlineStr">
+        <is>
+          <t>ekschéinch</t>
+        </is>
+      </c>
+      <c r="C482" s="0" t="inlineStr">
+        <is>
+          <t>The act of giving and receiving something in return — Intercambio.</t>
+        </is>
+      </c>
+      <c r="D482" s="0" t="inlineStr">
+        <is>
+          <t>We had a friendly exchange of ideas.</t>
+        </is>
+      </c>
+      <c r="E482" s="0" t="inlineStr">
+        <is>
+          <t>To give something and receive something else in return — Intercambiar.</t>
+        </is>
+      </c>
+      <c r="F482" s="0" t="inlineStr">
+        <is>
+          <t>I exchanged my dollars for euros at the airport.</t>
+        </is>
+      </c>
+      <c r="I482" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: exchange — Present: exchanges — Past: exchanged — Past participle: exchanged. Also used as a noun, e.g. 'exchange rate' or 'stock exchange'.</t>
+        </is>
+      </c>
+    </row>
     <row r="483" ht="28.5" customHeight="1" s="22"/>
     <row r="484" ht="28.5" customHeight="1" s="22"/>
     <row r="485" ht="28.5" customHeight="1" s="22"/>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -19080,7 +19080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I397"/>
+  <dimension ref="A1:I398"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="18.140625" customWidth="1" style="7" min="1" max="1"/>
@@ -33947,43 +33947,79 @@
       </c>
     </row>
     <row r="397" ht="28.5" customHeight="1" s="22">
-      <c r="A397" t="inlineStr">
+      <c r="A397" s="0" t="inlineStr">
         <is>
           <t>Back up</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
+      <c r="B397" s="0" t="inlineStr">
         <is>
           <t>bak ap</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr">
+      <c r="C397" s="0" t="inlineStr">
         <is>
           <t>Support or confirm with evidence — Respaldar o confirmar con pruebas.</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr">
+      <c r="D397" s="0" t="inlineStr">
         <is>
           <t>Do you have any recordings or witnesses to back this up?</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr">
+      <c r="E397" s="0" t="inlineStr">
         <is>
           <t>Make a copy of data for safety — Hacer una copia de seguridad.</t>
         </is>
       </c>
-      <c r="F397" t="inlineStr">
+      <c r="F397" s="0" t="inlineStr">
         <is>
           <t>Remember to back up your files before the update.</t>
         </is>
       </c>
-      <c r="I397" t="inlineStr">
+      <c r="I397" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: back up — Present: backs up — Past: backed up — Past participle: backed up. Separable: back something up / back up something.</t>
         </is>
       </c>
     </row>
-    <row r="398" ht="28.5" customHeight="1" s="22"/>
+    <row r="398" ht="28.5" customHeight="1" s="22">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Square</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>escuér</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>A shape with four equal sides — Cuadrado.</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Draw a square on the paper.</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Honest and fair, especially in the phrase "fair and square" — Limpio, honesto (en el sentido de justo).</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Did you earn your grade fair and square?</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Not a verb in this sense; 'square' can also function as a verb meaning to reconcile or match (e.g., 'that doesn't square with what you said'), but here it's used as an adjective in the fixed expression 'fair and square,' meaning honestly and without cheating.</t>
+        </is>
+      </c>
+    </row>
     <row r="399" ht="28.5" customHeight="1" s="22"/>
     <row r="400" ht="28.5" customHeight="1" s="22"/>
     <row r="401" ht="28.5" customHeight="1" s="22"/>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I395"/>
+  <dimension ref="A1:I406"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -16006,17 +16006,373 @@
         </is>
       </c>
     </row>
-    <row r="396" ht="28.5" customHeight="1" s="22"/>
-    <row r="397" ht="28.5" customHeight="1" s="22"/>
-    <row r="398" ht="42.75" customHeight="1" s="22"/>
-    <row r="399" ht="28.5" customHeight="1" s="22"/>
-    <row r="400" ht="28.5" customHeight="1" s="22"/>
-    <row r="401" ht="28.5" customHeight="1" s="22"/>
-    <row r="402" ht="28.5" customHeight="1" s="22"/>
-    <row r="403" ht="28.5" customHeight="1" s="22"/>
-    <row r="404" ht="28.5" customHeight="1" s="22"/>
-    <row r="405" ht="28.5" customHeight="1" s="22"/>
-    <row r="406" ht="42.75" customHeight="1" s="22"/>
+    <row r="396" ht="28.5" customHeight="1" s="22">
+      <c r="A396" s="0" t="inlineStr">
+        <is>
+          <t>Sort out</t>
+        </is>
+      </c>
+      <c r="B396" s="0" t="inlineStr">
+        <is>
+          <t>sort áut</t>
+        </is>
+      </c>
+      <c r="C396" s="0" t="inlineStr">
+        <is>
+          <t>Resolve or organize something confusing or messy — Resolver, poner en orden.</t>
+        </is>
+      </c>
+      <c r="D396" s="0" t="inlineStr">
+        <is>
+          <t>Can you help me sort this mess out?</t>
+        </is>
+      </c>
+      <c r="I396" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: sort out — Present: sorts out — Past: sorted out — Past participle: sorted out. Separable: sort something out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="28.5" customHeight="1" s="22">
+      <c r="A397" s="0" t="inlineStr">
+        <is>
+          <t>Mess out</t>
+        </is>
+      </c>
+      <c r="B397" s="0" t="inlineStr">
+        <is>
+          <t>mes áut</t>
+        </is>
+      </c>
+      <c r="C397" s="0" t="inlineStr">
+        <is>
+          <t>Not an actual phrasal verb — it's a false pattern — No es un verbo compuesto real.</t>
+        </is>
+      </c>
+      <c r="D397" s="0" t="inlineStr">
+        <is>
+          <t>Can you help me sort this whole mess out?</t>
+        </is>
+      </c>
+      <c r="I397" s="0" t="inlineStr">
+        <is>
+          <t>This is not a real phrasal verb. The verb here is 'sort out,' and 'mess' is simply its object placed between the two parts (a separable phrasal verb: sort something out). So 'sort this mess out' = 'sort out this mess.' Don't study 'mess out' as its own expression — study 'Sort out' instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="42.75" customHeight="1" s="22">
+      <c r="A398" s="0" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="B398" s="0" t="inlineStr">
+        <is>
+          <t>rikól</t>
+        </is>
+      </c>
+      <c r="C398" s="0" t="inlineStr">
+        <is>
+          <t>Remember — Recordar.</t>
+        </is>
+      </c>
+      <c r="D398" s="0" t="inlineStr">
+        <is>
+          <t>Can you recall if you were near the sinks?</t>
+        </is>
+      </c>
+      <c r="E398" s="0" t="inlineStr">
+        <is>
+          <t>Officially call back a faulty product — Retirar (un producto) del mercado.</t>
+        </is>
+      </c>
+      <c r="F398" s="0" t="inlineStr">
+        <is>
+          <t>The company had to recall thousands of toasters.</t>
+        </is>
+      </c>
+      <c r="I398" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: recall — Present: recalls — Past: recalled — Past participle: recalled. Also used as a noun: 'a product recall'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399" ht="28.5" customHeight="1" s="22">
+      <c r="A399" s="0" t="inlineStr">
+        <is>
+          <t>Far end</t>
+        </is>
+      </c>
+      <c r="B399" s="0" t="inlineStr">
+        <is>
+          <t>far énd</t>
+        </is>
+      </c>
+      <c r="C399" s="0" t="inlineStr">
+        <is>
+          <t>The most distant part of something — El extremo más lejano.</t>
+        </is>
+      </c>
+      <c r="D399" s="0" t="inlineStr">
+        <is>
+          <t>He was sitting at the far end of the table.</t>
+        </is>
+      </c>
+      <c r="I399" s="0" t="inlineStr">
+        <is>
+          <t>Not a verb. Often used with 'of': the far end of the hallway, the far end of the room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" ht="28.5" customHeight="1" s="22">
+      <c r="A400" s="0" t="inlineStr">
+        <is>
+          <t>Fuzzy</t>
+        </is>
+      </c>
+      <c r="B400" s="0" t="inlineStr">
+        <is>
+          <t>fázi</t>
+        </is>
+      </c>
+      <c r="C400" s="0" t="inlineStr">
+        <is>
+          <t>Unclear or blurry — Borroso.</t>
+        </is>
+      </c>
+      <c r="D400" s="0" t="inlineStr">
+        <is>
+          <t>The photo was too fuzzy to make out his face.</t>
+        </is>
+      </c>
+      <c r="E400" s="0" t="inlineStr">
+        <is>
+          <t>Covered with short, soft hair or fluff — Peludo, con pelusa.</t>
+        </is>
+      </c>
+      <c r="F400" s="0" t="inlineStr">
+        <is>
+          <t>The baby chick had fuzzy yellow feathers.</t>
+        </is>
+      </c>
+      <c r="I400" s="0" t="inlineStr">
+        <is>
+          <t>Adjective. Comparative: fuzzier — Superlative: fuzziest. Also used for vague thinking or memory, e.g. 'a fuzzy idea'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" ht="28.5" customHeight="1" s="22">
+      <c r="A401" s="0" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="B401" s="0" t="inlineStr">
+        <is>
+          <t>stéibol</t>
+        </is>
+      </c>
+      <c r="C401" s="0" t="inlineStr">
+        <is>
+          <t>A building where horses are kept — Establo.</t>
+        </is>
+      </c>
+      <c r="D401" s="0" t="inlineStr">
+        <is>
+          <t>The stable owner keeps six horses.</t>
+        </is>
+      </c>
+      <c r="E401" s="0" t="inlineStr">
+        <is>
+          <t>Firm, steady, not likely to change or fall — Estable.</t>
+        </is>
+      </c>
+      <c r="F401" s="0" t="inlineStr">
+        <is>
+          <t>The ladder felt stable when I climbed it.</t>
+        </is>
+      </c>
+      <c r="I401" s="0" t="inlineStr">
+        <is>
+          <t>Not a verb. Same spelling and pronunciation for both the noun and the adjective; context tells them apart. Comparative/superlative of the adjective: more stable — most stable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" ht="28.5" customHeight="1" s="22">
+      <c r="A402" s="0" t="inlineStr">
+        <is>
+          <t>Set up</t>
+        </is>
+      </c>
+      <c r="B402" s="0" t="inlineStr">
+        <is>
+          <t>sét ap</t>
+        </is>
+      </c>
+      <c r="C402" s="0" t="inlineStr">
+        <is>
+          <t>To install or arrange something for use — Instalar o montar algo.</t>
+        </is>
+      </c>
+      <c r="D402" s="0" t="inlineStr">
+        <is>
+          <t>I need to set up the projector before the meeting.</t>
+        </is>
+      </c>
+      <c r="E402" s="0" t="inlineStr">
+        <is>
+          <t>To establish a business or organization — Fundar o establecer.</t>
+        </is>
+      </c>
+      <c r="F402" s="0" t="inlineStr">
+        <is>
+          <t>They set up a new company last year.</t>
+        </is>
+      </c>
+      <c r="I402" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb (same form throughout). Base: set up — Present: sets up — Past: set up — Past participle: set up. Separable: set something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" ht="28.5" customHeight="1" s="22">
+      <c r="A403" s="0" t="inlineStr">
+        <is>
+          <t>Grouch</t>
+        </is>
+      </c>
+      <c r="B403" s="0" t="inlineStr">
+        <is>
+          <t>grauch</t>
+        </is>
+      </c>
+      <c r="C403" s="0" t="inlineStr">
+        <is>
+          <t>A person who complains a lot — Gruñón, quejica.</t>
+        </is>
+      </c>
+      <c r="D403" s="0" t="inlineStr">
+        <is>
+          <t>Don't be such a grouch this morning.</t>
+        </is>
+      </c>
+      <c r="E403" s="0" t="inlineStr">
+        <is>
+          <t>To complain or grumble — Quejarse, refunfuñar.</t>
+        </is>
+      </c>
+      <c r="F403" s="0" t="inlineStr">
+        <is>
+          <t>He always grouches about the weather.</t>
+        </is>
+      </c>
+      <c r="I403" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: grouch — Present: grouches — Past: grouched — Past participle: grouched. Informal. Related adjective: grouchy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="28.5" customHeight="1" s="22">
+      <c r="A404" s="0" t="inlineStr">
+        <is>
+          <t>Leaps and bounds</t>
+        </is>
+      </c>
+      <c r="B404" s="0" t="inlineStr">
+        <is>
+          <t>liips and báunds</t>
+        </is>
+      </c>
+      <c r="C404" s="0" t="inlineStr">
+        <is>
+          <t>Very rapidly, in large amounts of progress — A pasos agigantados.</t>
+        </is>
+      </c>
+      <c r="D404" s="0" t="inlineStr">
+        <is>
+          <t>The company's sales have grown by leaps and bounds this year.</t>
+        </is>
+      </c>
+      <c r="I404" s="0" t="inlineStr">
+        <is>
+          <t>Fixed expression, always used with 'by': by leaps and bounds. Not used in singular (a leap and a bound).</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="28.5" customHeight="1" s="22">
+      <c r="A405" s="0" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B405" s="0" t="inlineStr">
+        <is>
+          <t>estréit</t>
+        </is>
+      </c>
+      <c r="C405" s="0" t="inlineStr">
+        <is>
+          <t>Directly, without any delay or stop — Directamente.</t>
+        </is>
+      </c>
+      <c r="D405" s="0" t="inlineStr">
+        <is>
+          <t>The money goes straight to the stable for repairs.</t>
+        </is>
+      </c>
+      <c r="E405" s="0" t="inlineStr">
+        <is>
+          <t>Not curved or bent — Recto.</t>
+        </is>
+      </c>
+      <c r="F405" s="0" t="inlineStr">
+        <is>
+          <t>Draw a straight line across the page.</t>
+        </is>
+      </c>
+      <c r="I405" s="0" t="inlineStr">
+        <is>
+          <t>Adjective/adverb. Don't confuse with 'strait' (a narrow strip of water), which sounds the same.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" ht="42.75" customHeight="1" s="22">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Vet</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Veterinarian (informal) — Veterinario.</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>We took the horse to the vet for a checkup.</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>To examine carefully before approving — Investigar a fondo.</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>The company vets every new employee before hiring.</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Regular verb (sense 2). Base: vet — Present: vets — Past: vetted — Past participle: vetted. As a noun, it's a common shortening of 'veterinarian'.</t>
+        </is>
+      </c>
+    </row>
     <row r="407" ht="28.5" customHeight="1" s="22"/>
     <row r="408" ht="28.5" customHeight="1" s="22"/>
   </sheetData>
@@ -33984,37 +34340,37 @@
       </c>
     </row>
     <row r="398" ht="28.5" customHeight="1" s="22">
-      <c r="A398" t="inlineStr">
+      <c r="A398" s="0" t="inlineStr">
         <is>
           <t>Square</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
+      <c r="B398" s="0" t="inlineStr">
         <is>
           <t>escuér</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr">
+      <c r="C398" s="0" t="inlineStr">
         <is>
           <t>A shape with four equal sides — Cuadrado.</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr">
+      <c r="D398" s="0" t="inlineStr">
         <is>
           <t>Draw a square on the paper.</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr">
+      <c r="E398" s="0" t="inlineStr">
         <is>
           <t>Honest and fair, especially in the phrase "fair and square" — Limpio, honesto (en el sentido de justo).</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr">
+      <c r="F398" s="0" t="inlineStr">
         <is>
           <t>Did you earn your grade fair and square?</t>
         </is>
       </c>
-      <c r="I398" t="inlineStr">
+      <c r="I398" s="0" t="inlineStr">
         <is>
           <t>Not a verb in this sense; 'square' can also function as a verb meaning to reconcile or match (e.g., 'that doesn't square with what you said'), but here it's used as an adjective in the fixed expression 'fair and square,' meaning honestly and without cheating.</t>
         </is>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I406"/>
+  <dimension ref="A1:I409"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -16337,44 +16337,153 @@
       </c>
     </row>
     <row r="406" ht="42.75" customHeight="1" s="22">
-      <c r="A406" t="inlineStr">
+      <c r="A406" s="0" t="inlineStr">
         <is>
           <t>Vet</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
+      <c r="B406" s="0" t="inlineStr">
         <is>
           <t>bet</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr">
+      <c r="C406" s="0" t="inlineStr">
         <is>
           <t>Veterinarian (informal) — Veterinario.</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr">
+      <c r="D406" s="0" t="inlineStr">
         <is>
           <t>We took the horse to the vet for a checkup.</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr">
+      <c r="E406" s="0" t="inlineStr">
         <is>
           <t>To examine carefully before approving — Investigar a fondo.</t>
         </is>
       </c>
-      <c r="F406" t="inlineStr">
+      <c r="F406" s="0" t="inlineStr">
         <is>
           <t>The company vets every new employee before hiring.</t>
         </is>
       </c>
-      <c r="I406" t="inlineStr">
+      <c r="I406" s="0" t="inlineStr">
         <is>
           <t>Regular verb (sense 2). Base: vet — Present: vets — Past: vetted — Past participle: vetted. As a noun, it's a common shortening of 'veterinarian'.</t>
         </is>
       </c>
     </row>
-    <row r="407" ht="28.5" customHeight="1" s="22"/>
-    <row r="408" ht="28.5" customHeight="1" s="22"/>
+    <row r="407" ht="28.5" customHeight="1" s="22">
+      <c r="A407" s="0" t="inlineStr">
+        <is>
+          <t>Heads up</t>
+        </is>
+      </c>
+      <c r="B407" s="0" t="inlineStr">
+        <is>
+          <t>jeds ap</t>
+        </is>
+      </c>
+      <c r="C407" s="0" t="inlineStr">
+        <is>
+          <t>Advance warning or notice — Aviso previo.</t>
+        </is>
+      </c>
+      <c r="D407" s="0" t="inlineStr">
+        <is>
+          <t>Thanks for the heads up about the schedule change.</t>
+        </is>
+      </c>
+      <c r="E407" s="0" t="inlineStr">
+        <is>
+          <t>Warning to be careful, often shouted — ¡Cuidado!.</t>
+        </is>
+      </c>
+      <c r="F407" s="0" t="inlineStr">
+        <is>
+          <t>Heads up! The ball is coming your way.</t>
+        </is>
+      </c>
+      <c r="I407" s="0" t="inlineStr">
+        <is>
+          <t>Informal noun phrase; also used as an interjection. Often preceded by 'a' as in 'give someone a heads up'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="28.5" customHeight="1" s="22">
+      <c r="A408" s="0" t="inlineStr">
+        <is>
+          <t>Seize</t>
+        </is>
+      </c>
+      <c r="B408" s="0" t="inlineStr">
+        <is>
+          <t>siz</t>
+        </is>
+      </c>
+      <c r="C408" s="0" t="inlineStr">
+        <is>
+          <t>To grab or take hold of suddenly and firmly — Agarrar.</t>
+        </is>
+      </c>
+      <c r="D408" s="0" t="inlineStr">
+        <is>
+          <t>He seized her arm before she could fall.</t>
+        </is>
+      </c>
+      <c r="E408" s="0" t="inlineStr">
+        <is>
+          <t>To take control of, often by force or opportunity — Aprovechar/Apoderarse de.</t>
+        </is>
+      </c>
+      <c r="F408" s="0" t="inlineStr">
+        <is>
+          <t>The army seized the city within a day.</t>
+        </is>
+      </c>
+      <c r="I408" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: seize — Present: seizes — Past: seized — Past participle: seized. Often confused in spelling with 'cease'. Common in the fixed phrase 'seize the opportunity/day'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Appetite</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>ápetait</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Desire for food — Apetito.</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>I always have a good appetite before dinner.</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Strong desire or enthusiasm for something — Afición, ganas.</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Don't forget to bring your appetite for stable gossip too.</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Noun, usually singular. Common pattern: have an appetite for something.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I409"/>
+  <dimension ref="A1:I411"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -16448,39 +16448,93 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr">
+      <c r="A409" s="0" t="inlineStr">
         <is>
           <t>Appetite</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr">
+      <c r="B409" s="0" t="inlineStr">
         <is>
           <t>ápetait</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr">
+      <c r="C409" s="0" t="inlineStr">
         <is>
           <t>Desire for food — Apetito.</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr">
+      <c r="D409" s="0" t="inlineStr">
         <is>
           <t>I always have a good appetite before dinner.</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr">
+      <c r="E409" s="0" t="inlineStr">
         <is>
           <t>Strong desire or enthusiasm for something — Afición, ganas.</t>
         </is>
       </c>
-      <c r="F409" t="inlineStr">
+      <c r="F409" s="0" t="inlineStr">
         <is>
           <t>Don't forget to bring your appetite for stable gossip too.</t>
         </is>
       </c>
-      <c r="I409" t="inlineStr">
+      <c r="I409" s="0" t="inlineStr">
         <is>
           <t>Noun, usually singular. Common pattern: have an appetite for something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="0" t="inlineStr">
+        <is>
+          <t>You're all set</t>
+        </is>
+      </c>
+      <c r="B410" s="0" t="inlineStr">
+        <is>
+          <t>yor ol set</t>
+        </is>
+      </c>
+      <c r="C410" s="0" t="inlineStr">
+        <is>
+          <t>You are ready or finished — Ya está, todo listo.</t>
+        </is>
+      </c>
+      <c r="D410" s="0" t="inlineStr">
+        <is>
+          <t>You're all set — just sign here and you can go.</t>
+        </is>
+      </c>
+      <c r="I410" s="0" t="inlineStr">
+        <is>
+          <t>Fixed expression, not a verb. Common in customer service or after completing a task. Informal but polite; similar to 'you're good to go'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Uneven</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>aníven</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Not level or flat — Desigual, irregular.</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Honestly, with this uneven step, I could probably make a joke about a lawsuit if I'd actually hurt myself falling here!</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Adjective, not a verb. Comparative: more uneven — Superlative: most uneven (not 'unevener'). Opposite of 'even'.</t>
         </is>
       </c>
     </row>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I411"/>
+  <dimension ref="A1:I432"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -16512,29 +16512,706 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr">
+      <c r="A411" s="0" t="inlineStr">
         <is>
           <t>Uneven</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr">
+      <c r="B411" s="0" t="inlineStr">
         <is>
           <t>aníven</t>
         </is>
       </c>
-      <c r="C411" t="inlineStr">
+      <c r="C411" s="0" t="inlineStr">
         <is>
           <t>Not level or flat — Desigual, irregular.</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr">
+      <c r="D411" s="0" t="inlineStr">
         <is>
           <t>Honestly, with this uneven step, I could probably make a joke about a lawsuit if I'd actually hurt myself falling here!</t>
         </is>
       </c>
-      <c r="I411" t="inlineStr">
+      <c r="I411" s="0" t="inlineStr">
         <is>
           <t>Adjective, not a verb. Comparative: more uneven — Superlative: most uneven (not 'unevener'). Opposite of 'even'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="0" t="inlineStr">
+        <is>
+          <t>Hook</t>
+        </is>
+      </c>
+      <c r="B412" s="0" t="inlineStr">
+        <is>
+          <t>juk</t>
+        </is>
+      </c>
+      <c r="C412" s="0" t="inlineStr">
+        <is>
+          <t>Curved device for hanging or catching things — Gancho.</t>
+        </is>
+      </c>
+      <c r="D412" s="0" t="inlineStr">
+        <is>
+          <t>She hung her coat on the hook.</t>
+        </is>
+      </c>
+      <c r="E412" s="0" t="inlineStr">
+        <is>
+          <t>Curved metal device used to catch fish — Anzuelo.</t>
+        </is>
+      </c>
+      <c r="F412" s="0" t="inlineStr">
+        <is>
+          <t>The fisherman put bait on the hook.</t>
+        </is>
+      </c>
+      <c r="I412" s="0" t="inlineStr">
+        <is>
+          <t>Can also be used as a regular verb meaning to catch or attach with a hook. Base: hook — Present: hooks — Past: hooked — Past participle: hooked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="0" t="inlineStr">
+        <is>
+          <t>Fisherman</t>
+        </is>
+      </c>
+      <c r="B413" s="0" t="inlineStr">
+        <is>
+          <t>físherman</t>
+        </is>
+      </c>
+      <c r="C413" s="0" t="inlineStr">
+        <is>
+          <t>A person who catches fish, as a job or hobby — Pescador.</t>
+        </is>
+      </c>
+      <c r="D413" s="0" t="inlineStr">
+        <is>
+          <t>The fisherman sailed out early in the morning.</t>
+        </is>
+      </c>
+      <c r="I413" s="0" t="inlineStr">
+        <is>
+          <t>Not a verb. Plural: fishermen. Gender-neutral alternative: fisher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="0" t="inlineStr">
+        <is>
+          <t>Lure</t>
+        </is>
+      </c>
+      <c r="B414" s="0" t="inlineStr">
+        <is>
+          <t>lur</t>
+        </is>
+      </c>
+      <c r="C414" s="0" t="inlineStr">
+        <is>
+          <t>Something that attracts or tempts — Señuelo.</t>
+        </is>
+      </c>
+      <c r="D414" s="0" t="inlineStr">
+        <is>
+          <t>The lure of a better salary convinced him to change jobs.</t>
+        </is>
+      </c>
+      <c r="E414" s="0" t="inlineStr">
+        <is>
+          <t>To attract or tempt, often into danger — Atraer, tentar.</t>
+        </is>
+      </c>
+      <c r="F414" s="0" t="inlineStr">
+        <is>
+          <t>The scammers lured her with promises of easy money.</t>
+        </is>
+      </c>
+      <c r="I414" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: lure — Present: lures — Past: lured — Past participle: lured. As a noun, often used with 'the lure of' + noun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="0" t="inlineStr">
+        <is>
+          <t>Provoke</t>
+        </is>
+      </c>
+      <c r="B415" s="0" t="inlineStr">
+        <is>
+          <t>provóuk</t>
+        </is>
+      </c>
+      <c r="C415" s="0" t="inlineStr">
+        <is>
+          <t>To anger or annoy someone deliberately — Provocar.</t>
+        </is>
+      </c>
+      <c r="D415" s="0" t="inlineStr">
+        <is>
+          <t>Don't provoke the dog, it might bite you.</t>
+        </is>
+      </c>
+      <c r="E415" s="0" t="inlineStr">
+        <is>
+          <t>To cause a reaction or feeling — Provocar, incitar.</t>
+        </is>
+      </c>
+      <c r="F415" s="0" t="inlineStr">
+        <is>
+          <t>The comment provoked a heated debate.</t>
+        </is>
+      </c>
+      <c r="I415" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: provoke — Present: provokes — Past: provoked — Past participle: provoked. Often used as 'provoke someone into doing something' or 'provoke a reaction/response'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="0" t="inlineStr">
+        <is>
+          <t>Poke around</t>
+        </is>
+      </c>
+      <c r="B416" s="0" t="inlineStr">
+        <is>
+          <t>póuk aráund</t>
+        </is>
+      </c>
+      <c r="C416" s="0" t="inlineStr">
+        <is>
+          <t>Search or explore casually — Curiosear / fisgonear.</t>
+        </is>
+      </c>
+      <c r="D416" s="0" t="inlineStr">
+        <is>
+          <t>He liked to poke around in old bookstores.</t>
+        </is>
+      </c>
+      <c r="I416" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: poke around — Present: pokes around — Past: poked around — Past participle: poked around. Inseparable phrasal verb; often followed by "in" or "through".</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="0" t="inlineStr">
+        <is>
+          <t>Harmoniously</t>
+        </is>
+      </c>
+      <c r="B417" s="0" t="inlineStr">
+        <is>
+          <t>jarmóniusli</t>
+        </is>
+      </c>
+      <c r="C417" s="0" t="inlineStr">
+        <is>
+          <t>In a harmonious way — De manera armoniosa.</t>
+        </is>
+      </c>
+      <c r="D417" s="0" t="inlineStr">
+        <is>
+          <t>The old and new buildings blend harmoniously in the city center.</t>
+        </is>
+      </c>
+      <c r="I417" s="0" t="inlineStr">
+        <is>
+          <t>Adverb, from harmonious + ly. Often used with verbs like blend, fit, work, live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="0" t="inlineStr">
+        <is>
+          <t>Lightly</t>
+        </is>
+      </c>
+      <c r="B418" s="0" t="inlineStr">
+        <is>
+          <t>láitli</t>
+        </is>
+      </c>
+      <c r="C418" s="0" t="inlineStr">
+        <is>
+          <t>Gently, with little force or pressure — Suavemente / ligeramente.</t>
+        </is>
+      </c>
+      <c r="D418" s="0" t="inlineStr">
+        <is>
+          <t>Push the door lightly and it will open.</t>
+        </is>
+      </c>
+      <c r="E418" s="0" t="inlineStr">
+        <is>
+          <t>To a small degree — Levemente.</t>
+        </is>
+      </c>
+      <c r="F418" s="0" t="inlineStr">
+        <is>
+          <t>The soup was only lightly salted.</t>
+        </is>
+      </c>
+      <c r="I418" s="0" t="inlineStr">
+        <is>
+          <t>Adverb formed from 'light' + -ly. Not a verb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="0" t="inlineStr">
+        <is>
+          <t>Stick out</t>
+        </is>
+      </c>
+      <c r="B419" s="0" t="inlineStr">
+        <is>
+          <t>stik áut</t>
+        </is>
+      </c>
+      <c r="C419" s="0" t="inlineStr">
+        <is>
+          <t>Protrude or be clearly visible — Sobresalir / asomarse.</t>
+        </is>
+      </c>
+      <c r="D419" s="0" t="inlineStr">
+        <is>
+          <t>His ears stick out a lot.</t>
+        </is>
+      </c>
+      <c r="E419" s="0" t="inlineStr">
+        <is>
+          <t>Endure a difficult situation to the end — Aguantar hasta el final.</t>
+        </is>
+      </c>
+      <c r="F419" s="0" t="inlineStr">
+        <is>
+          <t>It was hard, but we decided to stick it out.</t>
+        </is>
+      </c>
+      <c r="I419" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: stick out — Present: sticks out — Past: stuck out — Past participle: stuck out. Separable: stick it out (common with 'it').</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="0" t="inlineStr">
+        <is>
+          <t>Rounded</t>
+        </is>
+      </c>
+      <c r="B420" s="0" t="inlineStr">
+        <is>
+          <t>ráundid</t>
+        </is>
+      </c>
+      <c r="C420" s="0" t="inlineStr">
+        <is>
+          <t>Having a curved or round shape — Redondeado.</t>
+        </is>
+      </c>
+      <c r="D420" s="0" t="inlineStr">
+        <is>
+          <t>The chair has rounded edges for safety.</t>
+        </is>
+      </c>
+      <c r="I420" s="0" t="inlineStr">
+        <is>
+          <t>Adjective; also the past participle of the verb 'round' (to round something off/up/down). Base: round — Present: rounds — Past: rounded — Past participle: rounded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="0" t="inlineStr">
+        <is>
+          <t>Roundabout</t>
+        </is>
+      </c>
+      <c r="B421" s="0" t="inlineStr">
+        <is>
+          <t>ráundabaut</t>
+        </is>
+      </c>
+      <c r="C421" s="0" t="inlineStr">
+        <is>
+          <t>Traffic circle — Rotonda o glorieta.</t>
+        </is>
+      </c>
+      <c r="D421" s="0" t="inlineStr">
+        <is>
+          <t>Take the second exit at the roundabout.</t>
+        </is>
+      </c>
+      <c r="E421" s="0" t="inlineStr">
+        <is>
+          <t>Indirect, not straightforward — Indirecto, con rodeos.</t>
+        </is>
+      </c>
+      <c r="F421" s="0" t="inlineStr">
+        <is>
+          <t>She gave a roundabout explanation instead of a clear answer.</t>
+        </is>
+      </c>
+      <c r="I421" s="0" t="inlineStr">
+        <is>
+          <t>Not a verb. British English word; Americans usually say 'traffic circle' for the noun sense. The adjective sense is common in phrases like 'a roundabout way of saying something'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="0" t="inlineStr">
+        <is>
+          <t>Sting</t>
+        </is>
+      </c>
+      <c r="B422" s="0" t="inlineStr">
+        <is>
+          <t>stin</t>
+        </is>
+      </c>
+      <c r="C422" s="0" t="inlineStr">
+        <is>
+          <t>A painful mark or sensation caused by an insect bite — Picadura.</t>
+        </is>
+      </c>
+      <c r="D422" s="0" t="inlineStr">
+        <is>
+          <t>The sting on my hand finally went down.</t>
+        </is>
+      </c>
+      <c r="E422" s="0" t="inlineStr">
+        <is>
+          <t>To cause a sharp, painful sensation, especially from an insect — Picar.</t>
+        </is>
+      </c>
+      <c r="F422" s="0" t="inlineStr">
+        <is>
+          <t>A wasp stung him on the arm.</t>
+        </is>
+      </c>
+      <c r="I422" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: sting — Present: stings — Past: stung — Past participle: stung. As a noun it refers to the mark or pain left by the bite; as a verb it describes the act of biting or causing that pain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="0" t="inlineStr">
+        <is>
+          <t>Go down</t>
+        </is>
+      </c>
+      <c r="B423" s="0" t="inlineStr">
+        <is>
+          <t>gou daun</t>
+        </is>
+      </c>
+      <c r="C423" s="0" t="inlineStr">
+        <is>
+          <t>To decrease or subside (pain, swelling, fever) — Bajar, disminuir.</t>
+        </is>
+      </c>
+      <c r="D423" s="0" t="inlineStr">
+        <is>
+          <t>The sting on my hand finally went down.</t>
+        </is>
+      </c>
+      <c r="E423" s="0" t="inlineStr">
+        <is>
+          <t>To set (the sun) — Ponerse (el sol).</t>
+        </is>
+      </c>
+      <c r="F423" s="0" t="inlineStr">
+        <is>
+          <t>We sat on the beach and watched the sun go down.</t>
+        </is>
+      </c>
+      <c r="G423" s="0" t="inlineStr">
+        <is>
+          <t>To sink (a ship or boat) — Hundirse.</t>
+        </is>
+      </c>
+      <c r="H423" s="0" t="inlineStr">
+        <is>
+          <t>The old fishing boat went down in the storm.</t>
+        </is>
+      </c>
+      <c r="I423" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: go down — Present: goes down — Past: went down — Past participle: gone down. Phrasal verb, intransitive (not separable).</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="0" t="inlineStr">
+        <is>
+          <t>Sweetcorn</t>
+        </is>
+      </c>
+      <c r="B424" s="0" t="inlineStr">
+        <is>
+          <t>suítcorn</t>
+        </is>
+      </c>
+      <c r="C424" s="0" t="inlineStr">
+        <is>
+          <t>Corn kernels eaten as a vegetable (especially canned or cooked) — Maíz dulce.</t>
+        </is>
+      </c>
+      <c r="D424" s="0" t="inlineStr">
+        <is>
+          <t>I heard a mix of sweetcorn and maggots works really well for fishing.</t>
+        </is>
+      </c>
+      <c r="I424" s="0" t="inlineStr">
+        <is>
+          <t>Not a verb; uncountable noun. Mainly British English — American English usually just says corn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="0" t="inlineStr">
+        <is>
+          <t>Wing it</t>
+        </is>
+      </c>
+      <c r="B425" s="0" t="inlineStr">
+        <is>
+          <t>uin it</t>
+        </is>
+      </c>
+      <c r="C425" s="0" t="inlineStr">
+        <is>
+          <t>To improvise without preparation — Improvisar.</t>
+        </is>
+      </c>
+      <c r="D425" s="0" t="inlineStr">
+        <is>
+          <t>We forgot the notes, so we just winged it during the presentation.</t>
+        </is>
+      </c>
+      <c r="I425" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: wing it — Present: wings it — Past: winged it — Past participle: winged it. Informal. Fixed expression; "it" doesn't change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="0" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="B426" s="0" t="inlineStr">
+        <is>
+          <t>esnáp</t>
+        </is>
+      </c>
+      <c r="C426" s="0" t="inlineStr">
+        <is>
+          <t>Break suddenly with a sharp sound — Romper(se) bruscamente.</t>
+        </is>
+      </c>
+      <c r="D426" s="0" t="inlineStr">
+        <is>
+          <t>Be careful not to snap the fishing rod while assembling it.</t>
+        </is>
+      </c>
+      <c r="I426" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: snap — Present: snaps — Past: snapped — Past participle: snapped. Double the final consonant before -ing/-ed: snapping, snapped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="0" t="inlineStr">
+        <is>
+          <t>Cast</t>
+        </is>
+      </c>
+      <c r="B427" s="0" t="inlineStr">
+        <is>
+          <t>kast</t>
+        </is>
+      </c>
+      <c r="C427" s="0" t="inlineStr">
+        <is>
+          <t>To throw out a fishing line — Lanzar (el sedal).</t>
+        </is>
+      </c>
+      <c r="D427" s="0" t="inlineStr">
+        <is>
+          <t>He cast his line into the calm lake.</t>
+        </is>
+      </c>
+      <c r="E427" s="0" t="inlineStr">
+        <is>
+          <t>The group of actors in a play or film — Reparto.</t>
+        </is>
+      </c>
+      <c r="F427" s="0" t="inlineStr">
+        <is>
+          <t>The whole cast took a bow at the end of the show.</t>
+        </is>
+      </c>
+      <c r="I427" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: cast — Present: casts — Past: cast — Past participle: cast. Same form in base, past and past participle. In fishing contexts, often used as 'cast a line' or simply 'cast'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="0" t="inlineStr">
+        <is>
+          <t>Practice run</t>
+        </is>
+      </c>
+      <c r="B428" s="0" t="inlineStr">
+        <is>
+          <t>práctis ran</t>
+        </is>
+      </c>
+      <c r="C428" s="0" t="inlineStr">
+        <is>
+          <t>A trial attempt before doing something for real — Ensayo, prueba.</t>
+        </is>
+      </c>
+      <c r="D428" s="0" t="inlineStr">
+        <is>
+          <t>This is basically a practice run before we try it for real.</t>
+        </is>
+      </c>
+      <c r="I428" s="0" t="inlineStr">
+        <is>
+          <t>Noun phrase, not a verb. Often used with 'a': do a practice run. Can also be written as one word, 'practice-run', as an adjective before a noun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="0" t="inlineStr">
+        <is>
+          <t>Onto</t>
+        </is>
+      </c>
+      <c r="B429" s="0" t="inlineStr">
+        <is>
+          <t>óntu</t>
+        </is>
+      </c>
+      <c r="C429" s="0" t="inlineStr">
+        <is>
+          <t>To a position on top of or attached to something — Sobre, encima de.</t>
+        </is>
+      </c>
+      <c r="D429" s="0" t="inlineStr">
+        <is>
+          <t>You poke the worm onto the hook, not the rod.</t>
+        </is>
+      </c>
+      <c r="I429" s="0" t="inlineStr">
+        <is>
+          <t>Preposition, not a verb. Shows movement toward a surface, as opposed to "on," which shows static position. Sometimes confused with the two-word sequence "on to" (as in "move on to the next step").</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="0" t="inlineStr">
+        <is>
+          <t>Ashes</t>
+        </is>
+      </c>
+      <c r="B430" s="0" t="inlineStr">
+        <is>
+          <t>áshis</t>
+        </is>
+      </c>
+      <c r="C430" s="0" t="inlineStr">
+        <is>
+          <t>Remains of something burned — Cenizas.</t>
+        </is>
+      </c>
+      <c r="D430" s="0" t="inlineStr">
+        <is>
+          <t>I was poking at the ashes from last night's campfire.</t>
+        </is>
+      </c>
+      <c r="I430" s="0" t="inlineStr">
+        <is>
+          <t>Plural noun. The singular form 'ash' refers to the substance in general or a single speck; 'ashes' is used for the leftover remains, as in a fireplace or after cremation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="0" t="inlineStr">
+        <is>
+          <t>Head down</t>
+        </is>
+      </c>
+      <c r="B431" s="0" t="inlineStr">
+        <is>
+          <t>jed daun</t>
+        </is>
+      </c>
+      <c r="C431" s="0" t="inlineStr">
+        <is>
+          <t>Go or travel toward a place, often one that is lower or further away — Dirigirse (hacia un lugar).</t>
+        </is>
+      </c>
+      <c r="D431" s="0" t="inlineStr">
+        <is>
+          <t>Want to head down to the lake now and start practicing?</t>
+        </is>
+      </c>
+      <c r="I431" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: head down — Present: heads down — Past: headed down — Past participle: headed down. Intransitive; not separable, always followed by a direction like 'to' or 'toward'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>jed</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Part of the body above the neck — Cabeza.</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>She turned her head to look at the view.</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>To move toward a place — Dirigirse.</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Let's head down to the lake before it gets dark.</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Regular verb (for the 'move toward' sense). Base: head — Present: heads — Past: headed — Past participle: headed. As a noun it's very common in idioms, e.g. 'head of the table', 'head start'.</t>
         </is>
       </c>
     </row>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I432"/>
+  <dimension ref="A1:I641"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -17179,39 +17179,5692 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="inlineStr">
+      <c r="A432" s="0" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="B432" t="inlineStr">
+      <c r="B432" s="0" t="inlineStr">
         <is>
           <t>jed</t>
         </is>
       </c>
-      <c r="C432" t="inlineStr">
+      <c r="C432" s="0" t="inlineStr">
         <is>
           <t>Part of the body above the neck — Cabeza.</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr">
+      <c r="D432" s="0" t="inlineStr">
         <is>
           <t>She turned her head to look at the view.</t>
         </is>
       </c>
-      <c r="E432" t="inlineStr">
+      <c r="E432" s="0" t="inlineStr">
         <is>
           <t>To move toward a place — Dirigirse.</t>
         </is>
       </c>
-      <c r="F432" t="inlineStr">
+      <c r="F432" s="0" t="inlineStr">
         <is>
           <t>Let's head down to the lake before it gets dark.</t>
         </is>
       </c>
-      <c r="I432" t="inlineStr">
+      <c r="I432" s="0" t="inlineStr">
         <is>
           <t>Regular verb (for the 'move toward' sense). Base: head — Present: heads — Past: headed — Past participle: headed. As a noun it's very common in idioms, e.g. 'head of the table', 'head start'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="0" t="inlineStr">
+        <is>
+          <t>Proper</t>
+        </is>
+      </c>
+      <c r="B433" s="0" t="inlineStr">
+        <is>
+          <t>próper</t>
+        </is>
+      </c>
+      <c r="C433" s="0" t="inlineStr">
+        <is>
+          <t>Correct or appropriate — Correcto, adecuado.</t>
+        </is>
+      </c>
+      <c r="D433" s="0" t="inlineStr">
+        <is>
+          <t>You need to use the proper tools for this job.</t>
+        </is>
+      </c>
+      <c r="E433" s="0" t="inlineStr">
+        <is>
+          <t>Real or genuine, used for emphasis (informal) — Auténtico, de verdad.</t>
+        </is>
+      </c>
+      <c r="F433" s="0" t="inlineStr">
+        <is>
+          <t>That's gonna be a proper adventure if we get it right.</t>
+        </is>
+      </c>
+      <c r="I433" s="0" t="inlineStr">
+        <is>
+          <t>Adjective. The second sense is common in British informal speech, used before a noun to intensify it (a proper mess, a proper laugh).</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="0" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="B434" s="0" t="inlineStr">
+        <is>
+          <t>uéik ap</t>
+        </is>
+      </c>
+      <c r="C434" s="0" t="inlineStr">
+        <is>
+          <t>Stop sleeping — Despertarse.</t>
+        </is>
+      </c>
+      <c r="D434" s="0" t="inlineStr">
+        <is>
+          <t>I wake up at 6:30 every morning.</t>
+        </is>
+      </c>
+      <c r="I434" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: wake up — Present: wakes up — Past: woke up — Past participle: woken up. Separable: wake someone up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="0" t="inlineStr">
+        <is>
+          <t>Get up</t>
+        </is>
+      </c>
+      <c r="B435" s="0" t="inlineStr">
+        <is>
+          <t>guét ap</t>
+        </is>
+      </c>
+      <c r="C435" s="0" t="inlineStr">
+        <is>
+          <t>Get out of bed — Levantarse.</t>
+        </is>
+      </c>
+      <c r="D435" s="0" t="inlineStr">
+        <is>
+          <t>She got up and opened the window.</t>
+        </is>
+      </c>
+      <c r="I435" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get up — Present: gets up — Past: got up — Past participle: got up / gotten up (US). Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="0" t="inlineStr">
+        <is>
+          <t>Put on</t>
+        </is>
+      </c>
+      <c r="B436" s="0" t="inlineStr">
+        <is>
+          <t>put on</t>
+        </is>
+      </c>
+      <c r="C436" s="0" t="inlineStr">
+        <is>
+          <t>Wear clothes or accessories — Ponerse (ropa).</t>
+        </is>
+      </c>
+      <c r="D436" s="0" t="inlineStr">
+        <is>
+          <t>He put on his jacket.</t>
+        </is>
+      </c>
+      <c r="I436" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: put on — Present: puts on — Past: put on — Past participle: put on. Separable: put something on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="0" t="inlineStr">
+        <is>
+          <t>Sit down</t>
+        </is>
+      </c>
+      <c r="B437" s="0" t="inlineStr">
+        <is>
+          <t>sit dáun</t>
+        </is>
+      </c>
+      <c r="C437" s="0" t="inlineStr">
+        <is>
+          <t>Move into a sitting position — Sentarse.</t>
+        </is>
+      </c>
+      <c r="D437" s="0" t="inlineStr">
+        <is>
+          <t>After a long walk I sat down to rest.</t>
+        </is>
+      </c>
+      <c r="I437" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: sit down — Present: sits down — Past: sat down — Past participle: sat down. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="0" t="inlineStr">
+        <is>
+          <t>Stand up</t>
+        </is>
+      </c>
+      <c r="B438" s="0" t="inlineStr">
+        <is>
+          <t>estand ap</t>
+        </is>
+      </c>
+      <c r="C438" s="0" t="inlineStr">
+        <is>
+          <t>Rise to your feet — Ponerse de pie.</t>
+        </is>
+      </c>
+      <c r="D438" s="0" t="inlineStr">
+        <is>
+          <t>He stood up from his chair.</t>
+        </is>
+      </c>
+      <c r="I438" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: stand up — Present: stands up — Past: stood up — Past participle: stood up. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="0" t="inlineStr">
+        <is>
+          <t>Go out</t>
+        </is>
+      </c>
+      <c r="B439" s="0" t="inlineStr">
+        <is>
+          <t>góu aut</t>
+        </is>
+      </c>
+      <c r="C439" s="0" t="inlineStr">
+        <is>
+          <t>Leave home — Salir.</t>
+        </is>
+      </c>
+      <c r="D439" s="0" t="inlineStr">
+        <is>
+          <t>We went out last night.</t>
+        </is>
+      </c>
+      <c r="I439" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: go out — Present: goes out — Past: went out — Past participle: gone out. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="0" t="inlineStr">
+        <is>
+          <t>Come back</t>
+        </is>
+      </c>
+      <c r="B440" s="0" t="inlineStr">
+        <is>
+          <t>kam bak</t>
+        </is>
+      </c>
+      <c r="C440" s="0" t="inlineStr">
+        <is>
+          <t>Return — Volver.</t>
+        </is>
+      </c>
+      <c r="D440" s="0" t="inlineStr">
+        <is>
+          <t>I'll come back later.</t>
+        </is>
+      </c>
+      <c r="I440" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: come back — Present: comes back — Past: came back — Past participle: come back. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="0" t="inlineStr">
+        <is>
+          <t>Go back</t>
+        </is>
+      </c>
+      <c r="B441" s="0" t="inlineStr">
+        <is>
+          <t>góu bak</t>
+        </is>
+      </c>
+      <c r="C441" s="0" t="inlineStr">
+        <is>
+          <t>Return to a place — Regresar.</t>
+        </is>
+      </c>
+      <c r="D441" s="0" t="inlineStr">
+        <is>
+          <t>She went back home.</t>
+        </is>
+      </c>
+      <c r="I441" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: go back — Present: goes back — Past: went back — Past participle: gone back. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="0" t="inlineStr">
+        <is>
+          <t>Pick up</t>
+        </is>
+      </c>
+      <c r="B442" s="0" t="inlineStr">
+        <is>
+          <t>pik ap</t>
+        </is>
+      </c>
+      <c r="C442" s="0" t="inlineStr">
+        <is>
+          <t>Collect something — Recoger.</t>
+        </is>
+      </c>
+      <c r="D442" s="0" t="inlineStr">
+        <is>
+          <t>I picked up my package.</t>
+        </is>
+      </c>
+      <c r="I442" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: pick up — Present: picks up — Past: picked up — Past participle: picked up. Separable: pick something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="0" t="inlineStr">
+        <is>
+          <t>Drop off</t>
+        </is>
+      </c>
+      <c r="B443" s="0" t="inlineStr">
+        <is>
+          <t>drap óf</t>
+        </is>
+      </c>
+      <c r="C443" s="0" t="inlineStr">
+        <is>
+          <t>Leave someone at a place — Dejar a alguien en un lugar.</t>
+        </is>
+      </c>
+      <c r="D443" s="0" t="inlineStr">
+        <is>
+          <t>My dad dropped me off at school.</t>
+        </is>
+      </c>
+      <c r="I443" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: drop off — Present: drops off — Past: dropped off — Past participle: dropped off. Separable: drop someone off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="0" t="inlineStr">
+        <is>
+          <t>Turn on</t>
+        </is>
+      </c>
+      <c r="B444" s="0" t="inlineStr">
+        <is>
+          <t>tern on</t>
+        </is>
+      </c>
+      <c r="C444" s="0" t="inlineStr">
+        <is>
+          <t>Start a device — Encender.</t>
+        </is>
+      </c>
+      <c r="D444" s="0" t="inlineStr">
+        <is>
+          <t>Jack Turned on the TV.</t>
+        </is>
+      </c>
+      <c r="I444" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: turn on — Present: turns on — Past: turned on — Past participle: turned on. Separable: turn something on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="0" t="inlineStr">
+        <is>
+          <t>Turn off</t>
+        </is>
+      </c>
+      <c r="B445" s="0" t="inlineStr">
+        <is>
+          <t>tern óf</t>
+        </is>
+      </c>
+      <c r="C445" s="0" t="inlineStr">
+        <is>
+          <t>Stop a device — Apagar.</t>
+        </is>
+      </c>
+      <c r="D445" s="0" t="inlineStr">
+        <is>
+          <t>Turn off the lights.</t>
+        </is>
+      </c>
+      <c r="I445" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: turn off — Present: turns off — Past: turned off — Past participle: turned off. Separable: turn something off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="0" t="inlineStr">
+        <is>
+          <t>Put away</t>
+        </is>
+      </c>
+      <c r="B446" s="0" t="inlineStr">
+        <is>
+          <t>put auéi</t>
+        </is>
+      </c>
+      <c r="C446" s="0" t="inlineStr">
+        <is>
+          <t>Put something in its place — Guardar.</t>
+        </is>
+      </c>
+      <c r="D446" s="0" t="inlineStr">
+        <is>
+          <t>Put away your toys.</t>
+        </is>
+      </c>
+      <c r="I446" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: put away — Present: puts away — Past: put away — Past participle: put away. Separable: put something away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="0" t="inlineStr">
+        <is>
+          <t>Clean up</t>
+        </is>
+      </c>
+      <c r="B447" s="0" t="inlineStr">
+        <is>
+          <t>clin ap</t>
+        </is>
+      </c>
+      <c r="C447" s="0" t="inlineStr">
+        <is>
+          <t>Make a place tidy — Ordenar.</t>
+        </is>
+      </c>
+      <c r="D447" s="0" t="inlineStr">
+        <is>
+          <t>Let's clean up the room.</t>
+        </is>
+      </c>
+      <c r="I447" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: clean up — Present: cleans up — Past: cleaned up — Past participle: cleaned up. Separable: clean something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="0" t="inlineStr">
+        <is>
+          <t>Wash up</t>
+        </is>
+      </c>
+      <c r="B448" s="0" t="inlineStr">
+        <is>
+          <t>wash ap</t>
+        </is>
+      </c>
+      <c r="C448" s="0" t="inlineStr">
+        <is>
+          <t>Wash your hands and face — Lavarse las manos y la cara.</t>
+        </is>
+      </c>
+      <c r="D448" s="0" t="inlineStr">
+        <is>
+          <t>Go wash up before dinner.</t>
+        </is>
+      </c>
+      <c r="I448" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: wash up — Present: washes up — Past: washed up — Past participle: washed up. Inseparable; used without an object (reflexive sense).</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="0" t="inlineStr">
+        <is>
+          <t>Look after</t>
+        </is>
+      </c>
+      <c r="B449" s="0" t="inlineStr">
+        <is>
+          <t>luk áfter</t>
+        </is>
+      </c>
+      <c r="C449" s="0" t="inlineStr">
+        <is>
+          <t>Take care of someone — Cuidar a alguien.</t>
+        </is>
+      </c>
+      <c r="D449" s="0" t="inlineStr">
+        <is>
+          <t>She looks after her brother.</t>
+        </is>
+      </c>
+      <c r="I449" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: look after — Present: looks after — Past: looked after — Past participle: looked after. Inseparable: look after someone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="0" t="inlineStr">
+        <is>
+          <t>Eat out</t>
+        </is>
+      </c>
+      <c r="B450" s="0" t="inlineStr">
+        <is>
+          <t>it áut</t>
+        </is>
+      </c>
+      <c r="C450" s="0" t="inlineStr">
+        <is>
+          <t>Eat at a restaurant — Comer fuera.</t>
+        </is>
+      </c>
+      <c r="D450" s="0" t="inlineStr">
+        <is>
+          <t>We ate out yesterday.</t>
+        </is>
+      </c>
+      <c r="I450" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: eat out — Present: eats out — Past: ate out — Past participle: eaten out. Not separable (no object).</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="0" t="inlineStr">
+        <is>
+          <t>Look for</t>
+        </is>
+      </c>
+      <c r="B451" s="0" t="inlineStr">
+        <is>
+          <t>luk fór</t>
+        </is>
+      </c>
+      <c r="C451" s="0" t="inlineStr">
+        <is>
+          <t>Search for something — Buscar algo.</t>
+        </is>
+      </c>
+      <c r="D451" s="0" t="inlineStr">
+        <is>
+          <t>I'm looking for my keys.</t>
+        </is>
+      </c>
+      <c r="I451" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: look for — Present: looks for — Past: looked for — Past participle: looked for. Not separable; always used with an object: look for something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="0" t="inlineStr">
+        <is>
+          <t>Check out</t>
+        </is>
+      </c>
+      <c r="B452" s="0" t="inlineStr">
+        <is>
+          <t>chek áut</t>
+        </is>
+      </c>
+      <c r="C452" s="0" t="inlineStr">
+        <is>
+          <t>Look at something — Mirar algo.</t>
+        </is>
+      </c>
+      <c r="D452" s="0" t="inlineStr">
+        <is>
+          <t>Check out my new bike.</t>
+        </is>
+      </c>
+      <c r="I452" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: check out — Present: checks out — Past: checked out — Past participle: checked out. Separable: check something out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="0" t="inlineStr">
+        <is>
+          <t>Come in</t>
+        </is>
+      </c>
+      <c r="B453" s="0" t="inlineStr">
+        <is>
+          <t>kam ín</t>
+        </is>
+      </c>
+      <c r="C453" s="0" t="inlineStr">
+        <is>
+          <t>Enter a room or place — Entrar.</t>
+        </is>
+      </c>
+      <c r="D453" s="0" t="inlineStr">
+        <is>
+          <t>Come in and sit down.</t>
+        </is>
+      </c>
+      <c r="I453" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: come in — Present: comes in — Past: came in — Past participle: come in. Not separable (no object).</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="0" t="inlineStr">
+        <is>
+          <t>Go away</t>
+        </is>
+      </c>
+      <c r="B454" s="0" t="inlineStr">
+        <is>
+          <t>gou euéi</t>
+        </is>
+      </c>
+      <c r="C454" s="0" t="inlineStr">
+        <is>
+          <t>Leave — Irse.</t>
+        </is>
+      </c>
+      <c r="D454" s="0" t="inlineStr">
+        <is>
+          <t>Please go away.</t>
+        </is>
+      </c>
+      <c r="I454" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: go away — Present: goes away — Past: went away — Past participle: gone away. Not separable (no object).</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="0" t="inlineStr">
+        <is>
+          <t>Hang up</t>
+        </is>
+      </c>
+      <c r="B455" s="0" t="inlineStr">
+        <is>
+          <t>jang áp</t>
+        </is>
+      </c>
+      <c r="C455" s="0" t="inlineStr">
+        <is>
+          <t>End a phone call — Colgar el teléfono.</t>
+        </is>
+      </c>
+      <c r="D455" s="0" t="inlineStr">
+        <is>
+          <t>She hung up suddenly.</t>
+        </is>
+      </c>
+      <c r="I455" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: hang up — Present: hangs up — Past: hung up — Past participle: hung up. Not separable in this sense (no object); also used for hanging something on a hook, where it is separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="0" t="inlineStr">
+        <is>
+          <t>Pick out</t>
+        </is>
+      </c>
+      <c r="B456" s="0" t="inlineStr">
+        <is>
+          <t>pik áut</t>
+        </is>
+      </c>
+      <c r="C456" s="0" t="inlineStr">
+        <is>
+          <t>Choose something — Elegir algo.</t>
+        </is>
+      </c>
+      <c r="D456" s="0" t="inlineStr">
+        <is>
+          <t>She picked out a new dress.</t>
+        </is>
+      </c>
+      <c r="I456" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: pick out — Present: picks out — Past: picked out — Past participle: picked out. Separable: pick something out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="0" t="inlineStr">
+        <is>
+          <t>Fill up</t>
+        </is>
+      </c>
+      <c r="B457" s="0" t="inlineStr">
+        <is>
+          <t>fil áp</t>
+        </is>
+      </c>
+      <c r="C457" s="0" t="inlineStr">
+        <is>
+          <t>Make something full — Llenar algo.</t>
+        </is>
+      </c>
+      <c r="D457" s="0" t="inlineStr">
+        <is>
+          <t>She is filling up the bottle.</t>
+        </is>
+      </c>
+      <c r="I457" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: fill up — Present: fills up — Past: filled up — Past participle: filled up. Separable: fill something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="0" t="inlineStr">
+        <is>
+          <t>Put together</t>
+        </is>
+      </c>
+      <c r="B458" s="0" t="inlineStr">
+        <is>
+          <t>put tuguéder</t>
+        </is>
+      </c>
+      <c r="C458" s="0" t="inlineStr">
+        <is>
+          <t>Assemble something — Armar o montar algo.</t>
+        </is>
+      </c>
+      <c r="D458" s="0" t="inlineStr">
+        <is>
+          <t>We put together a new shelf.</t>
+        </is>
+      </c>
+      <c r="I458" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: put together — Present: puts together — Past: put together — Past participle: put together. Separable: put something together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="0" t="inlineStr">
+        <is>
+          <t>Call back</t>
+        </is>
+      </c>
+      <c r="B459" s="0" t="inlineStr">
+        <is>
+          <t>col bac</t>
+        </is>
+      </c>
+      <c r="C459" s="0" t="inlineStr">
+        <is>
+          <t>Return a phone call — Devolver la llamada.</t>
+        </is>
+      </c>
+      <c r="D459" s="0" t="inlineStr">
+        <is>
+          <t>I'll call you back later.</t>
+        </is>
+      </c>
+      <c r="I459" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: call back — Present: calls back — Past: called back — Past participle: called back. Separable: call someone back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="0" t="inlineStr">
+        <is>
+          <t>Slow down</t>
+        </is>
+      </c>
+      <c r="B460" s="0" t="inlineStr">
+        <is>
+          <t>eslóu dáun</t>
+        </is>
+      </c>
+      <c r="C460" s="0" t="inlineStr">
+        <is>
+          <t>Move more slowly — Ir más despacio.</t>
+        </is>
+      </c>
+      <c r="D460" s="0" t="inlineStr">
+        <is>
+          <t>Slow down when driving.</t>
+        </is>
+      </c>
+      <c r="I460" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: slow down — Present: slows down — Past: slowed down — Past participle: slowed down. Inseparable, intransitive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="0" t="inlineStr">
+        <is>
+          <t>Hurry up</t>
+        </is>
+      </c>
+      <c r="B461" s="0" t="inlineStr">
+        <is>
+          <t>jári ap</t>
+        </is>
+      </c>
+      <c r="C461" s="0" t="inlineStr">
+        <is>
+          <t>Do something faster — Darse prisa.</t>
+        </is>
+      </c>
+      <c r="D461" s="0" t="inlineStr">
+        <is>
+          <t>Hurry up or we'll be late.</t>
+        </is>
+      </c>
+      <c r="I461" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: hurry up — Present: hurries up — Past: hurried up — Past participle: hurried up. Inseparable, intransitive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="0" t="inlineStr">
+        <is>
+          <t>Lie down</t>
+        </is>
+      </c>
+      <c r="B462" s="0" t="inlineStr">
+        <is>
+          <t>lái dáun</t>
+        </is>
+      </c>
+      <c r="C462" s="0" t="inlineStr">
+        <is>
+          <t>Lie on a bed or sofa — Acostarse o tumbarse.</t>
+        </is>
+      </c>
+      <c r="D462" s="0" t="inlineStr">
+        <is>
+          <t>I'm tired, so I'm going to lie down.</t>
+        </is>
+      </c>
+      <c r="I462" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: lie down — Present: lies down — Past: lay down — Past participle: lain down. Inseparable, intransitive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="0" t="inlineStr">
+        <is>
+          <t>Get dressed</t>
+        </is>
+      </c>
+      <c r="B463" s="0" t="inlineStr">
+        <is>
+          <t>guet drest</t>
+        </is>
+      </c>
+      <c r="C463" s="0" t="inlineStr">
+        <is>
+          <t>Put on your clothes — Vestirse.</t>
+        </is>
+      </c>
+      <c r="D463" s="0" t="inlineStr">
+        <is>
+          <t>The children got dressed quickly.</t>
+        </is>
+      </c>
+      <c r="I463" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get dressed — Present: gets dressed — Past: got dressed — Past participle: gotten dressed (US) / got dressed (UK). Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="0" t="inlineStr">
+        <is>
+          <t>Go to bed</t>
+        </is>
+      </c>
+      <c r="B464" s="0" t="inlineStr">
+        <is>
+          <t>góu tu bed</t>
+        </is>
+      </c>
+      <c r="C464" s="0" t="inlineStr">
+        <is>
+          <t>Go to sleep — Irse a dormir.</t>
+        </is>
+      </c>
+      <c r="D464" s="0" t="inlineStr">
+        <is>
+          <t>I go to bed at 11 p.m.</t>
+        </is>
+      </c>
+      <c r="I464" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: go to bed — Present: goes to bed — Past: went to bed — Past participle: gone to bed. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="0" t="inlineStr">
+        <is>
+          <t>Stay in</t>
+        </is>
+      </c>
+      <c r="B465" s="0" t="inlineStr">
+        <is>
+          <t>estéi in</t>
+        </is>
+      </c>
+      <c r="C465" s="0" t="inlineStr">
+        <is>
+          <t>Stay at home — Quedarse en casa.</t>
+        </is>
+      </c>
+      <c r="D465" s="0" t="inlineStr">
+        <is>
+          <t>I am staying in tonight.</t>
+        </is>
+      </c>
+      <c r="I465" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: stay in — Present: stays in — Past: stayed in — Past participle: stayed in. Inseparable, intransitive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="0" t="inlineStr">
+        <is>
+          <t>Sleep in</t>
+        </is>
+      </c>
+      <c r="B466" s="0" t="inlineStr">
+        <is>
+          <t>eslip in</t>
+        </is>
+      </c>
+      <c r="C466" s="0" t="inlineStr">
+        <is>
+          <t>Sleep later than usual — Dormir hasta tarde.</t>
+        </is>
+      </c>
+      <c r="D466" s="0" t="inlineStr">
+        <is>
+          <t>I slept in this morning.</t>
+        </is>
+      </c>
+      <c r="I466" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: sleep in — Present: sleeps in — Past: slept in — Past participle: slept in. Inseparable (no object).</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="0" t="inlineStr">
+        <is>
+          <t>Get in</t>
+        </is>
+      </c>
+      <c r="B467" s="0" t="inlineStr">
+        <is>
+          <t>guet in</t>
+        </is>
+      </c>
+      <c r="C467" s="0" t="inlineStr">
+        <is>
+          <t>Enter a car — Subirse a un coche.</t>
+        </is>
+      </c>
+      <c r="D467" s="0" t="inlineStr">
+        <is>
+          <t>Get in the car.</t>
+        </is>
+      </c>
+      <c r="I467" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get in — Present: gets in — Past: got in — Past participle: gotten in (US) / got in (UK). Inseparable; used specifically for small vehicles like cars.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="0" t="inlineStr">
+        <is>
+          <t>Take out</t>
+        </is>
+      </c>
+      <c r="B468" s="0" t="inlineStr">
+        <is>
+          <t>téik aut</t>
+        </is>
+      </c>
+      <c r="C468" s="0" t="inlineStr">
+        <is>
+          <t>Remove something — Sacar.</t>
+        </is>
+      </c>
+      <c r="D468" s="0" t="inlineStr">
+        <is>
+          <t>Take out the trash.</t>
+        </is>
+      </c>
+      <c r="I468" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: take out — Present: takes out — Past: took out — Past participle: taken out. Separable: take something out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="0" t="inlineStr">
+        <is>
+          <t>Try on</t>
+        </is>
+      </c>
+      <c r="B469" s="0" t="inlineStr">
+        <is>
+          <t>trái on</t>
+        </is>
+      </c>
+      <c r="C469" s="0" t="inlineStr">
+        <is>
+          <t>Put on clothes to see if they fit — Probarse ropa.</t>
+        </is>
+      </c>
+      <c r="D469" s="0" t="inlineStr">
+        <is>
+          <t>She tried on the dress.</t>
+        </is>
+      </c>
+      <c r="I469" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: try on — Present: tries on — Past: tried on — Past participle: tried on. Separable: try something on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="0" t="inlineStr">
+        <is>
+          <t>Put back</t>
+        </is>
+      </c>
+      <c r="B470" s="0" t="inlineStr">
+        <is>
+          <t>put bak</t>
+        </is>
+      </c>
+      <c r="C470" s="0" t="inlineStr">
+        <is>
+          <t>Return something to its place — Devolver algo a su lugar.</t>
+        </is>
+      </c>
+      <c r="D470" s="0" t="inlineStr">
+        <is>
+          <t>Put the book back on the shelf.</t>
+        </is>
+      </c>
+      <c r="I470" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: put back — Present: puts back — Past: put back — Past participle: put back. Separable: put something back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="0" t="inlineStr">
+        <is>
+          <t>Put down</t>
+        </is>
+      </c>
+      <c r="B471" s="0" t="inlineStr">
+        <is>
+          <t>put daun</t>
+        </is>
+      </c>
+      <c r="C471" s="0" t="inlineStr">
+        <is>
+          <t>Place something on a surface — Dejar algo en una superficie.</t>
+        </is>
+      </c>
+      <c r="D471" s="0" t="inlineStr">
+        <is>
+          <t>She put down her bag.</t>
+        </is>
+      </c>
+      <c r="I471" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: put down — Present: puts down — Past: put down — Past participle: put down. Separable: put something down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="0" t="inlineStr">
+        <is>
+          <t>Get on</t>
+        </is>
+      </c>
+      <c r="B472" s="0" t="inlineStr">
+        <is>
+          <t>guet on</t>
+        </is>
+      </c>
+      <c r="C472" s="0" t="inlineStr">
+        <is>
+          <t>Enter a bus, train, or plane — Subirse a un autobús, tren o avión.</t>
+        </is>
+      </c>
+      <c r="D472" s="0" t="inlineStr">
+        <is>
+          <t>He got on the bus.</t>
+        </is>
+      </c>
+      <c r="I472" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get on — Present: gets on — Past: got on — Past participle: gotten on (US) / got on (UK). Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="0" t="inlineStr">
+        <is>
+          <t>Get off</t>
+        </is>
+      </c>
+      <c r="B473" s="0" t="inlineStr">
+        <is>
+          <t>guet of</t>
+        </is>
+      </c>
+      <c r="C473" s="0" t="inlineStr">
+        <is>
+          <t>Leave a bus, train, or plane — Bajarse de un autobús, tren o avión.</t>
+        </is>
+      </c>
+      <c r="D473" s="0" t="inlineStr">
+        <is>
+          <t>She got off the train.</t>
+        </is>
+      </c>
+      <c r="I473" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get off — Present: gets off — Past: got off — Past participle: gotten off (US) / got off (UK). Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="0" t="inlineStr">
+        <is>
+          <t>Walk away</t>
+        </is>
+      </c>
+      <c r="B474" s="0" t="inlineStr">
+        <is>
+          <t>uók a-uéi</t>
+        </is>
+      </c>
+      <c r="C474" s="0" t="inlineStr">
+        <is>
+          <t>Leave by walking — Irse caminando.</t>
+        </is>
+      </c>
+      <c r="D474" s="0" t="inlineStr">
+        <is>
+          <t>He walked away.</t>
+        </is>
+      </c>
+      <c r="I474" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: walk away — Present: walks away — Past: walked away — Past participle: walked away. Intransitive; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="0" t="inlineStr">
+        <is>
+          <t>Walk by</t>
+        </is>
+      </c>
+      <c r="B475" s="0" t="inlineStr">
+        <is>
+          <t>uók bái</t>
+        </is>
+      </c>
+      <c r="C475" s="0" t="inlineStr">
+        <is>
+          <t>Pass someone or something while walking — Pasar caminando (al lado de).</t>
+        </is>
+      </c>
+      <c r="D475" s="0" t="inlineStr">
+        <is>
+          <t>She walked by the store.</t>
+        </is>
+      </c>
+      <c r="I475" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: walk by — Present: walks by — Past: walked by — Past participle: walked by. Prepositional verb; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="0" t="inlineStr">
+        <is>
+          <t>Move in</t>
+        </is>
+      </c>
+      <c r="B476" s="0" t="inlineStr">
+        <is>
+          <t>muv in</t>
+        </is>
+      </c>
+      <c r="C476" s="0" t="inlineStr">
+        <is>
+          <t>Start living in a new place — Mudarse (empezar a vivir en un sitio).</t>
+        </is>
+      </c>
+      <c r="D476" s="0" t="inlineStr">
+        <is>
+          <t>They moved in last week.</t>
+        </is>
+      </c>
+      <c r="I476" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: move in — Present: moves in — Past: moved in — Past participle: moved in. Intransitive; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="0" t="inlineStr">
+        <is>
+          <t>Move out</t>
+        </is>
+      </c>
+      <c r="B477" s="0" t="inlineStr">
+        <is>
+          <t>muv áut</t>
+        </is>
+      </c>
+      <c r="C477" s="0" t="inlineStr">
+        <is>
+          <t>Leave a place you live in — Mudarse (dejar de vivir en un sitio).</t>
+        </is>
+      </c>
+      <c r="D477" s="0" t="inlineStr">
+        <is>
+          <t>She moved out yesterday.</t>
+        </is>
+      </c>
+      <c r="I477" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: move out — Present: moves out — Past: moved out — Past participle: moved out. Intransitive; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="0" t="inlineStr">
+        <is>
+          <t>Pass by</t>
+        </is>
+      </c>
+      <c r="B478" s="0" t="inlineStr">
+        <is>
+          <t>pas bái</t>
+        </is>
+      </c>
+      <c r="C478" s="0" t="inlineStr">
+        <is>
+          <t>Go past a place without stopping — Pasar de largo.</t>
+        </is>
+      </c>
+      <c r="D478" s="0" t="inlineStr">
+        <is>
+          <t>We passed by the museum.</t>
+        </is>
+      </c>
+      <c r="I478" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: pass by — Present: passes by — Past: passed by — Past participle: passed by. Prepositional verb; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="0" t="inlineStr">
+        <is>
+          <t>Drive off</t>
+        </is>
+      </c>
+      <c r="B479" s="0" t="inlineStr">
+        <is>
+          <t>dráiv of</t>
+        </is>
+      </c>
+      <c r="C479" s="0" t="inlineStr">
+        <is>
+          <t>Leave quickly in a vehicle — Irse rápido en coche.</t>
+        </is>
+      </c>
+      <c r="D479" s="0" t="inlineStr">
+        <is>
+          <t>He drove off quickly.</t>
+        </is>
+      </c>
+      <c r="I479" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: drive off — Present: drives off — Past: drove off — Past participle: driven off. Intransitive; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="0" t="inlineStr">
+        <is>
+          <t>Go through</t>
+        </is>
+      </c>
+      <c r="B480" s="0" t="inlineStr">
+        <is>
+          <t>góu zru</t>
+        </is>
+      </c>
+      <c r="C480" s="0" t="inlineStr">
+        <is>
+          <t>Travel through a place — Atravesar.</t>
+        </is>
+      </c>
+      <c r="D480" s="0" t="inlineStr">
+        <is>
+          <t>We went through the tunnel.</t>
+        </is>
+      </c>
+      <c r="I480" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: go through — Present: goes through — Past: went through — Past participle: gone through. Prepositional verb; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="0" t="inlineStr">
+        <is>
+          <t>Step in</t>
+        </is>
+      </c>
+      <c r="B481" s="0" t="inlineStr">
+        <is>
+          <t>step in</t>
+        </is>
+      </c>
+      <c r="C481" s="0" t="inlineStr">
+        <is>
+          <t>Enter a place — Entrar.</t>
+        </is>
+      </c>
+      <c r="D481" s="0" t="inlineStr">
+        <is>
+          <t>She stepped in quietly.</t>
+        </is>
+      </c>
+      <c r="I481" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: step in — Present: steps in — Past: stepped in — Past participle: stepped in. Intransitive; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="0" t="inlineStr">
+        <is>
+          <t>Step out</t>
+        </is>
+      </c>
+      <c r="B482" s="0" t="inlineStr">
+        <is>
+          <t>estep áut</t>
+        </is>
+      </c>
+      <c r="C482" s="0" t="inlineStr">
+        <is>
+          <t>Leave a place for a short time — Salir un momento.</t>
+        </is>
+      </c>
+      <c r="D482" s="0" t="inlineStr">
+        <is>
+          <t>He stepped out for a minute.</t>
+        </is>
+      </c>
+      <c r="I482" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: step out — Present: steps out — Past: stepped out — Past participle: stepped out. Inseparable (intransitive).</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="0" t="inlineStr">
+        <is>
+          <t>Move along</t>
+        </is>
+      </c>
+      <c r="B483" s="0" t="inlineStr">
+        <is>
+          <t>muv alóng</t>
+        </is>
+      </c>
+      <c r="C483" s="0" t="inlineStr">
+        <is>
+          <t>Continue moving forward — Seguir avanzando.</t>
+        </is>
+      </c>
+      <c r="D483" s="0" t="inlineStr">
+        <is>
+          <t>The crowd moved along the street.</t>
+        </is>
+      </c>
+      <c r="I483" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: move along — Present: moves along — Past: moved along — Past participle: moved along. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="0" t="inlineStr">
+        <is>
+          <t>Go across</t>
+        </is>
+      </c>
+      <c r="B484" s="0" t="inlineStr">
+        <is>
+          <t>gou acrós</t>
+        </is>
+      </c>
+      <c r="C484" s="0" t="inlineStr">
+        <is>
+          <t>Move from one side to another — Cruzar.</t>
+        </is>
+      </c>
+      <c r="D484" s="0" t="inlineStr">
+        <is>
+          <t>They went across the bridge.</t>
+        </is>
+      </c>
+      <c r="I484" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: go across — Present: goes across — Past: went across — Past participle: gone across. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="0" t="inlineStr">
+        <is>
+          <t>Cross over</t>
+        </is>
+      </c>
+      <c r="B485" s="0" t="inlineStr">
+        <is>
+          <t>cros óuver</t>
+        </is>
+      </c>
+      <c r="C485" s="0" t="inlineStr">
+        <is>
+          <t>Move from one side to another — Cruzar.</t>
+        </is>
+      </c>
+      <c r="D485" s="0" t="inlineStr">
+        <is>
+          <t>We crossed over the road.</t>
+        </is>
+      </c>
+      <c r="I485" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: cross over — Present: crosses over — Past: crossed over — Past participle: crossed over. Usually inseparable, used intransitively.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="0" t="inlineStr">
+        <is>
+          <t>Travel around</t>
+        </is>
+      </c>
+      <c r="B486" s="0" t="inlineStr">
+        <is>
+          <t>trável araund</t>
+        </is>
+      </c>
+      <c r="C486" s="0" t="inlineStr">
+        <is>
+          <t>Visit many different places — Viajar por varios lugares.</t>
+        </is>
+      </c>
+      <c r="D486" s="0" t="inlineStr">
+        <is>
+          <t>They traveled around Europe.</t>
+        </is>
+      </c>
+      <c r="I486" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: travel around — Present: travels around — Past: traveled around — Past participle: traveled around. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="0" t="inlineStr">
+        <is>
+          <t>Follow along</t>
+        </is>
+      </c>
+      <c r="B487" s="0" t="inlineStr">
+        <is>
+          <t>fólou alóng</t>
+        </is>
+      </c>
+      <c r="C487" s="0" t="inlineStr">
+        <is>
+          <t>Go behind someone — Seguir a alguien.</t>
+        </is>
+      </c>
+      <c r="D487" s="0" t="inlineStr">
+        <is>
+          <t>The children followed along.</t>
+        </is>
+      </c>
+      <c r="I487" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: follow along — Present: follows along — Past: followed along — Past participle: followed along. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="0" t="inlineStr">
+        <is>
+          <t>Drop by</t>
+        </is>
+      </c>
+      <c r="B488" s="0" t="inlineStr">
+        <is>
+          <t>drap bái</t>
+        </is>
+      </c>
+      <c r="C488" s="0" t="inlineStr">
+        <is>
+          <t>Visit someone for a short time — Pasar a visitar.</t>
+        </is>
+      </c>
+      <c r="D488" s="0" t="inlineStr">
+        <is>
+          <t>We dropped by after work.</t>
+        </is>
+      </c>
+      <c r="I488" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: drop by — Present: drops by — Past: dropped by — Past participle: dropped by. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="0" t="inlineStr">
+        <is>
+          <t>Go up</t>
+        </is>
+      </c>
+      <c r="B489" s="0" t="inlineStr">
+        <is>
+          <t>gou ap</t>
+        </is>
+      </c>
+      <c r="C489" s="0" t="inlineStr">
+        <is>
+          <t>Move to a higher place — Subir.</t>
+        </is>
+      </c>
+      <c r="D489" s="0" t="inlineStr">
+        <is>
+          <t>We went up the hill.</t>
+        </is>
+      </c>
+      <c r="I489" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: go up — Present: goes up — Past: went up — Past participle: gone up. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="0" t="inlineStr">
+        <is>
+          <t>Go past</t>
+        </is>
+      </c>
+      <c r="B490" s="0" t="inlineStr">
+        <is>
+          <t>gou past</t>
+        </is>
+      </c>
+      <c r="C490" s="0" t="inlineStr">
+        <is>
+          <t>Move beyond something — Pasar por delante de algo.</t>
+        </is>
+      </c>
+      <c r="D490" s="0" t="inlineStr">
+        <is>
+          <t>We went past library.</t>
+        </is>
+      </c>
+      <c r="I490" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: go past — Present: goes past — Past: went past — Past participle: gone past. Not separable (prepositional verb).</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="0" t="inlineStr">
+        <is>
+          <t>Go in</t>
+        </is>
+      </c>
+      <c r="B491" s="0" t="inlineStr">
+        <is>
+          <t>gou in</t>
+        </is>
+      </c>
+      <c r="C491" s="0" t="inlineStr">
+        <is>
+          <t>Enter a building — Entrar.</t>
+        </is>
+      </c>
+      <c r="D491" s="0" t="inlineStr">
+        <is>
+          <t>She went in the house.</t>
+        </is>
+      </c>
+      <c r="I491" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: go in — Present: goes in — Past: went in — Past participle: gone in. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="0" t="inlineStr">
+        <is>
+          <t>Head back</t>
+        </is>
+      </c>
+      <c r="B492" s="0" t="inlineStr">
+        <is>
+          <t>jed bak</t>
+        </is>
+      </c>
+      <c r="C492" s="0" t="inlineStr">
+        <is>
+          <t>Return to a previous place — Regresar.</t>
+        </is>
+      </c>
+      <c r="D492" s="0" t="inlineStr">
+        <is>
+          <t>He headed back home.</t>
+        </is>
+      </c>
+      <c r="I492" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: head back — Present: heads back — Past: headed back — Past participle: headed back. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="0" t="inlineStr">
+        <is>
+          <t>Move on</t>
+        </is>
+      </c>
+      <c r="B493" s="0" t="inlineStr">
+        <is>
+          <t>muv on</t>
+        </is>
+      </c>
+      <c r="C493" s="0" t="inlineStr">
+        <is>
+          <t>Continue to another place — Continuar hacia otro lugar.</t>
+        </is>
+      </c>
+      <c r="D493" s="0" t="inlineStr">
+        <is>
+          <t>After the park, we moved on to the museum.</t>
+        </is>
+      </c>
+      <c r="I493" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: move on — Present: moves on — Past: moved on — Past participle: moved on. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="0" t="inlineStr">
+        <is>
+          <t>Figure out</t>
+        </is>
+      </c>
+      <c r="B494" s="0" t="inlineStr">
+        <is>
+          <t>fíguer aut</t>
+        </is>
+      </c>
+      <c r="C494" s="0" t="inlineStr">
+        <is>
+          <t>Understand or solve something — Entender o resolver algo.</t>
+        </is>
+      </c>
+      <c r="D494" s="0" t="inlineStr">
+        <is>
+          <t>We figured out the problem.</t>
+        </is>
+      </c>
+      <c r="I494" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: figure out — Present: figures out — Past: figured out — Past participle: figured out. Separable: figure something out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="0" t="inlineStr">
+        <is>
+          <t>Hand in</t>
+        </is>
+      </c>
+      <c r="B495" s="0" t="inlineStr">
+        <is>
+          <t>jand in</t>
+        </is>
+      </c>
+      <c r="C495" s="0" t="inlineStr">
+        <is>
+          <t>Submit work or an assignment — Entregar un trabajo.</t>
+        </is>
+      </c>
+      <c r="D495" s="0" t="inlineStr">
+        <is>
+          <t>I handed in my assignment.</t>
+        </is>
+      </c>
+      <c r="I495" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: hand in — Present: hands in — Past: handed in — Past participle: handed in. Separable: hand something in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="0" t="inlineStr">
+        <is>
+          <t>Turn in</t>
+        </is>
+      </c>
+      <c r="B496" s="0" t="inlineStr">
+        <is>
+          <t>tern in</t>
+        </is>
+      </c>
+      <c r="C496" s="0" t="inlineStr">
+        <is>
+          <t>Submit work or an assignment — Entregar un trabajo.</t>
+        </is>
+      </c>
+      <c r="D496" s="0" t="inlineStr">
+        <is>
+          <t>She turned in her report.</t>
+        </is>
+      </c>
+      <c r="I496" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: turn in — Present: turns in — Past: turned in — Past participle: turned in. Separable: turn something in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="0" t="inlineStr">
+        <is>
+          <t>Fill in</t>
+        </is>
+      </c>
+      <c r="B497" s="0" t="inlineStr">
+        <is>
+          <t>fil in</t>
+        </is>
+      </c>
+      <c r="C497" s="0" t="inlineStr">
+        <is>
+          <t>Complete missing information — Rellenar.</t>
+        </is>
+      </c>
+      <c r="D497" s="0" t="inlineStr">
+        <is>
+          <t>Fill in your name on the form.</t>
+        </is>
+      </c>
+      <c r="I497" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: fill in — Present: fills in — Past: filled in — Past participle: filled in. Separable: fill something in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="0" t="inlineStr">
+        <is>
+          <t>Read over</t>
+        </is>
+      </c>
+      <c r="B498" s="0" t="inlineStr">
+        <is>
+          <t>riid óuver</t>
+        </is>
+      </c>
+      <c r="C498" s="0" t="inlineStr">
+        <is>
+          <t>Read again and check — Revisar.</t>
+        </is>
+      </c>
+      <c r="D498" s="0" t="inlineStr">
+        <is>
+          <t>She read over her essay before submitting it.</t>
+        </is>
+      </c>
+      <c r="I498" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: read over — Present: reads over — Past: read over — Past participle: read over (pronounced "red" in past forms). Separable: read something over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="0" t="inlineStr">
+        <is>
+          <t>Work on</t>
+        </is>
+      </c>
+      <c r="B499" s="0" t="inlineStr">
+        <is>
+          <t>uórk on</t>
+        </is>
+      </c>
+      <c r="C499" s="0" t="inlineStr">
+        <is>
+          <t>Spend time improving something — Trabajar en.</t>
+        </is>
+      </c>
+      <c r="D499" s="0" t="inlineStr">
+        <is>
+          <t>I am working on my project.</t>
+        </is>
+      </c>
+      <c r="I499" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: work on — Present: works on — Past: worked on — Past participle: worked on. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="0" t="inlineStr">
+        <is>
+          <t>Keep on</t>
+        </is>
+      </c>
+      <c r="B500" s="0" t="inlineStr">
+        <is>
+          <t>kiip on</t>
+        </is>
+      </c>
+      <c r="C500" s="0" t="inlineStr">
+        <is>
+          <t>Continue doing something — Seguir haciendo algo.</t>
+        </is>
+      </c>
+      <c r="D500" s="0" t="inlineStr">
+        <is>
+          <t>Keep on practicing English.</t>
+        </is>
+      </c>
+      <c r="I500" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: keep on — Present: keeps on — Past: kept on — Past participle: kept on. Inseparable; usually followed by a gerund.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="0" t="inlineStr">
+        <is>
+          <t>Keep up with</t>
+        </is>
+      </c>
+      <c r="B501" s="0" t="inlineStr">
+        <is>
+          <t>kiip ap uíz</t>
+        </is>
+      </c>
+      <c r="C501" s="0" t="inlineStr">
+        <is>
+          <t>Stay at the same pace as others — Mantenerse al día con.</t>
+        </is>
+      </c>
+      <c r="D501" s="0" t="inlineStr">
+        <is>
+          <t>She keeps up with the class easily.</t>
+        </is>
+      </c>
+      <c r="I501" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: keep up with — Present: keeps up with — Past: kept up with — Past participle: kept up with. Inseparable, three-word phrasal verb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="0" t="inlineStr">
+        <is>
+          <t>Point out</t>
+        </is>
+      </c>
+      <c r="B502" s="0" t="inlineStr">
+        <is>
+          <t>póint aut</t>
+        </is>
+      </c>
+      <c r="C502" s="0" t="inlineStr">
+        <is>
+          <t>Show or mention something important — Señalar.</t>
+        </is>
+      </c>
+      <c r="D502" s="0" t="inlineStr">
+        <is>
+          <t>The teacher pointed out the mistake.</t>
+        </is>
+      </c>
+      <c r="I502" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: point out — Present: points out — Past: pointed out — Past participle: pointed out. Separable: point something out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="0" t="inlineStr">
+        <is>
+          <t>Bring up</t>
+        </is>
+      </c>
+      <c r="B503" s="0" t="inlineStr">
+        <is>
+          <t>bring ap</t>
+        </is>
+      </c>
+      <c r="C503" s="0" t="inlineStr">
+        <is>
+          <t>Introduce a topic — Mencionar.</t>
+        </is>
+      </c>
+      <c r="D503" s="0" t="inlineStr">
+        <is>
+          <t>He brought up an interesting question in class.</t>
+        </is>
+      </c>
+      <c r="I503" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: bring up — Present: brings up — Past: brought up — Past participle: brought up. Separable: bring something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="0" t="inlineStr">
+        <is>
+          <t>Follow up</t>
+        </is>
+      </c>
+      <c r="B504" s="0" t="inlineStr">
+        <is>
+          <t>fálou ap</t>
+        </is>
+      </c>
+      <c r="C504" s="0" t="inlineStr">
+        <is>
+          <t>Take action after something — Dar seguimiento.</t>
+        </is>
+      </c>
+      <c r="D504" s="0" t="inlineStr">
+        <is>
+          <t>The manager followed up with the team after meeting.</t>
+        </is>
+      </c>
+      <c r="I504" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: follow up — Present: follows up — Past: followed up — Past participle: followed up. Usually inseparable; often used with "with" or "on".</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="0" t="inlineStr">
+        <is>
+          <t>Leave out</t>
+        </is>
+      </c>
+      <c r="B505" s="0" t="inlineStr">
+        <is>
+          <t>liiv aut</t>
+        </is>
+      </c>
+      <c r="C505" s="0" t="inlineStr">
+        <is>
+          <t>Not include something — Omitir.</t>
+        </is>
+      </c>
+      <c r="D505" s="0" t="inlineStr">
+        <is>
+          <t>Don't leave out any details.</t>
+        </is>
+      </c>
+      <c r="I505" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: leave out — Present: leaves out — Past: left out — Past participle: left out. Separable: leave something out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="0" t="inlineStr">
+        <is>
+          <t>Put off</t>
+        </is>
+      </c>
+      <c r="B506" s="0" t="inlineStr">
+        <is>
+          <t>put óf</t>
+        </is>
+      </c>
+      <c r="C506" s="0" t="inlineStr">
+        <is>
+          <t>Delay something — Posponer.</t>
+        </is>
+      </c>
+      <c r="D506" s="0" t="inlineStr">
+        <is>
+          <t>They put off the meeting until next week.</t>
+        </is>
+      </c>
+      <c r="I506" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: put off — Present: puts off — Past: put off — Past participle: put off. Separable: put something off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="0" t="inlineStr">
+        <is>
+          <t>Check over</t>
+        </is>
+      </c>
+      <c r="B507" s="0" t="inlineStr">
+        <is>
+          <t>chek óuver</t>
+        </is>
+      </c>
+      <c r="C507" s="0" t="inlineStr">
+        <is>
+          <t>Review carefully — Revisar cuidadosamente.</t>
+        </is>
+      </c>
+      <c r="D507" s="0" t="inlineStr">
+        <is>
+          <t>Check over your answers before submitting.</t>
+        </is>
+      </c>
+      <c r="I507" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: check over — Present: checks over — Past: checked over — Past participle: checked over. Separable: check something over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="0" t="inlineStr">
+        <is>
+          <t>Think over</t>
+        </is>
+      </c>
+      <c r="B508" s="0" t="inlineStr">
+        <is>
+          <t>zink óuver</t>
+        </is>
+      </c>
+      <c r="C508" s="0" t="inlineStr">
+        <is>
+          <t>Think carefully about something — Reflexionar sobre algo.</t>
+        </is>
+      </c>
+      <c r="D508" s="0" t="inlineStr">
+        <is>
+          <t>Think over the idea before deciding.</t>
+        </is>
+      </c>
+      <c r="I508" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: think over — Present: thinks over — Past: thought over — Past participle: thought over. Separable: think something over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="0" t="inlineStr">
+        <is>
+          <t>Deal with</t>
+        </is>
+      </c>
+      <c r="B509" s="0" t="inlineStr">
+        <is>
+          <t>díl wiz</t>
+        </is>
+      </c>
+      <c r="C509" s="0" t="inlineStr">
+        <is>
+          <t>Handle a task or problem — Ocuparse de.</t>
+        </is>
+      </c>
+      <c r="D509" s="0" t="inlineStr">
+        <is>
+          <t>She deals with customer complaints.</t>
+        </is>
+      </c>
+      <c r="I509" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: deal with — Present: deals with — Past: dealt with — Past participle: dealt with. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="0" t="inlineStr">
+        <is>
+          <t>Focus on</t>
+        </is>
+      </c>
+      <c r="B510" s="0" t="inlineStr">
+        <is>
+          <t>fócus on</t>
+        </is>
+      </c>
+      <c r="C510" s="0" t="inlineStr">
+        <is>
+          <t>Pay attention to something important — Concentrarse en.</t>
+        </is>
+      </c>
+      <c r="D510" s="0" t="inlineStr">
+        <is>
+          <t>Focus on your homework.</t>
+        </is>
+      </c>
+      <c r="I510" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: focus on — Present: focuses on — Past: focused on — Past participle: focused on. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="0" t="inlineStr">
+        <is>
+          <t>Sum up</t>
+        </is>
+      </c>
+      <c r="B511" s="0" t="inlineStr">
+        <is>
+          <t>sam ap</t>
+        </is>
+      </c>
+      <c r="C511" s="0" t="inlineStr">
+        <is>
+          <t>Give a short summary — Resumir.</t>
+        </is>
+      </c>
+      <c r="D511" s="0" t="inlineStr">
+        <is>
+          <t>The teacher summed up the lesson.</t>
+        </is>
+      </c>
+      <c r="I511" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb (doubles consonant). Base: sum up — Present: sums up — Past: summed up — Past participle: summed up. Separable: sum something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="0" t="inlineStr">
+        <is>
+          <t>Look through</t>
+        </is>
+      </c>
+      <c r="B512" s="0" t="inlineStr">
+        <is>
+          <t>luk zru</t>
+        </is>
+      </c>
+      <c r="C512" s="0" t="inlineStr">
+        <is>
+          <t>Read or examine something quickly — Revisar rápidamente.</t>
+        </is>
+      </c>
+      <c r="D512" s="0" t="inlineStr">
+        <is>
+          <t>She looked through her notes before the test.</t>
+        </is>
+      </c>
+      <c r="I512" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: look through — Present: looks through — Past: looked through — Past participle: looked through. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="0" t="inlineStr">
+        <is>
+          <t>Write up</t>
+        </is>
+      </c>
+      <c r="B513" s="0" t="inlineStr">
+        <is>
+          <t>rait ap</t>
+        </is>
+      </c>
+      <c r="C513" s="0" t="inlineStr">
+        <is>
+          <t>Write a complete report or document — Redactar por completo.</t>
+        </is>
+      </c>
+      <c r="D513" s="0" t="inlineStr">
+        <is>
+          <t>He wrote up the report yesterday.</t>
+        </is>
+      </c>
+      <c r="I513" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: write up — Present: writes up — Past: wrote up — Past participle: written up. Separable: write something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="0" t="inlineStr">
+        <is>
+          <t>Speak up</t>
+        </is>
+      </c>
+      <c r="B514" s="0" t="inlineStr">
+        <is>
+          <t>spik ap</t>
+        </is>
+      </c>
+      <c r="C514" s="0" t="inlineStr">
+        <is>
+          <t>Speak louder — Hablar más alto.</t>
+        </is>
+      </c>
+      <c r="D514" s="0" t="inlineStr">
+        <is>
+          <t>Please speak up.</t>
+        </is>
+      </c>
+      <c r="I514" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: speak up — Present: speaks up — Past: spoke up — Past participle: spoken up. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="0" t="inlineStr">
+        <is>
+          <t>Get back to</t>
+        </is>
+      </c>
+      <c r="B515" s="0" t="inlineStr">
+        <is>
+          <t>guet bak tu</t>
+        </is>
+      </c>
+      <c r="C515" s="0" t="inlineStr">
+        <is>
+          <t>Reply later — Responder más tarde.</t>
+        </is>
+      </c>
+      <c r="D515" s="0" t="inlineStr">
+        <is>
+          <t>I'll get back to you tomorrow.</t>
+        </is>
+      </c>
+      <c r="I515" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get back to — Present: gets back to — Past: got back to — Past participle: got/gotten back to. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="0" t="inlineStr">
+        <is>
+          <t>Talk over</t>
+        </is>
+      </c>
+      <c r="B516" s="0" t="inlineStr">
+        <is>
+          <t>tok óuver</t>
+        </is>
+      </c>
+      <c r="C516" s="0" t="inlineStr">
+        <is>
+          <t>Discuss something carefully — Discutir algo detenidamente.</t>
+        </is>
+      </c>
+      <c r="D516" s="0" t="inlineStr">
+        <is>
+          <t>Let's talk over the plan.</t>
+        </is>
+      </c>
+      <c r="I516" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: talk over — Present: talks over — Past: talked over — Past participle: talked over. Separable: talk something over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="0" t="inlineStr">
+        <is>
+          <t>Ask for</t>
+        </is>
+      </c>
+      <c r="B517" s="0" t="inlineStr">
+        <is>
+          <t>ask for</t>
+        </is>
+      </c>
+      <c r="C517" s="0" t="inlineStr">
+        <is>
+          <t>Request something — Pedir algo.</t>
+        </is>
+      </c>
+      <c r="D517" s="0" t="inlineStr">
+        <is>
+          <t>She asked for help.</t>
+        </is>
+      </c>
+      <c r="I517" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: ask for — Present: asks for — Past: asked for — Past participle: asked for. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="0" t="inlineStr">
+        <is>
+          <t>Reply to</t>
+        </is>
+      </c>
+      <c r="B518" s="0" t="inlineStr">
+        <is>
+          <t>riplái tu</t>
+        </is>
+      </c>
+      <c r="C518" s="0" t="inlineStr">
+        <is>
+          <t>Answer a message or question — Responder a un mensaje o pregunta.</t>
+        </is>
+      </c>
+      <c r="D518" s="0" t="inlineStr">
+        <is>
+          <t>He replied to my email.</t>
+        </is>
+      </c>
+      <c r="I518" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: reply to — Present: replies to — Past: replied to — Past participle: replied to. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="0" t="inlineStr">
+        <is>
+          <t>Get through</t>
+        </is>
+      </c>
+      <c r="B519" s="0" t="inlineStr">
+        <is>
+          <t>guet zrú</t>
+        </is>
+      </c>
+      <c r="C519" s="0" t="inlineStr">
+        <is>
+          <t>Successfully contact someone — Lograr comunicarse con alguien.</t>
+        </is>
+      </c>
+      <c r="D519" s="0" t="inlineStr">
+        <is>
+          <t>I finally got through to her.</t>
+        </is>
+      </c>
+      <c r="I519" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get through — Present: gets through — Past: got through — Past participle: got/gotten through. Inseparable, usually followed by 'to'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="0" t="inlineStr">
+        <is>
+          <t>Call off</t>
+        </is>
+      </c>
+      <c r="B520" s="0" t="inlineStr">
+        <is>
+          <t>col of</t>
+        </is>
+      </c>
+      <c r="C520" s="0" t="inlineStr">
+        <is>
+          <t>Cancel something — Cancelar algo.</t>
+        </is>
+      </c>
+      <c r="D520" s="0" t="inlineStr">
+        <is>
+          <t>They called off the meeting.</t>
+        </is>
+      </c>
+      <c r="I520" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: call off — Present: calls off — Past: called off — Past participle: called off. Separable: call something off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="0" t="inlineStr">
+        <is>
+          <t>Reach out</t>
+        </is>
+      </c>
+      <c r="B521" s="0" t="inlineStr">
+        <is>
+          <t>rich áut</t>
+        </is>
+      </c>
+      <c r="C521" s="0" t="inlineStr">
+        <is>
+          <t>Contact someone — Contactar a alguien.</t>
+        </is>
+      </c>
+      <c r="D521" s="0" t="inlineStr">
+        <is>
+          <t>She reached out to a friend.</t>
+        </is>
+      </c>
+      <c r="I521" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: reach out — Present: reaches out — Past: reached out — Past participle: reached out. Inseparable, often followed by 'to'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="0" t="inlineStr">
+        <is>
+          <t>Listen in</t>
+        </is>
+      </c>
+      <c r="B522" s="0" t="inlineStr">
+        <is>
+          <t>lísen in</t>
+        </is>
+      </c>
+      <c r="C522" s="0" t="inlineStr">
+        <is>
+          <t>Listen to a conversation without being invited — Escuchar a escondidas.</t>
+        </is>
+      </c>
+      <c r="D522" s="0" t="inlineStr">
+        <is>
+          <t>He listened in on the conversation.</t>
+        </is>
+      </c>
+      <c r="I522" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: listen in — Present: listens in — Past: listened in — Past participle: listened in. Inseparable; often followed by 'on'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="0" t="inlineStr">
+        <is>
+          <t>Read out</t>
+        </is>
+      </c>
+      <c r="B523" s="0" t="inlineStr">
+        <is>
+          <t>rid áut</t>
+        </is>
+      </c>
+      <c r="C523" s="0" t="inlineStr">
+        <is>
+          <t>Read something aloud — Leer en voz alta.</t>
+        </is>
+      </c>
+      <c r="D523" s="0" t="inlineStr">
+        <is>
+          <t>The teacher read out the names.</t>
+        </is>
+      </c>
+      <c r="I523" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb (present 'rid', past/participle 'red' in pronunciation, same spelling 'read'). Base: read out — Present: reads out — Past: read out — Past participle: read out. Separable: read something out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="0" t="inlineStr">
+        <is>
+          <t>Pass on</t>
+        </is>
+      </c>
+      <c r="B524" s="0" t="inlineStr">
+        <is>
+          <t>pas on</t>
+        </is>
+      </c>
+      <c r="C524" s="0" t="inlineStr">
+        <is>
+          <t>Give information to another person — Transmitir información.</t>
+        </is>
+      </c>
+      <c r="D524" s="0" t="inlineStr">
+        <is>
+          <t>Please pass on the message.</t>
+        </is>
+      </c>
+      <c r="I524" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: pass on — Present: passes on — Past: passed on — Past participle: passed on. Separable: pass something on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="0" t="inlineStr">
+        <is>
+          <t>Tell apart</t>
+        </is>
+      </c>
+      <c r="B525" s="0" t="inlineStr">
+        <is>
+          <t>tel apárt</t>
+        </is>
+      </c>
+      <c r="C525" s="0" t="inlineStr">
+        <is>
+          <t>Recognize the difference between things — Distinguir, diferenciar.</t>
+        </is>
+      </c>
+      <c r="D525" s="0" t="inlineStr">
+        <is>
+          <t>I can't tell the twins apart.</t>
+        </is>
+      </c>
+      <c r="I525" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: tell apart — Present: tells apart — Past: told apart — Past participle: told apart. Separable: tell them apart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="0" t="inlineStr">
+        <is>
+          <t>Write back</t>
+        </is>
+      </c>
+      <c r="B526" s="0" t="inlineStr">
+        <is>
+          <t>ráit bak</t>
+        </is>
+      </c>
+      <c r="C526" s="0" t="inlineStr">
+        <is>
+          <t>Reply in writing — Responder por escrito.</t>
+        </is>
+      </c>
+      <c r="D526" s="0" t="inlineStr">
+        <is>
+          <t>She wrote back immediately.</t>
+        </is>
+      </c>
+      <c r="I526" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: write back — Present: writes back — Past: wrote back — Past participle: written back. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="0" t="inlineStr">
+        <is>
+          <t>Call on</t>
+        </is>
+      </c>
+      <c r="B527" s="0" t="inlineStr">
+        <is>
+          <t>col on</t>
+        </is>
+      </c>
+      <c r="C527" s="0" t="inlineStr">
+        <is>
+          <t>Ask someone to speak or answer — Pedir que hable o responda.</t>
+        </is>
+      </c>
+      <c r="D527" s="0" t="inlineStr">
+        <is>
+          <t>The teacher called on Tom.</t>
+        </is>
+      </c>
+      <c r="I527" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: call on — Present: calls on — Past: called on — Past participle: called on. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="0" t="inlineStr">
+        <is>
+          <t>Check in</t>
+        </is>
+      </c>
+      <c r="B528" s="0" t="inlineStr">
+        <is>
+          <t>chek in</t>
+        </is>
+      </c>
+      <c r="C528" s="0" t="inlineStr">
+        <is>
+          <t>Report your arrival or status — Registrarse.</t>
+        </is>
+      </c>
+      <c r="D528" s="0" t="inlineStr">
+        <is>
+          <t>I checked in at the hotel.</t>
+        </is>
+      </c>
+      <c r="I528" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: check in — Present: checks in — Past: checked in — Past participle: checked in. Usually inseparable in this sense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="0" t="inlineStr">
+        <is>
+          <t>Hear from</t>
+        </is>
+      </c>
+      <c r="B529" s="0" t="inlineStr">
+        <is>
+          <t>jíer from</t>
+        </is>
+      </c>
+      <c r="C529" s="0" t="inlineStr">
+        <is>
+          <t>Receive a message from someone — Recibir noticias de alguien.</t>
+        </is>
+      </c>
+      <c r="D529" s="0" t="inlineStr">
+        <is>
+          <t>I haven't heard from him yet.</t>
+        </is>
+      </c>
+      <c r="I529" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: hear from — Present: hears from — Past: heard from — Past participle: heard from. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="0" t="inlineStr">
+        <is>
+          <t>Send back</t>
+        </is>
+      </c>
+      <c r="B530" s="0" t="inlineStr">
+        <is>
+          <t>send bák</t>
+        </is>
+      </c>
+      <c r="C530" s="0" t="inlineStr">
+        <is>
+          <t>Return something — Devolver algo.</t>
+        </is>
+      </c>
+      <c r="D530" s="0" t="inlineStr">
+        <is>
+          <t>She sent back the package.</t>
+        </is>
+      </c>
+      <c r="I530" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: send back — Present: sends back — Past: sent back — Past participle: sent back. Separable: send something back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="0" t="inlineStr">
+        <is>
+          <t>Speak out</t>
+        </is>
+      </c>
+      <c r="B531" s="0" t="inlineStr">
+        <is>
+          <t>spik áut</t>
+        </is>
+      </c>
+      <c r="C531" s="0" t="inlineStr">
+        <is>
+          <t>Express an opinion openly — Hablar abiertamente.</t>
+        </is>
+      </c>
+      <c r="D531" s="0" t="inlineStr">
+        <is>
+          <t>He spoke out against  bullying.</t>
+        </is>
+      </c>
+      <c r="I531" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: speak out — Present: speaks out — Past: spoke out — Past participle: spoken out. Inseparable; often followed by 'against'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="0" t="inlineStr">
+        <is>
+          <t>Talk back</t>
+        </is>
+      </c>
+      <c r="B532" s="0" t="inlineStr">
+        <is>
+          <t>tok bák</t>
+        </is>
+      </c>
+      <c r="C532" s="0" t="inlineStr">
+        <is>
+          <t>Answer rudely — Contestar de mala manera.</t>
+        </is>
+      </c>
+      <c r="D532" s="0" t="inlineStr">
+        <is>
+          <t>Don't talk back to your parents.</t>
+        </is>
+      </c>
+      <c r="I532" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: talk back — Present: talks back — Past: talked back — Past participle: talked back. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="0" t="inlineStr">
+        <is>
+          <t>Put through</t>
+        </is>
+      </c>
+      <c r="B533" s="0" t="inlineStr">
+        <is>
+          <t>put zrú</t>
+        </is>
+      </c>
+      <c r="C533" s="0" t="inlineStr">
+        <is>
+          <t>Connect a phone call — Poner en contacto (por teléfono).</t>
+        </is>
+      </c>
+      <c r="D533" s="0" t="inlineStr">
+        <is>
+          <t>The receptionist put me through to the manager.</t>
+        </is>
+      </c>
+      <c r="I533" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb (no change in past forms). Base: put through — Present: puts through — Past: put through — Past participle: put through. Separable: put someone through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="0" t="inlineStr">
+        <is>
+          <t>Ring back</t>
+        </is>
+      </c>
+      <c r="B534" s="0" t="inlineStr">
+        <is>
+          <t>ring bák</t>
+        </is>
+      </c>
+      <c r="C534" s="0" t="inlineStr">
+        <is>
+          <t>Call someone again — Volver a llamar.</t>
+        </is>
+      </c>
+      <c r="D534" s="0" t="inlineStr">
+        <is>
+          <t>I'll ring you back later.</t>
+        </is>
+      </c>
+      <c r="I534" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: ring back — Present: rings back — Past: rang back — Past participle: rung back. Separable: ring someone back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="0" t="inlineStr">
+        <is>
+          <t>Call around</t>
+        </is>
+      </c>
+      <c r="B535" s="0" t="inlineStr">
+        <is>
+          <t>col araúnd</t>
+        </is>
+      </c>
+      <c r="C535" s="0" t="inlineStr">
+        <is>
+          <t>Call several people — Llamar a varias personas.</t>
+        </is>
+      </c>
+      <c r="D535" s="0" t="inlineStr">
+        <is>
+          <t>He called around for information.</t>
+        </is>
+      </c>
+      <c r="I535" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: call around — Present: calls around — Past: called around — Past participle: called around. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="0" t="inlineStr">
+        <is>
+          <t>Ask around</t>
+        </is>
+      </c>
+      <c r="B536" s="0" t="inlineStr">
+        <is>
+          <t>ask araúnd</t>
+        </is>
+      </c>
+      <c r="C536" s="0" t="inlineStr">
+        <is>
+          <t>Ask several people — Preguntar por ahí.</t>
+        </is>
+      </c>
+      <c r="D536" s="0" t="inlineStr">
+        <is>
+          <t>She asked around for advice.</t>
+        </is>
+      </c>
+      <c r="I536" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: ask around — Present: asks around — Past: asked around — Past participle: asked around. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="0" t="inlineStr">
+        <is>
+          <t>Talk to</t>
+        </is>
+      </c>
+      <c r="B537" s="0" t="inlineStr">
+        <is>
+          <t>tók tu</t>
+        </is>
+      </c>
+      <c r="C537" s="0" t="inlineStr">
+        <is>
+          <t>Speak with someone — Hablar con alguien.</t>
+        </is>
+      </c>
+      <c r="D537" s="0" t="inlineStr">
+        <is>
+          <t>I talked to my teacher.</t>
+        </is>
+      </c>
+      <c r="I537" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: talk to — Present: talks to — Past: talked to — Past participle: talked to. Inseparable; takes a direct object after 'to'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="0" t="inlineStr">
+        <is>
+          <t>Chat with</t>
+        </is>
+      </c>
+      <c r="B538" s="0" t="inlineStr">
+        <is>
+          <t>chat uíd</t>
+        </is>
+      </c>
+      <c r="C538" s="0" t="inlineStr">
+        <is>
+          <t>Talk with someone in a friendly way — Charlar con.</t>
+        </is>
+      </c>
+      <c r="D538" s="0" t="inlineStr">
+        <is>
+          <t>I chatted with my neighbor.</t>
+        </is>
+      </c>
+      <c r="I538" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: chat with — Present: chats with — Past: chatted with — Past participle: chatted with. Not separable; note the doubled "t" before -ed/-ing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="0" t="inlineStr">
+        <is>
+          <t>Get across</t>
+        </is>
+      </c>
+      <c r="B539" s="0" t="inlineStr">
+        <is>
+          <t>guet acrós</t>
+        </is>
+      </c>
+      <c r="C539" s="0" t="inlineStr">
+        <is>
+          <t>Communicate an idea successfully — Hacer entender.</t>
+        </is>
+      </c>
+      <c r="D539" s="0" t="inlineStr">
+        <is>
+          <t>She got her point across clearly.</t>
+        </is>
+      </c>
+      <c r="I539" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get across — Present: gets across — Past: got across — Past participle: gotten across (US) / got across (UK). Separable: get something across.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="0" t="inlineStr">
+        <is>
+          <t>Check with</t>
+        </is>
+      </c>
+      <c r="B540" s="0" t="inlineStr">
+        <is>
+          <t>chek uíd</t>
+        </is>
+      </c>
+      <c r="C540" s="0" t="inlineStr">
+        <is>
+          <t>Ask someone for confirmation — Consultar con.</t>
+        </is>
+      </c>
+      <c r="D540" s="0" t="inlineStr">
+        <is>
+          <t>Check with your teacher first.</t>
+        </is>
+      </c>
+      <c r="I540" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: check with — Present: checks with — Past: checked with — Past participle: checked with. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="0" t="inlineStr">
+        <is>
+          <t>Get in touch with</t>
+        </is>
+      </c>
+      <c r="B541" s="0" t="inlineStr">
+        <is>
+          <t>guet in tach uíd</t>
+        </is>
+      </c>
+      <c r="C541" s="0" t="inlineStr">
+        <is>
+          <t>Contact someone — Ponerse en contacto con.</t>
+        </is>
+      </c>
+      <c r="D541" s="0" t="inlineStr">
+        <is>
+          <t>I got in touch with an old friend.</t>
+        </is>
+      </c>
+      <c r="I541" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get in touch with — Present: gets in touch with — Past: got in touch with — Past participle: gotten in touch with (US) / got in touch with (UK). Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="0" t="inlineStr">
+        <is>
+          <t>Pass around</t>
+        </is>
+      </c>
+      <c r="B542" s="0" t="inlineStr">
+        <is>
+          <t>pas aráund</t>
+        </is>
+      </c>
+      <c r="C542" s="0" t="inlineStr">
+        <is>
+          <t>Share something with several people — Repartir, hacer circular.</t>
+        </is>
+      </c>
+      <c r="D542" s="0" t="inlineStr">
+        <is>
+          <t>The teacher passed around the worksheets.</t>
+        </is>
+      </c>
+      <c r="I542" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: pass around — Present: passes around — Past: passed around — Past participle: passed around. Separable: pass something around.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="0" t="inlineStr">
+        <is>
+          <t>Log in</t>
+        </is>
+      </c>
+      <c r="B543" s="0" t="inlineStr">
+        <is>
+          <t>log in</t>
+        </is>
+      </c>
+      <c r="C543" s="0" t="inlineStr">
+        <is>
+          <t>Enter an account or system — Iniciar sesión.</t>
+        </is>
+      </c>
+      <c r="D543" s="0" t="inlineStr">
+        <is>
+          <t>Tom logged in to his email account.</t>
+        </is>
+      </c>
+      <c r="I543" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: log in — Present: logs in — Past: logged in — Past participle: logged in. Intransitive; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="0" t="inlineStr">
+        <is>
+          <t>Log out</t>
+        </is>
+      </c>
+      <c r="B544" s="0" t="inlineStr">
+        <is>
+          <t>log áut</t>
+        </is>
+      </c>
+      <c r="C544" s="0" t="inlineStr">
+        <is>
+          <t>Exit an account or system — Cerrar sesión.</t>
+        </is>
+      </c>
+      <c r="D544" s="0" t="inlineStr">
+        <is>
+          <t>Sarah logged out before leaving.</t>
+        </is>
+      </c>
+      <c r="I544" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: log out — Present: logs out — Past: logged out — Past participle: logged out. Intransitive; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="0" t="inlineStr">
+        <is>
+          <t>Sign up</t>
+        </is>
+      </c>
+      <c r="B545" s="0" t="inlineStr">
+        <is>
+          <t>sáin ap</t>
+        </is>
+      </c>
+      <c r="C545" s="0" t="inlineStr">
+        <is>
+          <t>Register for a service — Inscribirse, apuntarse.</t>
+        </is>
+      </c>
+      <c r="D545" s="0" t="inlineStr">
+        <is>
+          <t>Emma signed up for an online course.</t>
+        </is>
+      </c>
+      <c r="I545" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: sign up — Present: signs up — Past: signed up — Past participle: signed up. Separable: sign someone up; often followed by "for".</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="0" t="inlineStr">
+        <is>
+          <t>Sign in</t>
+        </is>
+      </c>
+      <c r="B546" s="0" t="inlineStr">
+        <is>
+          <t>sain in</t>
+        </is>
+      </c>
+      <c r="C546" s="0" t="inlineStr">
+        <is>
+          <t>Enter an account — Iniciar sesión.</t>
+        </is>
+      </c>
+      <c r="D546" s="0" t="inlineStr">
+        <is>
+          <t>Jack signed in to the website.</t>
+        </is>
+      </c>
+      <c r="I546" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: sign in — Present: signs in — Past: signed in — Past participle: signed in. Intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="0" t="inlineStr">
+        <is>
+          <t>Sign out</t>
+        </is>
+      </c>
+      <c r="B547" s="0" t="inlineStr">
+        <is>
+          <t>sain aut</t>
+        </is>
+      </c>
+      <c r="C547" s="0" t="inlineStr">
+        <is>
+          <t>Leave an account — Cerrar sesión.</t>
+        </is>
+      </c>
+      <c r="D547" s="0" t="inlineStr">
+        <is>
+          <t>Lisa signed out of her account.</t>
+        </is>
+      </c>
+      <c r="I547" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: sign out — Present: signs out — Past: signed out — Past participle: signed out. Intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="0" t="inlineStr">
+        <is>
+          <t>Plug in</t>
+        </is>
+      </c>
+      <c r="B548" s="0" t="inlineStr">
+        <is>
+          <t>plag in</t>
+        </is>
+      </c>
+      <c r="C548" s="0" t="inlineStr">
+        <is>
+          <t>Connect a device to power — Enchufar.</t>
+        </is>
+      </c>
+      <c r="D548" s="0" t="inlineStr">
+        <is>
+          <t>Alex plugged in his laptop charger.</t>
+        </is>
+      </c>
+      <c r="I548" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: plug in — Present: plugs in — Past: plugged in — Past participle: plugged in. Separable: plug something in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="0" t="inlineStr">
+        <is>
+          <t>Unplug</t>
+        </is>
+      </c>
+      <c r="B549" s="0" t="inlineStr">
+        <is>
+          <t>anplag</t>
+        </is>
+      </c>
+      <c r="C549" s="0" t="inlineStr">
+        <is>
+          <t>Disconnect a device from power — Desenchufar.</t>
+        </is>
+      </c>
+      <c r="D549" s="0" t="inlineStr">
+        <is>
+          <t>Dad unplugged the printer.</t>
+        </is>
+      </c>
+      <c r="I549" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb, written as one word (not a true phrasal verb). Base: unplug — Present: unplugs — Past: unplugged — Past participle: unplugged. Transitive: unplug something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="0" t="inlineStr">
+        <is>
+          <t>Shut down</t>
+        </is>
+      </c>
+      <c r="B550" s="0" t="inlineStr">
+        <is>
+          <t>shat daun</t>
+        </is>
+      </c>
+      <c r="C550" s="0" t="inlineStr">
+        <is>
+          <t>Turn off completely — Apagar completamente.</t>
+        </is>
+      </c>
+      <c r="D550" s="0" t="inlineStr">
+        <is>
+          <t>Ben shut down his computer.</t>
+        </is>
+      </c>
+      <c r="I550" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: shut down — Present: shuts down — Past: shut down — Past participle: shut down. Separable: shut something down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="0" t="inlineStr">
+        <is>
+          <t>Start up</t>
+        </is>
+      </c>
+      <c r="B551" s="0" t="inlineStr">
+        <is>
+          <t>start ap</t>
+        </is>
+      </c>
+      <c r="C551" s="0" t="inlineStr">
+        <is>
+          <t>Begin operating — Empezar a funcionar.</t>
+        </is>
+      </c>
+      <c r="D551" s="0" t="inlineStr">
+        <is>
+          <t>The computer started up quickly.</t>
+        </is>
+      </c>
+      <c r="I551" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: start up — Present: starts up — Past: started up — Past participle: started up. Intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="0" t="inlineStr">
+        <is>
+          <t>Boot up</t>
+        </is>
+      </c>
+      <c r="B552" s="0" t="inlineStr">
+        <is>
+          <t>but ap</t>
+        </is>
+      </c>
+      <c r="C552" s="0" t="inlineStr">
+        <is>
+          <t>Start a computer system — Arrancar un ordenador.</t>
+        </is>
+      </c>
+      <c r="D552" s="0" t="inlineStr">
+        <is>
+          <t>My laptop booted up in seconds.</t>
+        </is>
+      </c>
+      <c r="I552" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: boot up — Present: boots up — Past: booted up — Past participle: booted up. Separable: boot something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="0" t="inlineStr">
+        <is>
+          <t>Load up</t>
+        </is>
+      </c>
+      <c r="B553" s="0" t="inlineStr">
+        <is>
+          <t>loud ap</t>
+        </is>
+      </c>
+      <c r="C553" s="0" t="inlineStr">
+        <is>
+          <t>Open or load a program — Cargar un programa.</t>
+        </is>
+      </c>
+      <c r="D553" s="0" t="inlineStr">
+        <is>
+          <t>Jack loaded up a game.</t>
+        </is>
+      </c>
+      <c r="I553" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: load up — Present: loads up — Past: loaded up — Past participle: loaded up. Separable: load something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="0" t="inlineStr">
+        <is>
+          <t>Click on</t>
+        </is>
+      </c>
+      <c r="B554" s="0" t="inlineStr">
+        <is>
+          <t>clic on</t>
+        </is>
+      </c>
+      <c r="C554" s="0" t="inlineStr">
+        <is>
+          <t>Press or select on a screen — Hacer clic en.</t>
+        </is>
+      </c>
+      <c r="D554" s="0" t="inlineStr">
+        <is>
+          <t>Emma clicked on the icon.</t>
+        </is>
+      </c>
+      <c r="I554" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: click on — Present: clicks on — Past: clicked on — Past participle: clicked on. Not separable: the object always follows 'on' (click on the icon).</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="0" t="inlineStr">
+        <is>
+          <t>Scroll down</t>
+        </is>
+      </c>
+      <c r="B555" s="0" t="inlineStr">
+        <is>
+          <t>escról daun</t>
+        </is>
+      </c>
+      <c r="C555" s="0" t="inlineStr">
+        <is>
+          <t>Move down a page — Desplazarse hacia abajo.</t>
+        </is>
+      </c>
+      <c r="D555" s="0" t="inlineStr">
+        <is>
+          <t>Alex scrolled down the webpage.</t>
+        </is>
+      </c>
+      <c r="I555" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: scroll down — Present: scrolls down — Past: scrolled down — Past participle: scrolled down. Intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="0" t="inlineStr">
+        <is>
+          <t>Scroll up</t>
+        </is>
+      </c>
+      <c r="B556" s="0" t="inlineStr">
+        <is>
+          <t>escról ap</t>
+        </is>
+      </c>
+      <c r="C556" s="0" t="inlineStr">
+        <is>
+          <t>Move up a page — Desplazarse hacia arriba.</t>
+        </is>
+      </c>
+      <c r="D556" s="0" t="inlineStr">
+        <is>
+          <t>Mia scrolled up to the top.</t>
+        </is>
+      </c>
+      <c r="I556" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: scroll up — Present: scrolls up — Past: scrolled up — Past participle: scrolled up. Intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="0" t="inlineStr">
+        <is>
+          <t>Zoom in</t>
+        </is>
+      </c>
+      <c r="B557" s="0" t="inlineStr">
+        <is>
+          <t>zum in</t>
+        </is>
+      </c>
+      <c r="C557" s="0" t="inlineStr">
+        <is>
+          <t>Make something appear larger — Acercar la imagen.</t>
+        </is>
+      </c>
+      <c r="D557" s="0" t="inlineStr">
+        <is>
+          <t>Tom zoomed in on the photo.</t>
+        </is>
+      </c>
+      <c r="I557" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: zoom in — Present: zooms in — Past: zoomed in — Past participle: zoomed in. Often followed by 'on'; intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="0" t="inlineStr">
+        <is>
+          <t>Zoom out</t>
+        </is>
+      </c>
+      <c r="B558" s="0" t="inlineStr">
+        <is>
+          <t>zum aut</t>
+        </is>
+      </c>
+      <c r="C558" s="0" t="inlineStr">
+        <is>
+          <t>Make something appear smaller — Alejar la imagen.</t>
+        </is>
+      </c>
+      <c r="D558" s="0" t="inlineStr">
+        <is>
+          <t>Emma zoomed out on the map.</t>
+        </is>
+      </c>
+      <c r="I558" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: zoom out — Present: zooms out — Past: zoomed out — Past participle: zoomed out. Often followed by 'on'; intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="0" t="inlineStr">
+        <is>
+          <t>Go online</t>
+        </is>
+      </c>
+      <c r="B559" s="0" t="inlineStr">
+        <is>
+          <t>gou onláin</t>
+        </is>
+      </c>
+      <c r="C559" s="0" t="inlineStr">
+        <is>
+          <t>Connect to the internet — Conectarse a internet.</t>
+        </is>
+      </c>
+      <c r="D559" s="0" t="inlineStr">
+        <is>
+          <t>Ben went online to check emails.</t>
+        </is>
+      </c>
+      <c r="I559" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: go online — Present: goes online — Past: went online — Past participle: gone online. Intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="0" t="inlineStr">
+        <is>
+          <t>Go offline</t>
+        </is>
+      </c>
+      <c r="B560" s="0" t="inlineStr">
+        <is>
+          <t>gou ofláin</t>
+        </is>
+      </c>
+      <c r="C560" s="0" t="inlineStr">
+        <is>
+          <t>Disconnect from the internet — Desconectarse de internet.</t>
+        </is>
+      </c>
+      <c r="D560" s="0" t="inlineStr">
+        <is>
+          <t>The website went offline suddenly.</t>
+        </is>
+      </c>
+      <c r="I560" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: go offline — Present: goes offline — Past: went offline — Past participle: gone offline. Intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="0" t="inlineStr">
+        <is>
+          <t>Opt out</t>
+        </is>
+      </c>
+      <c r="B561" s="0" t="inlineStr">
+        <is>
+          <t>opt aut</t>
+        </is>
+      </c>
+      <c r="C561" s="0" t="inlineStr">
+        <is>
+          <t>Choose not to participate — Optar por no participar.</t>
+        </is>
+      </c>
+      <c r="D561" s="0" t="inlineStr">
+        <is>
+          <t>Tom opted out of marketing emails.</t>
+        </is>
+      </c>
+      <c r="I561" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: opt out — Present: opts out — Past: opted out — Past participle: opted out. Often followed by 'of'; intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="0" t="inlineStr">
+        <is>
+          <t>Log onto</t>
+        </is>
+      </c>
+      <c r="B562" s="0" t="inlineStr">
+        <is>
+          <t>log ónto</t>
+        </is>
+      </c>
+      <c r="C562" s="0" t="inlineStr">
+        <is>
+          <t>Access a computer network — Acceder a una red informática.</t>
+        </is>
+      </c>
+      <c r="D562" s="0" t="inlineStr">
+        <is>
+          <t>Sarah logged onto the company network.</t>
+        </is>
+      </c>
+      <c r="I562" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: log onto — Present: logs onto — Past: logged onto — Past participle: logged onto. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="0" t="inlineStr">
+        <is>
+          <t>Send out</t>
+        </is>
+      </c>
+      <c r="B563" s="0" t="inlineStr">
+        <is>
+          <t>send áut</t>
+        </is>
+      </c>
+      <c r="C563" s="0" t="inlineStr">
+        <is>
+          <t>Distribute electronically to many people — Distribuir electrónicamente a muchas personas.</t>
+        </is>
+      </c>
+      <c r="D563" s="0" t="inlineStr">
+        <is>
+          <t>The company sent out a newsletter.</t>
+        </is>
+      </c>
+      <c r="I563" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb: send — sent — sent. Separable: send something out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="0" t="inlineStr">
+        <is>
+          <t>Type in</t>
+        </is>
+      </c>
+      <c r="B564" s="0" t="inlineStr">
+        <is>
+          <t>táip in</t>
+        </is>
+      </c>
+      <c r="C564" s="0" t="inlineStr">
+        <is>
+          <t>Enter information using a keyboard — Introducir información con el teclado.</t>
+        </is>
+      </c>
+      <c r="D564" s="0" t="inlineStr">
+        <is>
+          <t>Emma typed in her password.</t>
+        </is>
+      </c>
+      <c r="I564" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: type in — Present: types in — Past: typed in — Past participle: typed in. Separable: type something in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="0" t="inlineStr">
+        <is>
+          <t>Print out</t>
+        </is>
+      </c>
+      <c r="B565" s="0" t="inlineStr">
+        <is>
+          <t>print áut</t>
+        </is>
+      </c>
+      <c r="C565" s="0" t="inlineStr">
+        <is>
+          <t>Produce a paper copy — Imprimir una copia en papel.</t>
+        </is>
+      </c>
+      <c r="D565" s="0" t="inlineStr">
+        <is>
+          <t>Sarah printed out her ticket.</t>
+        </is>
+      </c>
+      <c r="I565" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: print out — Present: prints out — Past: printed out — Past participle: printed out. Separable: print something out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="0" t="inlineStr">
+        <is>
+          <t>Browse through</t>
+        </is>
+      </c>
+      <c r="B566" s="0" t="inlineStr">
+        <is>
+          <t>bráuz zru</t>
+        </is>
+      </c>
+      <c r="C566" s="0" t="inlineStr">
+        <is>
+          <t>Look through websites or files — Hojear sitios web o archivos.</t>
+        </is>
+      </c>
+      <c r="D566" s="0" t="inlineStr">
+        <is>
+          <t>Emma browsed through some websites.</t>
+        </is>
+      </c>
+      <c r="I566" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: browse through — Present: browses through — Past: browsed through — Past participle: browsed through. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="0" t="inlineStr">
+        <is>
+          <t>Pop up</t>
+        </is>
+      </c>
+      <c r="B567" s="0" t="inlineStr">
+        <is>
+          <t>pop áp</t>
+        </is>
+      </c>
+      <c r="C567" s="0" t="inlineStr">
+        <is>
+          <t>Appear suddenly on a screen — Aparecer repentinamente en la pantalla.</t>
+        </is>
+      </c>
+      <c r="D567" s="0" t="inlineStr">
+        <is>
+          <t>An ad popped up on the screen.</t>
+        </is>
+      </c>
+      <c r="I567" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb (doubles consonant: popped, popping). Base: pop up — Present: pops up — Past: popped up — Past participle: popped up. Intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="0" t="inlineStr">
+        <is>
+          <t>Freeze up</t>
+        </is>
+      </c>
+      <c r="B568" s="0" t="inlineStr">
+        <is>
+          <t>friz áp</t>
+        </is>
+      </c>
+      <c r="C568" s="0" t="inlineStr">
+        <is>
+          <t>Stop responding temporarily — Dejar de responder temporalmente.</t>
+        </is>
+      </c>
+      <c r="D568" s="0" t="inlineStr">
+        <is>
+          <t>My computer froze up while I was working.</t>
+        </is>
+      </c>
+      <c r="I568" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb: freeze — froze — frozen. Base: freeze up — Present: freezes up — Past: froze up — Past participle: frozen up. Intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="0" t="inlineStr">
+        <is>
+          <t>Log back in</t>
+        </is>
+      </c>
+      <c r="B569" s="0" t="inlineStr">
+        <is>
+          <t>log bak-ín</t>
+        </is>
+      </c>
+      <c r="C569" s="0" t="inlineStr">
+        <is>
+          <t>Sign in again to an account or system — Volver a iniciar sesión en una cuenta o sistema.</t>
+        </is>
+      </c>
+      <c r="D569" s="0" t="inlineStr">
+        <is>
+          <t>Tom logged back in after restarting his computer.</t>
+        </is>
+      </c>
+      <c r="I569" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: log back in — Present: logs back in — Past: logged back in — Past participle: logged back in. Not separable; often used as log back into + noun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="0" t="inlineStr">
+        <is>
+          <t>Swipe through</t>
+        </is>
+      </c>
+      <c r="B570" s="0" t="inlineStr">
+        <is>
+          <t>suaip zru</t>
+        </is>
+      </c>
+      <c r="C570" s="0" t="inlineStr">
+        <is>
+          <t>Move through content by swiping — Deslizar para pasar contenido.</t>
+        </is>
+      </c>
+      <c r="D570" s="0" t="inlineStr">
+        <is>
+          <t>Emma swiped through the photos on her phone.</t>
+        </is>
+      </c>
+      <c r="I570" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: swipe through — Present: swipes through — Past: swiped through — Past participle: swiped through. Inseparable: swipe through something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="0" t="inlineStr">
+        <is>
+          <t>Link up</t>
+        </is>
+      </c>
+      <c r="B571" s="0" t="inlineStr">
+        <is>
+          <t>link ap</t>
+        </is>
+      </c>
+      <c r="C571" s="0" t="inlineStr">
+        <is>
+          <t>Connect devices or systems — Conectar dispositivos o sistemas.</t>
+        </is>
+      </c>
+      <c r="D571" s="0" t="inlineStr">
+        <is>
+          <t>Alex linked up his phone to TV.</t>
+        </is>
+      </c>
+      <c r="I571" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: link up — Present: links up — Past: linked up — Past participle: linked up. Separable: link something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="0" t="inlineStr">
+        <is>
+          <t>Opt in</t>
+        </is>
+      </c>
+      <c r="B572" s="0" t="inlineStr">
+        <is>
+          <t>apt in</t>
+        </is>
+      </c>
+      <c r="C572" s="0" t="inlineStr">
+        <is>
+          <t>Choose to participate in something — Decidir participar en algo.</t>
+        </is>
+      </c>
+      <c r="D572" s="0" t="inlineStr">
+        <is>
+          <t>Sarah opted in to receive email notifications.</t>
+        </is>
+      </c>
+      <c r="I572" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: opt in — Present: opts in — Past: opted in — Past participle: opted in. Inseparable: opt in to something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="0" t="inlineStr">
+        <is>
+          <t>Pay back</t>
+        </is>
+      </c>
+      <c r="B573" s="0" t="inlineStr">
+        <is>
+          <t>pei bak</t>
+        </is>
+      </c>
+      <c r="C573" s="0" t="inlineStr">
+        <is>
+          <t>Return borrowed money — Devolver dinero prestado.</t>
+        </is>
+      </c>
+      <c r="D573" s="0" t="inlineStr">
+        <is>
+          <t>Tom paid back the money he borrowed.</t>
+        </is>
+      </c>
+      <c r="I573" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: pay back — Present: pays back — Past: paid back — Past participle: paid back. Separable: pay something back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="0" t="inlineStr">
+        <is>
+          <t>Pay off</t>
+        </is>
+      </c>
+      <c r="B574" s="0" t="inlineStr">
+        <is>
+          <t>pei of</t>
+        </is>
+      </c>
+      <c r="C574" s="0" t="inlineStr">
+        <is>
+          <t>Finish paying a debt — Terminar de pagar una deuda.</t>
+        </is>
+      </c>
+      <c r="D574" s="0" t="inlineStr">
+        <is>
+          <t>Sarah paid off her loan.</t>
+        </is>
+      </c>
+      <c r="I574" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: pay off — Present: pays off — Past: paid off — Past participle: paid off. Separable: pay something off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="0" t="inlineStr">
+        <is>
+          <t>Spend on</t>
+        </is>
+      </c>
+      <c r="B575" s="0" t="inlineStr">
+        <is>
+          <t>spend on</t>
+        </is>
+      </c>
+      <c r="C575" s="0" t="inlineStr">
+        <is>
+          <t>Use money to buy something — Gastar dinero en algo.</t>
+        </is>
+      </c>
+      <c r="D575" s="0" t="inlineStr">
+        <is>
+          <t>Emma spent money on a new dress.</t>
+        </is>
+      </c>
+      <c r="I575" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: spend on — Present: spends on — Past: spent on — Past participle: spent on. Inseparable: spend money on something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="0" t="inlineStr">
+        <is>
+          <t>Cut back on</t>
+        </is>
+      </c>
+      <c r="B576" s="0" t="inlineStr">
+        <is>
+          <t>cat bak on</t>
+        </is>
+      </c>
+      <c r="C576" s="0" t="inlineStr">
+        <is>
+          <t>Reduce spending on something — Reducir el gasto en algo.</t>
+        </is>
+      </c>
+      <c r="D576" s="0" t="inlineStr">
+        <is>
+          <t>Sarah cut back on eating out.</t>
+        </is>
+      </c>
+      <c r="I576" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: cut back on — Present: cuts back on — Past: cut back on — Past participle: cut back on. Inseparable: cut back on something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="0" t="inlineStr">
+        <is>
+          <t>Live on</t>
+        </is>
+      </c>
+      <c r="B577" s="0" t="inlineStr">
+        <is>
+          <t>liv on</t>
+        </is>
+      </c>
+      <c r="C577" s="0" t="inlineStr">
+        <is>
+          <t>Survive using only a certain amount of money — Vivir con cierta cantidad de dinero.</t>
+        </is>
+      </c>
+      <c r="D577" s="0" t="inlineStr">
+        <is>
+          <t>Ben lives on a small salary.</t>
+        </is>
+      </c>
+      <c r="I577" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: live on — Present: lives on — Past: lived on — Past participle: lived on. Inseparable: live on something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="0" t="inlineStr">
+        <is>
+          <t>Put aside</t>
+        </is>
+      </c>
+      <c r="B578" s="0" t="inlineStr">
+        <is>
+          <t>put asáid</t>
+        </is>
+      </c>
+      <c r="C578" s="0" t="inlineStr">
+        <is>
+          <t>Save money for future use — Ahorrar.</t>
+        </is>
+      </c>
+      <c r="D578" s="0" t="inlineStr">
+        <is>
+          <t>Emma put aside some money for her vacation.</t>
+        </is>
+      </c>
+      <c r="I578" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: put aside — Present: puts aside — Past: put aside — Past participle: put aside. Separable: put something aside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="0" t="inlineStr">
+        <is>
+          <t>Hand over</t>
+        </is>
+      </c>
+      <c r="B579" s="0" t="inlineStr">
+        <is>
+          <t>jand óuver</t>
+        </is>
+      </c>
+      <c r="C579" s="0" t="inlineStr">
+        <is>
+          <t>Give money or something to someone — Entregar.</t>
+        </is>
+      </c>
+      <c r="D579" s="0" t="inlineStr">
+        <is>
+          <t>Tom handed over the cash to the cashier.</t>
+        </is>
+      </c>
+      <c r="I579" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: hand over — Present: hands over — Past: handed over — Past participle: handed over. Separable: hand something over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="0" t="inlineStr">
+        <is>
+          <t>Give back</t>
+        </is>
+      </c>
+      <c r="B580" s="0" t="inlineStr">
+        <is>
+          <t>guiv bak</t>
+        </is>
+      </c>
+      <c r="C580" s="0" t="inlineStr">
+        <is>
+          <t>Return something to its owner — Devolver.</t>
+        </is>
+      </c>
+      <c r="D580" s="0" t="inlineStr">
+        <is>
+          <t>Emma gave back the sweater.</t>
+        </is>
+      </c>
+      <c r="I580" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: give back — Present: gives back — Past: gave back — Past participle: given back. Separable: give something back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="0" t="inlineStr">
+        <is>
+          <t>Take back</t>
+        </is>
+      </c>
+      <c r="B581" s="0" t="inlineStr">
+        <is>
+          <t>téik bak</t>
+        </is>
+      </c>
+      <c r="C581" s="0" t="inlineStr">
+        <is>
+          <t>Return an item to a store — Devolver.</t>
+        </is>
+      </c>
+      <c r="D581" s="0" t="inlineStr">
+        <is>
+          <t>Emma took back the sweater because it was too small.</t>
+        </is>
+      </c>
+      <c r="I581" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: take back — Present: takes back — Past: took back — Past participle: taken back. Separable: take something back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="0" t="inlineStr">
+        <is>
+          <t>Buy up</t>
+        </is>
+      </c>
+      <c r="B582" s="0" t="inlineStr">
+        <is>
+          <t>bái ap</t>
+        </is>
+      </c>
+      <c r="C582" s="0" t="inlineStr">
+        <is>
+          <t>Buy all or most of something available — Acaparar.</t>
+        </is>
+      </c>
+      <c r="D582" s="0" t="inlineStr">
+        <is>
+          <t>Customers bought up all the discounted laptops.</t>
+        </is>
+      </c>
+      <c r="I582" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: buy up — Present: buys up — Past: bought up — Past participle: bought up. Separable: buy something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="0" t="inlineStr">
+        <is>
+          <t>Shop around</t>
+        </is>
+      </c>
+      <c r="B583" s="0" t="inlineStr">
+        <is>
+          <t>shap aráund</t>
+        </is>
+      </c>
+      <c r="C583" s="0" t="inlineStr">
+        <is>
+          <t>Compare prices or products before buying — Comparar precios.</t>
+        </is>
+      </c>
+      <c r="D583" s="0" t="inlineStr">
+        <is>
+          <t>Emma shopped around before buying a new laptop.</t>
+        </is>
+      </c>
+      <c r="I583" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: shop around — Present: shops around — Past: shopped around — Past participle: shopped around. Inseparable and intransitive, no object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="0" t="inlineStr">
+        <is>
+          <t>Stock up on</t>
+        </is>
+      </c>
+      <c r="B584" s="0" t="inlineStr">
+        <is>
+          <t>stak ap on</t>
+        </is>
+      </c>
+      <c r="C584" s="0" t="inlineStr">
+        <is>
+          <t>Buy a large amount of something for future use — Abastecerse de.</t>
+        </is>
+      </c>
+      <c r="D584" s="0" t="inlineStr">
+        <is>
+          <t>Alex stocked up on groceries at the supermarket.</t>
+        </is>
+      </c>
+      <c r="I584" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: stock up on — Present: stocks up on — Past: stocked up on — Past participle: stocked up on. Inseparable, always followed by 'on' plus a noun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="0" t="inlineStr">
+        <is>
+          <t>Line up</t>
+        </is>
+      </c>
+      <c r="B585" s="0" t="inlineStr">
+        <is>
+          <t>láin ap</t>
+        </is>
+      </c>
+      <c r="C585" s="0" t="inlineStr">
+        <is>
+          <t>Stand in a line — Hacer fila.</t>
+        </is>
+      </c>
+      <c r="D585" s="0" t="inlineStr">
+        <is>
+          <t>Shoppers lined up at the checkout counter.</t>
+        </is>
+      </c>
+      <c r="I585" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: line up — Present: lines up — Past: lined up — Past participle: lined up. Intransitive here, no object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="0" t="inlineStr">
+        <is>
+          <t>Give away</t>
+        </is>
+      </c>
+      <c r="B586" s="0" t="inlineStr">
+        <is>
+          <t>guiv awéi</t>
+        </is>
+      </c>
+      <c r="C586" s="0" t="inlineStr">
+        <is>
+          <t>Give something for free — Regalar.</t>
+        </is>
+      </c>
+      <c r="D586" s="0" t="inlineStr">
+        <is>
+          <t>The store gave away free samples.</t>
+        </is>
+      </c>
+      <c r="I586" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: give away — Present: gives away — Past: gave away — Past participle: given away. Separable: give something away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="0" t="inlineStr">
+        <is>
+          <t>Mark down</t>
+        </is>
+      </c>
+      <c r="B587" s="0" t="inlineStr">
+        <is>
+          <t>mark daun</t>
+        </is>
+      </c>
+      <c r="C587" s="0" t="inlineStr">
+        <is>
+          <t>Reduce the price of something — Rebajar.</t>
+        </is>
+      </c>
+      <c r="D587" s="0" t="inlineStr">
+        <is>
+          <t>The store marked down all winter clothes.</t>
+        </is>
+      </c>
+      <c r="I587" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: mark down — Present: marks down — Past: marked down — Past participle: marked down. Separable: mark something down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="0" t="inlineStr">
+        <is>
+          <t>Trade in</t>
+        </is>
+      </c>
+      <c r="B588" s="0" t="inlineStr">
+        <is>
+          <t>tréid in</t>
+        </is>
+      </c>
+      <c r="C588" s="0" t="inlineStr">
+        <is>
+          <t>Exchange an old item for a new one at a lower price — Entregar a cuenta.</t>
+        </is>
+      </c>
+      <c r="D588" s="0" t="inlineStr">
+        <is>
+          <t>Tom traded in his old phone for a new one.</t>
+        </is>
+      </c>
+      <c r="I588" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: trade in — Present: trades in — Past: traded in — Past participle: traded in. Separable: trade something in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="0" t="inlineStr">
+        <is>
+          <t>Sell off</t>
+        </is>
+      </c>
+      <c r="B589" s="0" t="inlineStr">
+        <is>
+          <t>sel of</t>
+        </is>
+      </c>
+      <c r="C589" s="0" t="inlineStr">
+        <is>
+          <t>Sell something quickly, often at a lower price — Liquidar.</t>
+        </is>
+      </c>
+      <c r="D589" s="0" t="inlineStr">
+        <is>
+          <t>The store sold off its summer clothes at the end of the season.</t>
+        </is>
+      </c>
+      <c r="I589" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: sell off — Present: sells off — Past: sold off — Past participle: sold off. Separable: sell something off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="0" t="inlineStr">
+        <is>
+          <t>Mark up</t>
+        </is>
+      </c>
+      <c r="B590" s="0" t="inlineStr">
+        <is>
+          <t>mark ap</t>
+        </is>
+      </c>
+      <c r="C590" s="0" t="inlineStr">
+        <is>
+          <t>Increase the price of something — Subir el precio.</t>
+        </is>
+      </c>
+      <c r="D590" s="0" t="inlineStr">
+        <is>
+          <t>The store marked up the handbags.</t>
+        </is>
+      </c>
+      <c r="I590" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: mark up — Present: marks up — Past: marked up — Past participle: marked up. Separable: mark something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="0" t="inlineStr">
+        <is>
+          <t>Ring up</t>
+        </is>
+      </c>
+      <c r="B591" s="0" t="inlineStr">
+        <is>
+          <t>ring ap</t>
+        </is>
+      </c>
+      <c r="C591" s="0" t="inlineStr">
+        <is>
+          <t>Total a customer's purchases — Cobrar.</t>
+        </is>
+      </c>
+      <c r="D591" s="0" t="inlineStr">
+        <is>
+          <t>The cashier rang up the items.</t>
+        </is>
+      </c>
+      <c r="I591" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: ring up — Present: rings up — Past: rang up — Past participle: rung up. Separable: ring something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="0" t="inlineStr">
+        <is>
+          <t>Pay in</t>
+        </is>
+      </c>
+      <c r="B592" s="0" t="inlineStr">
+        <is>
+          <t>péi in</t>
+        </is>
+      </c>
+      <c r="C592" s="0" t="inlineStr">
+        <is>
+          <t>Deposit money into an account — Ingresar dinero.</t>
+        </is>
+      </c>
+      <c r="D592" s="0" t="inlineStr">
+        <is>
+          <t>Emma paid in some cash at the bank.</t>
+        </is>
+      </c>
+      <c r="I592" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: pay in — Present: pays in — Past: paid in — Past participle: paid in. Separable: pay something in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="0" t="inlineStr">
+        <is>
+          <t>Snap up</t>
+        </is>
+      </c>
+      <c r="B593" s="0" t="inlineStr">
+        <is>
+          <t>snap ap</t>
+        </is>
+      </c>
+      <c r="C593" s="0" t="inlineStr">
+        <is>
+          <t>Buy something quickly before it's gone — Agarrar rápido.</t>
+        </is>
+      </c>
+      <c r="D593" s="0" t="inlineStr">
+        <is>
+          <t>Emma snapped up the last pair of shoes.</t>
+        </is>
+      </c>
+      <c r="I593" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb (doubles the p). Base: snap up — Present: snaps up — Past: snapped up — Past participle: snapped up. Separable: snap something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="0" t="inlineStr">
+        <is>
+          <t>Splash out</t>
+        </is>
+      </c>
+      <c r="B594" s="0" t="inlineStr">
+        <is>
+          <t>splash áut</t>
+        </is>
+      </c>
+      <c r="C594" s="0" t="inlineStr">
+        <is>
+          <t>Spend a lot of money on something special — Derrochar dinero.</t>
+        </is>
+      </c>
+      <c r="D594" s="0" t="inlineStr">
+        <is>
+          <t>Tom splashed out on a new gaming laptop.</t>
+        </is>
+      </c>
+      <c r="I594" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: splash out — Present: splashes out — Past: splashed out — Past participle: splashed out. Usually followed by "on": splash out on something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="0" t="inlineStr">
+        <is>
+          <t>Come to</t>
+        </is>
+      </c>
+      <c r="B595" s="0" t="inlineStr">
+        <is>
+          <t>cam tu</t>
+        </is>
+      </c>
+      <c r="C595" s="0" t="inlineStr">
+        <is>
+          <t>Reach a total amount — Ascender a (un total).</t>
+        </is>
+      </c>
+      <c r="D595" s="0" t="inlineStr">
+        <is>
+          <t>The bill came to $50.</t>
+        </is>
+      </c>
+      <c r="I595" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: come to — Present: comes to — Past: came to — Past participle: come to. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="0" t="inlineStr">
+        <is>
+          <t>Work out</t>
+        </is>
+      </c>
+      <c r="B596" s="0" t="inlineStr">
+        <is>
+          <t>uórk áut</t>
+        </is>
+      </c>
+      <c r="C596" s="0" t="inlineStr">
+        <is>
+          <t>Do physical exercise to stay fit — Hacer ejercicio.</t>
+        </is>
+      </c>
+      <c r="D596" s="0" t="inlineStr">
+        <is>
+          <t>Tom works out at the gym.</t>
+        </is>
+      </c>
+      <c r="I596" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: work out — Present: works out — Past: worked out — Past participle: worked out. Inseparable in this sense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="0" t="inlineStr">
+        <is>
+          <t>Warm up</t>
+        </is>
+      </c>
+      <c r="B597" s="0" t="inlineStr">
+        <is>
+          <t>uórm ap</t>
+        </is>
+      </c>
+      <c r="C597" s="0" t="inlineStr">
+        <is>
+          <t>Prepare your body before exercise — Calentar antes de hacer ejercicio.</t>
+        </is>
+      </c>
+      <c r="D597" s="0" t="inlineStr">
+        <is>
+          <t>Sarah warmed up before running.</t>
+        </is>
+      </c>
+      <c r="I597" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: warm up — Present: warms up — Past: warmed up — Past participle: warmed up. Separable: warm yourself up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="0" t="inlineStr">
+        <is>
+          <t>Cool down</t>
+        </is>
+      </c>
+      <c r="B598" s="0" t="inlineStr">
+        <is>
+          <t>cul dáun</t>
+        </is>
+      </c>
+      <c r="C598" s="0" t="inlineStr">
+        <is>
+          <t>Relax your body after exercise — Enfriarse después de hacer ejercicio.</t>
+        </is>
+      </c>
+      <c r="D598" s="0" t="inlineStr">
+        <is>
+          <t>Jack cooled down after his workout.</t>
+        </is>
+      </c>
+      <c r="I598" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: cool down — Present: cools down — Past: cooled down — Past participle: cooled down. Usually intransitive, no object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="0" t="inlineStr">
+        <is>
+          <t>Build up</t>
+        </is>
+      </c>
+      <c r="B599" s="0" t="inlineStr">
+        <is>
+          <t>bild ap</t>
+        </is>
+      </c>
+      <c r="C599" s="0" t="inlineStr">
+        <is>
+          <t>Gradually increase strength — Aumentar gradualmente.</t>
+        </is>
+      </c>
+      <c r="D599" s="0" t="inlineStr">
+        <is>
+          <t>Tom built up his strength.</t>
+        </is>
+      </c>
+      <c r="I599" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: build up — Present: builds up — Past: built up — Past participle: built up. Separable: build something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="0" t="inlineStr">
+        <is>
+          <t>Burn off</t>
+        </is>
+      </c>
+      <c r="B600" s="0" t="inlineStr">
+        <is>
+          <t>bern of</t>
+        </is>
+      </c>
+      <c r="C600" s="0" t="inlineStr">
+        <is>
+          <t>Use energy through exercise — Quemar calorías.</t>
+        </is>
+      </c>
+      <c r="D600" s="0" t="inlineStr">
+        <is>
+          <t>Sarah burned off extra calories.</t>
+        </is>
+      </c>
+      <c r="I600" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: burn off — Present: burns off — Past: burned off — Past participle: burned off. Separable: burn something off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="0" t="inlineStr">
+        <is>
+          <t>Slim down</t>
+        </is>
+      </c>
+      <c r="B601" s="0" t="inlineStr">
+        <is>
+          <t>slim dáun</t>
+        </is>
+      </c>
+      <c r="C601" s="0" t="inlineStr">
+        <is>
+          <t>Lose weight and become thinner — Adelgazar.</t>
+        </is>
+      </c>
+      <c r="D601" s="0" t="inlineStr">
+        <is>
+          <t>Jack slimmed down after exercising.</t>
+        </is>
+      </c>
+      <c r="I601" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: slim down — Present: slims down — Past: slimmed down — Past participle: slimmed down. Usually intransitive, no object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="0" t="inlineStr">
+        <is>
+          <t>Tone up</t>
+        </is>
+      </c>
+      <c r="B602" s="0" t="inlineStr">
+        <is>
+          <t>tóun ap</t>
+        </is>
+      </c>
+      <c r="C602" s="0" t="inlineStr">
+        <is>
+          <t>Make your muscles firmer — Tonificar.</t>
+        </is>
+      </c>
+      <c r="D602" s="0" t="inlineStr">
+        <is>
+          <t>Tom toned up his arms.</t>
+        </is>
+      </c>
+      <c r="I602" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: tone up — Present: tones up — Past: toned up — Past participle: toned up. Separable: tone something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="0" t="inlineStr">
+        <is>
+          <t>Bulk up</t>
+        </is>
+      </c>
+      <c r="B603" s="0" t="inlineStr">
+        <is>
+          <t>balk ap</t>
+        </is>
+      </c>
+      <c r="C603" s="0" t="inlineStr">
+        <is>
+          <t>Gain muscle and become bigger — Ganar músculo.</t>
+        </is>
+      </c>
+      <c r="D603" s="0" t="inlineStr">
+        <is>
+          <t>Jack bulked up at the gym.</t>
+        </is>
+      </c>
+      <c r="I603" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: bulk up — Present: bulks up — Past: bulked up — Past participle: bulked up. Usually intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="0" t="inlineStr">
+        <is>
+          <t>Cut down on</t>
+        </is>
+      </c>
+      <c r="B604" s="0" t="inlineStr">
+        <is>
+          <t>cat daun on</t>
+        </is>
+      </c>
+      <c r="C604" s="0" t="inlineStr">
+        <is>
+          <t>Reduce something unhealthy — Reducir.</t>
+        </is>
+      </c>
+      <c r="D604" s="0" t="inlineStr">
+        <is>
+          <t>Sarah cut down on sugar.</t>
+        </is>
+      </c>
+      <c r="I604" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: cut down on — Present: cuts down on — Past: cut down on — Past participle: cut down on. Inseparable; always followed by "on".</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="0" t="inlineStr">
+        <is>
+          <t>Stick to</t>
+        </is>
+      </c>
+      <c r="B605" s="0" t="inlineStr">
+        <is>
+          <t>stic tu</t>
+        </is>
+      </c>
+      <c r="C605" s="0" t="inlineStr">
+        <is>
+          <t>Continue following a plan — Seguir con.</t>
+        </is>
+      </c>
+      <c r="D605" s="0" t="inlineStr">
+        <is>
+          <t>Jack stuck to his diet.</t>
+        </is>
+      </c>
+      <c r="I605" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: stick to — Present: sticks to — Past: stuck to — Past participle: stuck to. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="0" t="inlineStr">
+        <is>
+          <t>Come down with</t>
+        </is>
+      </c>
+      <c r="B606" s="0" t="inlineStr">
+        <is>
+          <t>cam daun wiz</t>
+        </is>
+      </c>
+      <c r="C606" s="0" t="inlineStr">
+        <is>
+          <t>Become sick — Contraer una enfermedad.</t>
+        </is>
+      </c>
+      <c r="D606" s="0" t="inlineStr">
+        <is>
+          <t>Emma came down with a cold.</t>
+        </is>
+      </c>
+      <c r="I606" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: come down with — Present: comes down with — Past: came down with — Past participle: come down with. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="0" t="inlineStr">
+        <is>
+          <t>Get over</t>
+        </is>
+      </c>
+      <c r="B607" s="0" t="inlineStr">
+        <is>
+          <t>guet óuver</t>
+        </is>
+      </c>
+      <c r="C607" s="0" t="inlineStr">
+        <is>
+          <t>Recover from an illness — Recuperarse de.</t>
+        </is>
+      </c>
+      <c r="D607" s="0" t="inlineStr">
+        <is>
+          <t>Tom got over the flu quickly.</t>
+        </is>
+      </c>
+      <c r="I607" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get over — Present: gets over — Past: got over — Past participle: got/gotten over. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="0" t="inlineStr">
+        <is>
+          <t>Fight off</t>
+        </is>
+      </c>
+      <c r="B608" s="0" t="inlineStr">
+        <is>
+          <t>fáit of</t>
+        </is>
+      </c>
+      <c r="C608" s="0" t="inlineStr">
+        <is>
+          <t>Resist or overcome an illness — Combatir.</t>
+        </is>
+      </c>
+      <c r="D608" s="0" t="inlineStr">
+        <is>
+          <t>Sarah fought off the infection.</t>
+        </is>
+      </c>
+      <c r="I608" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: fight off — Present: fights off — Past: fought off — Past participle: fought off. Separable: fight something off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="0" t="inlineStr">
+        <is>
+          <t>Wear out</t>
+        </is>
+      </c>
+      <c r="B609" s="0" t="inlineStr">
+        <is>
+          <t>uér aut</t>
+        </is>
+      </c>
+      <c r="C609" s="0" t="inlineStr">
+        <is>
+          <t>Become very tired — Agotarse.</t>
+        </is>
+      </c>
+      <c r="D609" s="0" t="inlineStr">
+        <is>
+          <t>Sarah wore herself out at the gym.</t>
+        </is>
+      </c>
+      <c r="I609" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: wear out — Present: wears out — Past: wore out — Past participle: worn out. Separable, often reflexive: wear yourself out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="0" t="inlineStr">
+        <is>
+          <t>Recover from</t>
+        </is>
+      </c>
+      <c r="B610" s="0" t="inlineStr">
+        <is>
+          <t>rikáver from</t>
+        </is>
+      </c>
+      <c r="C610" s="0" t="inlineStr">
+        <is>
+          <t>Recover from illness or injury — Recuperarse de.</t>
+        </is>
+      </c>
+      <c r="D610" s="0" t="inlineStr">
+        <is>
+          <t>Emma recovered from her injury.</t>
+        </is>
+      </c>
+      <c r="I610" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: recover from — Present: recovers from — Past: recovered from — Past participle: recovered from. Inseparable (prepositional verb).</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="0" t="inlineStr">
+        <is>
+          <t>Speed up</t>
+        </is>
+      </c>
+      <c r="B611" s="0" t="inlineStr">
+        <is>
+          <t>espíd ap</t>
+        </is>
+      </c>
+      <c r="C611" s="0" t="inlineStr">
+        <is>
+          <t>Move faster — Acelerar.</t>
+        </is>
+      </c>
+      <c r="D611" s="0" t="inlineStr">
+        <is>
+          <t>Sarah sped up during the race.</t>
+        </is>
+      </c>
+      <c r="I611" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: speed up — Present: speeds up — Past: sped up — Past participle: sped up. Usually inseparable when used intransitively.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="0" t="inlineStr">
+        <is>
+          <t>Ease off</t>
+        </is>
+      </c>
+      <c r="B612" s="0" t="inlineStr">
+        <is>
+          <t>ís of</t>
+        </is>
+      </c>
+      <c r="C612" s="0" t="inlineStr">
+        <is>
+          <t>Reduce effort or intensity — Disminuir.</t>
+        </is>
+      </c>
+      <c r="D612" s="0" t="inlineStr">
+        <is>
+          <t>Jack eased off after the pain started.</t>
+        </is>
+      </c>
+      <c r="I612" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: ease off — Present: eases off — Past: eased off — Past participle: eased off. Inseparable (intransitive).</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="0" t="inlineStr">
+        <is>
+          <t>Check up on</t>
+        </is>
+      </c>
+      <c r="B613" s="0" t="inlineStr">
+        <is>
+          <t>chek áp on</t>
+        </is>
+      </c>
+      <c r="C613" s="0" t="inlineStr">
+        <is>
+          <t>Examine someone's health — Revisar a alguien.</t>
+        </is>
+      </c>
+      <c r="D613" s="0" t="inlineStr">
+        <is>
+          <t>The doctor checked up on the patient.</t>
+        </is>
+      </c>
+      <c r="I613" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: check up on — Present: checks up on — Past: checked up on — Past participle: checked up on. Inseparable (three-word phrasal verb).</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="0" t="inlineStr">
+        <is>
+          <t>Keep off</t>
+        </is>
+      </c>
+      <c r="B614" s="0" t="inlineStr">
+        <is>
+          <t>kip óf</t>
+        </is>
+      </c>
+      <c r="C614" s="0" t="inlineStr">
+        <is>
+          <t>Avoid eating or using something — Evitar.</t>
+        </is>
+      </c>
+      <c r="D614" s="0" t="inlineStr">
+        <is>
+          <t>Sarah kept off chocolate for a month.</t>
+        </is>
+      </c>
+      <c r="I614" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: keep off — Present: keeps off — Past: kept off — Past participle: kept off. Separable: keep something off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="0" t="inlineStr">
+        <is>
+          <t>Bounce back</t>
+        </is>
+      </c>
+      <c r="B615" s="0" t="inlineStr">
+        <is>
+          <t>báuns bak</t>
+        </is>
+      </c>
+      <c r="C615" s="0" t="inlineStr">
+        <is>
+          <t>Recover quickly — Recuperarse rápidamente.</t>
+        </is>
+      </c>
+      <c r="D615" s="0" t="inlineStr">
+        <is>
+          <t>Jack bounced back after the injury.</t>
+        </is>
+      </c>
+      <c r="I615" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: bounce back — Present: bounces back — Past: bounced back — Past participle: bounced back. Inseparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="0" t="inlineStr">
+        <is>
+          <t>Sit up</t>
+        </is>
+      </c>
+      <c r="B616" s="0" t="inlineStr">
+        <is>
+          <t>sít ap</t>
+        </is>
+      </c>
+      <c r="C616" s="0" t="inlineStr">
+        <is>
+          <t>Move into a sitting position — Incorporarse.</t>
+        </is>
+      </c>
+      <c r="D616" s="0" t="inlineStr">
+        <is>
+          <t>Tom sat up slowly after resting.</t>
+        </is>
+      </c>
+      <c r="I616" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: sit up — Present: sits up — Past: sat up — Past participle: sat up. Inseparable (intransitive).</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="0" t="inlineStr">
+        <is>
+          <t>Work off</t>
+        </is>
+      </c>
+      <c r="B617" s="0" t="inlineStr">
+        <is>
+          <t>uórk of</t>
+        </is>
+      </c>
+      <c r="C617" s="0" t="inlineStr">
+        <is>
+          <t>Get rid of through exercise — Eliminar haciendo ejercicio.</t>
+        </is>
+      </c>
+      <c r="D617" s="0" t="inlineStr">
+        <is>
+          <t>Sarah worked off stress at the gym.</t>
+        </is>
+      </c>
+      <c r="I617" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: work off — Present: works off — Past: worked off — Past participle: worked off. Separable: work something off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="0" t="inlineStr">
+        <is>
+          <t>Grow up</t>
+        </is>
+      </c>
+      <c r="B618" s="0" t="inlineStr">
+        <is>
+          <t>gróu ap</t>
+        </is>
+      </c>
+      <c r="C618" s="0" t="inlineStr">
+        <is>
+          <t>Become an adult — Crecer, hacerse adulto.</t>
+        </is>
+      </c>
+      <c r="D618" s="0" t="inlineStr">
+        <is>
+          <t>Jack grew up in a small town.</t>
+        </is>
+      </c>
+      <c r="I618" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: grow up — Present: grows up — Past: grew up — Past participle: grown up. Intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="0" t="inlineStr">
+        <is>
+          <t>Take after</t>
+        </is>
+      </c>
+      <c r="B619" s="0" t="inlineStr">
+        <is>
+          <t>téik áfter</t>
+        </is>
+      </c>
+      <c r="C619" s="0" t="inlineStr">
+        <is>
+          <t>Look or act like a family member — Parecerse a un familiar.</t>
+        </is>
+      </c>
+      <c r="D619" s="0" t="inlineStr">
+        <is>
+          <t>Emma takes after her mother.</t>
+        </is>
+      </c>
+      <c r="I619" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: take after — Present: takes after — Past: took after — Past participle: taken after. Not separable; stative, not used in progressive tenses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="0" t="inlineStr">
+        <is>
+          <t>Look up to</t>
+        </is>
+      </c>
+      <c r="B620" s="0" t="inlineStr">
+        <is>
+          <t>luk áp tu</t>
+        </is>
+      </c>
+      <c r="C620" s="0" t="inlineStr">
+        <is>
+          <t>Admire and respect someone — Admirar a alguien.</t>
+        </is>
+      </c>
+      <c r="D620" s="0" t="inlineStr">
+        <is>
+          <t>Tom looks up to his father.</t>
+        </is>
+      </c>
+      <c r="I620" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: look up to — Present: looks up to — Past: looked up to — Past participle: looked up to. Not separable; three-word phrasal verb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="0" t="inlineStr">
+        <is>
+          <t>Get along with</t>
+        </is>
+      </c>
+      <c r="B621" s="0" t="inlineStr">
+        <is>
+          <t>guet aláng wiz</t>
+        </is>
+      </c>
+      <c r="C621" s="0" t="inlineStr">
+        <is>
+          <t>Have a good relationship with someone — Llevarse bien con alguien.</t>
+        </is>
+      </c>
+      <c r="D621" s="0" t="inlineStr">
+        <is>
+          <t>Lisa gets along with her sister.</t>
+        </is>
+      </c>
+      <c r="I621" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get along with — Present: gets along with — Past: got along with — Past participle: gotten along with (US) / got along with (UK). Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="0" t="inlineStr">
+        <is>
+          <t>Stay over</t>
+        </is>
+      </c>
+      <c r="B622" s="0" t="inlineStr">
+        <is>
+          <t>stéi óuver</t>
+        </is>
+      </c>
+      <c r="C622" s="0" t="inlineStr">
+        <is>
+          <t>Spend the night at someone's home — Quedarse a dormir.</t>
+        </is>
+      </c>
+      <c r="D622" s="0" t="inlineStr">
+        <is>
+          <t>Emma stayed over at her aunt's house.</t>
+        </is>
+      </c>
+      <c r="I622" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: stay over — Present: stays over — Past: stayed over — Past participle: stayed over. Intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="0" t="inlineStr">
+        <is>
+          <t>Eat up</t>
+        </is>
+      </c>
+      <c r="B623" s="0" t="inlineStr">
+        <is>
+          <t>it áp</t>
+        </is>
+      </c>
+      <c r="C623" s="0" t="inlineStr">
+        <is>
+          <t>Finish all your food — Comérselo todo.</t>
+        </is>
+      </c>
+      <c r="D623" s="0" t="inlineStr">
+        <is>
+          <t>Tom ate up his dinner.</t>
+        </is>
+      </c>
+      <c r="I623" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: eat up — Present: eats up — Past: ate up — Past participle: eaten up. Separable: eat something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="0" t="inlineStr">
+        <is>
+          <t>Clear away</t>
+        </is>
+      </c>
+      <c r="B624" s="0" t="inlineStr">
+        <is>
+          <t>clír awéi</t>
+        </is>
+      </c>
+      <c r="C624" s="0" t="inlineStr">
+        <is>
+          <t>Remove things after a meal — Recoger la mesa.</t>
+        </is>
+      </c>
+      <c r="D624" s="0" t="inlineStr">
+        <is>
+          <t>Emma cleared away the dishes.</t>
+        </is>
+      </c>
+      <c r="I624" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: clear away — Present: clears away — Past: cleared away — Past participle: cleared away. Separable: clear something away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="0" t="inlineStr">
+        <is>
+          <t>Fix up</t>
+        </is>
+      </c>
+      <c r="B625" s="0" t="inlineStr">
+        <is>
+          <t>fix áp</t>
+        </is>
+      </c>
+      <c r="C625" s="0" t="inlineStr">
+        <is>
+          <t>Repair or improve something — Arreglar algo.</t>
+        </is>
+      </c>
+      <c r="D625" s="0" t="inlineStr">
+        <is>
+          <t>Jack fixed up his old house.</t>
+        </is>
+      </c>
+      <c r="I625" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: fix up — Present: fixes up — Past: fixed up — Past participle: fixed up. Separable: fix something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="0" t="inlineStr">
+        <is>
+          <t>Fall out</t>
+        </is>
+      </c>
+      <c r="B626" s="0" t="inlineStr">
+        <is>
+          <t>fól aut</t>
+        </is>
+      </c>
+      <c r="C626" s="0" t="inlineStr">
+        <is>
+          <t>Have an argument — Discutir.</t>
+        </is>
+      </c>
+      <c r="D626" s="0" t="inlineStr">
+        <is>
+          <t>Jack fell out with his brother.</t>
+        </is>
+      </c>
+      <c r="I626" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: fall out — Past: fell out — Past participle: fallen out. Not separable; used with 'with' (fall out with someone).</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="0" t="inlineStr">
+        <is>
+          <t>Grow apart</t>
+        </is>
+      </c>
+      <c r="B627" s="0" t="inlineStr">
+        <is>
+          <t>gróu apárt</t>
+        </is>
+      </c>
+      <c r="C627" s="0" t="inlineStr">
+        <is>
+          <t>Become less close over time — Distanciarse.</t>
+        </is>
+      </c>
+      <c r="D627" s="0" t="inlineStr">
+        <is>
+          <t>The brothers grew apart after college.</t>
+        </is>
+      </c>
+      <c r="I627" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: grow apart — Past: grew apart — Past participle: grown apart. Intransitive; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="0" t="inlineStr">
+        <is>
+          <t>Get together</t>
+        </is>
+      </c>
+      <c r="B628" s="0" t="inlineStr">
+        <is>
+          <t>guét tuguéder</t>
+        </is>
+      </c>
+      <c r="C628" s="0" t="inlineStr">
+        <is>
+          <t>Meet and spend time together — Reunirse.</t>
+        </is>
+      </c>
+      <c r="D628" s="0" t="inlineStr">
+        <is>
+          <t>The family got together on Sunday.</t>
+        </is>
+      </c>
+      <c r="I628" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get together — Past: got together — Past participle: gotten/got together. Intransitive; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="0" t="inlineStr">
+        <is>
+          <t>Look out for</t>
+        </is>
+      </c>
+      <c r="B629" s="0" t="inlineStr">
+        <is>
+          <t>luk áut for</t>
+        </is>
+      </c>
+      <c r="C629" s="0" t="inlineStr">
+        <is>
+          <t>Protect or care about someone — Cuidar de alguien.</t>
+        </is>
+      </c>
+      <c r="D629" s="0" t="inlineStr">
+        <is>
+          <t>Jack looks out for his little sister.</t>
+        </is>
+      </c>
+      <c r="I629" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: look out for — Past: looked out for — Past participle: looked out for. Intransitive; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="0" t="inlineStr">
+        <is>
+          <t>Leave behind</t>
+        </is>
+      </c>
+      <c r="B630" s="0" t="inlineStr">
+        <is>
+          <t>liv bijáind</t>
+        </is>
+      </c>
+      <c r="C630" s="0" t="inlineStr">
+        <is>
+          <t>Leave something and not take it with you — Olvidar algo (dejarlo atrás).</t>
+        </is>
+      </c>
+      <c r="D630" s="0" t="inlineStr">
+        <is>
+          <t>Tom left his bag behind.</t>
+        </is>
+      </c>
+      <c r="I630" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: leave behind — Past: left behind — Past participle: left behind. Separable: leave something behind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="0" t="inlineStr">
+        <is>
+          <t>Settle down</t>
+        </is>
+      </c>
+      <c r="B631" s="0" t="inlineStr">
+        <is>
+          <t>sétel daun</t>
+        </is>
+      </c>
+      <c r="C631" s="0" t="inlineStr">
+        <is>
+          <t>Start a stable family life — Sentar cabeza.</t>
+        </is>
+      </c>
+      <c r="D631" s="0" t="inlineStr">
+        <is>
+          <t>Jack settled down and started a family.</t>
+        </is>
+      </c>
+      <c r="I631" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: settle down — Past: settled down — Past participle: settled down. Intransitive; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="0" t="inlineStr">
+        <is>
+          <t>Grow closer</t>
+        </is>
+      </c>
+      <c r="B632" s="0" t="inlineStr">
+        <is>
+          <t>gróu clóuser</t>
+        </is>
+      </c>
+      <c r="C632" s="0" t="inlineStr">
+        <is>
+          <t>Become more connected — Acercarse (emocionalmente).</t>
+        </is>
+      </c>
+      <c r="D632" s="0" t="inlineStr">
+        <is>
+          <t>The sisters grew closer over time.</t>
+        </is>
+      </c>
+      <c r="I632" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: grow closer — Past: grew closer — Past participle: grown closer. Intransitive; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="0" t="inlineStr">
+        <is>
+          <t>Gather around</t>
+        </is>
+      </c>
+      <c r="B633" s="0" t="inlineStr">
+        <is>
+          <t>gáder araund</t>
+        </is>
+      </c>
+      <c r="C633" s="0" t="inlineStr">
+        <is>
+          <t>Come together in a group — Reunirse en grupo.</t>
+        </is>
+      </c>
+      <c r="D633" s="0" t="inlineStr">
+        <is>
+          <t>The family gathered around the table.</t>
+        </is>
+      </c>
+      <c r="I633" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: gather around — Past: gathered around — Past participle: gathered around. Intransitive; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="0" t="inlineStr">
+        <is>
+          <t>Take in</t>
+        </is>
+      </c>
+      <c r="B634" s="0" t="inlineStr">
+        <is>
+          <t>téik in</t>
+        </is>
+      </c>
+      <c r="C634" s="0" t="inlineStr">
+        <is>
+          <t>Provide a home for someone or an animal — Acoger.</t>
+        </is>
+      </c>
+      <c r="D634" s="0" t="inlineStr">
+        <is>
+          <t>The family took in a stray dog.</t>
+        </is>
+      </c>
+      <c r="I634" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: take in — Present: takes in — Past: took in — Past participle: taken in. Separable: take someone in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="0" t="inlineStr">
+        <is>
+          <t>Grow out of</t>
+        </is>
+      </c>
+      <c r="B635" s="0" t="inlineStr">
+        <is>
+          <t>gróu áut ov</t>
+        </is>
+      </c>
+      <c r="C635" s="0" t="inlineStr">
+        <is>
+          <t>Become too old for something — Dejar atrás (por haber crecido).</t>
+        </is>
+      </c>
+      <c r="D635" s="0" t="inlineStr">
+        <is>
+          <t>Jack grew out of his old toys.</t>
+        </is>
+      </c>
+      <c r="I635" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: grow out of — Present: grows out of — Past: grew out of — Past participle: grown out of. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="0" t="inlineStr">
+        <is>
+          <t>Move away</t>
+        </is>
+      </c>
+      <c r="B636" s="0" t="inlineStr">
+        <is>
+          <t>múv awéi</t>
+        </is>
+      </c>
+      <c r="C636" s="0" t="inlineStr">
+        <is>
+          <t>Leave home and live elsewhere — Mudarse.</t>
+        </is>
+      </c>
+      <c r="D636" s="0" t="inlineStr">
+        <is>
+          <t>Sarah moved away after college.</t>
+        </is>
+      </c>
+      <c r="I636" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: move away — Present: moves away — Past: moved away — Past participle: moved away. Intransitive, not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="0" t="inlineStr">
+        <is>
+          <t>Drop in on</t>
+        </is>
+      </c>
+      <c r="B637" s="0" t="inlineStr">
+        <is>
+          <t>dráp in on</t>
+        </is>
+      </c>
+      <c r="C637" s="0" t="inlineStr">
+        <is>
+          <t>Visit someone unexpectedly — Visitar de improviso.</t>
+        </is>
+      </c>
+      <c r="D637" s="0" t="inlineStr">
+        <is>
+          <t>Tom dropped in on his aunt.</t>
+        </is>
+      </c>
+      <c r="I637" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: drop in on — Present: drops in on — Past: dropped in on — Past participle: dropped in on. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="0" t="inlineStr">
+        <is>
+          <t>Come by</t>
+        </is>
+      </c>
+      <c r="B638" s="0" t="inlineStr">
+        <is>
+          <t>kam bái</t>
+        </is>
+      </c>
+      <c r="C638" s="0" t="inlineStr">
+        <is>
+          <t>Visit someone — Pasar a visitar.</t>
+        </is>
+      </c>
+      <c r="D638" s="0" t="inlineStr">
+        <is>
+          <t>My grandparents came by for lunch.</t>
+        </is>
+      </c>
+      <c r="I638" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: come by — Present: comes by — Past: came by — Past participle: come by. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="0" t="inlineStr">
+        <is>
+          <t>Look in on</t>
+        </is>
+      </c>
+      <c r="B639" s="0" t="inlineStr">
+        <is>
+          <t>lúk in on</t>
+        </is>
+      </c>
+      <c r="C639" s="0" t="inlineStr">
+        <is>
+          <t>Visit briefly to check on someone — Pasar a ver cómo está alguien.</t>
+        </is>
+      </c>
+      <c r="D639" s="0" t="inlineStr">
+        <is>
+          <t>Emma looked in on her grandmother.</t>
+        </is>
+      </c>
+      <c r="I639" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: look in on — Present: looks in on — Past: looked in on — Past participle: looked in on. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="0" t="inlineStr">
+        <is>
+          <t>Join in</t>
+        </is>
+      </c>
+      <c r="B640" s="0" t="inlineStr">
+        <is>
+          <t>yóin in</t>
+        </is>
+      </c>
+      <c r="C640" s="0" t="inlineStr">
+        <is>
+          <t>Take part in a family activity — Participar.</t>
+        </is>
+      </c>
+      <c r="D640" s="0" t="inlineStr">
+        <is>
+          <t>Jack joined in the family game.</t>
+        </is>
+      </c>
+      <c r="I640" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: join in — Present: joins in — Past: joined in — Past participle: joined in. Usually not separable: join in the game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="0" t="inlineStr">
+        <is>
+          <t>Take over</t>
+        </is>
+      </c>
+      <c r="B641" s="0" t="inlineStr">
+        <is>
+          <t>téik óuver</t>
+        </is>
+      </c>
+      <c r="C641" s="0" t="inlineStr">
+        <is>
+          <t>Take responsibility for something — Hacerse cargo.</t>
+        </is>
+      </c>
+      <c r="D641" s="0" t="inlineStr">
+        <is>
+          <t>Tom took over the household duties.</t>
+        </is>
+      </c>
+      <c r="I641" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: take over — Present: takes over — Past: took over — Past participle: taken over. Separable: take something over.</t>
         </is>
       </c>
     </row>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I641"/>
+  <dimension ref="A1:I696"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -22865,6 +22865,1491 @@
       <c r="I641" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: take over — Present: takes over — Past: took over — Past participle: taken over. Separable: take something over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Pitch in</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>pich ín</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Help with a shared task — Echar una mano.</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Everyone pitched in to clean the house.</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: pitch in — Present: pitches in — Past: pitched in — Past participle: pitched in. Intransitive; not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Cheer up</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>chír ap</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Become happier — Animarse.</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Emma cheered up after hearing the good news.</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: cheer up — Present: cheers up — Past: cheered up — Past participle: cheered up. Separable: cheer someone up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Calm down</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>cálm daun</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Become less upset or angry — Calmarse.</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Tom calmed down after a few minutes.</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: calm down — Present: calms down — Past: calmed down — Past participle: calmed down. Separable: calm someone down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Brighten up</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>bráiten ap</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Become happier or more cheerful — Alegrarse.</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Sarah brightened up when she saw her friends.</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: brighten up — Present: brightens up — Past: brightened up — Past participle: brightened up. Also used of weather and of rooms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Open up</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>óupen ap</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Share your feelings with someone — Abrirse.</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Jack opened up to his best friend.</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: open up — Present: opens up — Past: opened up — Past participle: opened up. Intransitive in this sense: open up to someone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Bottle up</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>bótel ap</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Keep your feelings inside — Reprimir los sentimientos.</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Emma bottled up her emotions.</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: bottle up — Present: bottles up — Past: bottled up — Past participle: bottled up. Separable: bottle something up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Break down</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>bréik daun</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Lose control of your emotions — Derrumbarse.</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Sarah broke down in tears.</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: break down — Present: breaks down — Past: broke down — Past participle: broken down. Intransitive in this sense; of a machine it means to stop working.</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Hold back</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>jóuld bak</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Stop yourself from showing emotion — Contener.</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Jack held back his tears.</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: hold back — Present: holds back — Past: held back — Past participle: held back. Separable: hold something back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Bring down</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>bring dáun</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Make someone feel sad — Desanimar.</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>The bad news brought him down.</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: bring down — Present: brings down — Past: brought down — Past participle: brought down. Separable: bring someone down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Fall apart</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>fol apárt</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Become emotionally upset — Desmoronarse.</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Jack fell apart after the loss.</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: fall apart — Present: falls apart — Past: fell apart — Past participle: fallen apart. Intransitive; also used of things that break into pieces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Feel up to</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>fíl ap tu</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Feel able to do something — Sentirse capaz de.</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Tom didn't feel up to going out.</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: feel up to — Present: feels up to — Past: felt up to — Past participle: felt up to. Not separable. Followed by a noun or by -ing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Wear down</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>uér daun</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Make someone tired or stressed — Desgastar.</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>The long week wore him down.</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: wear down — Present: wears down — Past: wore down — Past participle: worn down. Separable: wear someone down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Ease up</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>ís ap</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Become less worried or tense — Relajarse.</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Sarah eased up after the test.</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: ease up — Present: eases up — Past: eased up — Past participle: eased up. Intransitive. Also said of rain or pressure letting up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Snap out of</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>snáp aut of</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Stop feeling sad or worried — Salir de un estado de ánimo.</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Emma snapped out of her bad mood.</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: snap out of — Present: snaps out of — Past: snapped out of — Past participle: snapped out of. Not separable. Often an imperative: snap out of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Lighten up</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>láiten ap</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Become less serious or worried — Tomárselo con calma.</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Jack lightened up after hearing the joke.</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: lighten up — Present: lightens up — Past: lightened up — Past participle: lightened up. Intransitive, and usually said as an instruction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Warm up to</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>uórm ap tu</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Gradually start liking someone — Agarrar confianza con.</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Sarah warmed up to her new neighbor.</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: warm up to — Present: warms up to — Past: warmed up to — Past participle: warmed up to. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Lean on</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>lín on</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Depend on someone for support — Apoyarse en.</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Emma leaned on her sister.</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: lean on — Present: leans on — Past: leaned on — Past participle: leaned on. Not separable. British English also uses leant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Well up</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>uél ap</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Fill with tears or strong emotion — Llenarse de lágrimas.</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Tears welled up in her eyes.</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: well up — Present: wells up — Past: welled up — Past participle: welled up. Intransitive. The subject is usually tears or a feeling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Come around</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>kam aráund</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Change your opinion or attitude — Cambiar de opinión.</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Tom came around after talking to her.</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: come around — Present: comes around — Past: came around — Past participle: come around. Intransitive. Also means to regain consciousness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Dwell on</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>duél on</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Keep thinking about something upsetting — Darle vueltas a.</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Emma dwelled on her mistake.</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: dwell on — Present: dwells on — Past: dwelled on — Past participle: dwelled on. Not separable. British English also uses dwelt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Shake off</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>shéik of</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Stop feeling something unpleasant — Quitarse de encima.</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Tom shook off his worries.</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: shake off — Present: shakes off — Past: shook off — Past participle: shaken off. Separable: shake something off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Hang on to</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>jáng on tu</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Keep a feeling or a memory — Aferrarse a.</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Emma hung on to her childhood memories.</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: hang on to — Present: hangs on to — Past: hung on to — Past participle: hung on to. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Sink in</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>sínk in</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Be fully understood — Asimilarse.</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>The news finally sank in.</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: sink in — Present: sinks in — Past: sank in — Past participle: sunk in. Intransitive. The subject is the news or the fact, not the person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Live through</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>lív zru</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Experience something difficult — Vivir algo difícil.</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Tom lived through a stressful year.</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: live through — Present: lives through — Past: lived through — Past participle: lived through. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Look down on</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>lúk daun on</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Think you are better than someone — Menospreciar.</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Jack looked down on his classmates.</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: look down on — Present: looks down on — Past: looked down on — Past participle: looked down on. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Beat yourself up</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>bít yorsélf ap</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Criticise yourself too much — Culparse demasiado.</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Emma beat herself up over the mistake.</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: beat yourself up — Present: beats himself up — Past: beat herself up — Past participle: beaten yourself up. The middle word changes with the person: beat myself up, beat himself up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Miss out on</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>mís aut on</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Lose the chance to experience something — Perderse algo.</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Tom missed out on the trip.</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: miss out on — Present: misses out on — Past: missed out on — Past participle: missed out on. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Break into</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>bréik íntu</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Suddenly show an emotion — Echarse a.</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Emma broke into laughter.</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: break into — Present: breaks into — Past: broke into — Past participle: broken into. Not separable. Also means to enter a building by force.</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Get carried away</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>guét kárid auéi</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Become too excited or emotional — Dejarse llevar.</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Tom got carried away during the celebration.</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get carried away — Present: gets carried away — Past: got carried away — Past participle: gotten carried away. A fixed expression; the three words stay together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Bottle out</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>bótel áut</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Lose courage and back out — Echarse atrás.</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Jack bottled out of giving the speech.</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: bottle out — Present: bottles out — Past: bottled out — Past participle: bottled out. Intransitive. British and informal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Fight back</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>fáit bak</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Stop yourself from showing emotion — Contener.</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Sarah fought back her tears.</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: fight back — Present: fights back — Past: fought back — Past participle: fought back. Separable in this sense. On its own it means to defend yourself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Clam up</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>klám ap</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Suddenly stop talking — Quedarse callado.</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Tom clammed up during the interview.</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: clam up — Present: clams up — Past: clammed up — Past participle: clammed up. Intransitive and informal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Bring about</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>bring abáut</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Cause something to happen — Provocar.</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>The new rule brought about positive changes.</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: bring about — Present: brings about — Past: brought about — Past participle: brought about. Separable, though the object usually follows the whole verb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Carry out</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>kári áut</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Complete a task or a plan — Llevar a cabo.</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>The students carried out the project successfully.</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: carry out — Present: carries out — Past: carried out — Past participle: carried out. Separable: carry it out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Come up with</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>kam ap uith</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Think of an idea or a solution — Ocurrírsele a uno.</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Sarah came up with a clever idea.</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: come up with — Present: comes up with — Past: came up with — Past participle: come up with. Not separable; all three words stay together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Turn out</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>tern áut</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Happen or develop in a particular way — Resultar.</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>The party turned out great.</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: turn out — Present: turns out — Past: turned out — Past participle: turned out. Intransitive in this sense. Often: it turned out that...</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Get away with</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>guét auéi uith</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Avoid punishment for something — Salirse con la suya.</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Jack got away with breaking the rules.</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get away with — Present: gets away with — Past: got away with — Past participle: gotten away with. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Put up with</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>pút ap uith</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Tolerate something unpleasant — Aguantar.</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Sarah put up with the loud noise.</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: put up with — Present: puts up with — Past: put up with — Past participle: put up with. Not separable. The past looks the same as the base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Back out</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>bák áut</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Withdraw from an agreement or a plan — Echarse atrás.</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Jack backed out of the deal.</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: back out — Present: backs out — Past: backed out — Past participle: backed out. Intransitive: back out of something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Come up against</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>kam ap aguénst</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Face a difficulty — Toparse con.</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>The team came up against many problems.</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: come up against — Present: comes up against — Past: came up against — Past participle: come up against. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Drop out</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>dráp áut</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Leave a course before finishing — Abandonar los estudios.</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Jack dropped out of college.</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: drop out — Present: drops out — Past: dropped out — Past participle: dropped out. Intransitive: drop out of something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Get over with</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>guét óuver uith</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Finish something unpleasant — Terminar de una vez.</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Emma got the exam over with quickly.</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: get over with — Present: gets over with — Past: got over with — Past participle: gotten over with. The object goes in the middle: get it over with.</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Pull off</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>púl of</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Succeed in doing something difficult — Lograr.</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Sarah pulled off a great performance.</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: pull off — Present: pulls off — Past: pulled off — Past participle: pulled off. Separable: pull it off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Turn down</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>tern dáun</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Refuse an offer or a request — Rechazar.</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Emma turned down the job offer.</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: turn down — Present: turns down — Past: turned down — Past participle: turned down. Separable: turn it down. Also means to lower the volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Turn up</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>tern ap</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Appear or be found unexpectedly — Aparecer.</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>My keys turned up yesterday.</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: turn up — Present: turns up — Past: turned up — Past participle: turned up. Intransitive in this sense. Also means to raise the volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Work through</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>uérk zru</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Deal with a problem step by step — Resolver poco a poco.</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Sarah worked through her difficulties.</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: work through — Present: works through — Past: worked through — Past participle: worked through. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Write off</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>ráit of</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Consider something a loss — Dar por perdido.</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>The company wrote off the damaged equipment.</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: write off — Present: writes off — Past: wrote off — Past participle: written off. Separable: write it off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Pass up</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>pás ap</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Miss an opportunity by not taking it — Dejar pasar.</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Tom passed up a great offer.</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: pass up — Present: passes up — Past: passed up — Past participle: passed up. Separable: pass it up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Follow through</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>fólou zru</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Complete what you started — Cumplir hasta el final.</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Emma followed through on her promise.</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: follow through — Present: follows through — Past: followed through — Past participle: followed through. Not separable; usually follow through on something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Let down</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>lét daun</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Disappoint someone — Defraudar.</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Sarah let her team down.</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: let down — Present: lets down — Past: let down — Past participle: let down. Separable: let someone down. All the forms look the same.</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Call for</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>kol for</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Require something — Requerir.</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>The situation called for quick action.</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: call for — Present: calls for — Past: called for — Past participle: called for. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Rule out</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>rúl áut</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Eliminate a possibility — Descartar.</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>The doctor ruled out an infection.</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: rule out — Present: rules out — Past: ruled out — Past participle: ruled out. Separable: rule it out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Put down to</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>pút daun tu</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Explain something as caused by — Atribuir a.</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Tom put his success down to practice.</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: put down to — Present: puts down to — Past: put down to — Past participle: put down to. The object goes in the middle: put it down to luck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>See through</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>sí zru</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Recognise the truth about something — Calar.</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Emma saw through the excuse.</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: see through — Present: sees through — Past: saw through — Past participle: seen through. Not separable in this sense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Stand up for</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>stand ap for</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Defend someone or something — Defender.</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Jack stood up for his friend.</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: stand up for — Present: stands up for — Past: stood up for — Past participle: stood up for. Not separable.</t>
         </is>
       </c>
     </row>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -22869,1485 +22869,1485 @@
       </c>
     </row>
     <row r="642">
-      <c r="A642" t="inlineStr">
+      <c r="A642" s="0" t="inlineStr">
         <is>
           <t>Pitch in</t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
+      <c r="B642" s="0" t="inlineStr">
         <is>
           <t>pich ín</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr">
+      <c r="C642" s="0" t="inlineStr">
         <is>
           <t>Help with a shared task — Echar una mano.</t>
         </is>
       </c>
-      <c r="D642" t="inlineStr">
+      <c r="D642" s="0" t="inlineStr">
         <is>
           <t>Everyone pitched in to clean the house.</t>
         </is>
       </c>
-      <c r="I642" t="inlineStr">
+      <c r="I642" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: pitch in — Present: pitches in — Past: pitched in — Past participle: pitched in. Intransitive; not separable.</t>
         </is>
       </c>
     </row>
     <row r="643">
-      <c r="A643" t="inlineStr">
+      <c r="A643" s="0" t="inlineStr">
         <is>
           <t>Cheer up</t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
+      <c r="B643" s="0" t="inlineStr">
         <is>
           <t>chír ap</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
+      <c r="C643" s="0" t="inlineStr">
         <is>
           <t>Become happier — Animarse.</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr">
+      <c r="D643" s="0" t="inlineStr">
         <is>
           <t>Emma cheered up after hearing the good news.</t>
         </is>
       </c>
-      <c r="I643" t="inlineStr">
+      <c r="I643" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: cheer up — Present: cheers up — Past: cheered up — Past participle: cheered up. Separable: cheer someone up.</t>
         </is>
       </c>
     </row>
     <row r="644">
-      <c r="A644" t="inlineStr">
+      <c r="A644" s="0" t="inlineStr">
         <is>
           <t>Calm down</t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B644" s="0" t="inlineStr">
         <is>
           <t>cálm daun</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
+      <c r="C644" s="0" t="inlineStr">
         <is>
           <t>Become less upset or angry — Calmarse.</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr">
+      <c r="D644" s="0" t="inlineStr">
         <is>
           <t>Tom calmed down after a few minutes.</t>
         </is>
       </c>
-      <c r="I644" t="inlineStr">
+      <c r="I644" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: calm down — Present: calms down — Past: calmed down — Past participle: calmed down. Separable: calm someone down.</t>
         </is>
       </c>
     </row>
     <row r="645">
-      <c r="A645" t="inlineStr">
+      <c r="A645" s="0" t="inlineStr">
         <is>
           <t>Brighten up</t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
+      <c r="B645" s="0" t="inlineStr">
         <is>
           <t>bráiten ap</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr">
+      <c r="C645" s="0" t="inlineStr">
         <is>
           <t>Become happier or more cheerful — Alegrarse.</t>
         </is>
       </c>
-      <c r="D645" t="inlineStr">
+      <c r="D645" s="0" t="inlineStr">
         <is>
           <t>Sarah brightened up when she saw her friends.</t>
         </is>
       </c>
-      <c r="I645" t="inlineStr">
+      <c r="I645" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: brighten up — Present: brightens up — Past: brightened up — Past participle: brightened up. Also used of weather and of rooms.</t>
         </is>
       </c>
     </row>
     <row r="646">
-      <c r="A646" t="inlineStr">
+      <c r="A646" s="0" t="inlineStr">
         <is>
           <t>Open up</t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
+      <c r="B646" s="0" t="inlineStr">
         <is>
           <t>óupen ap</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr">
+      <c r="C646" s="0" t="inlineStr">
         <is>
           <t>Share your feelings with someone — Abrirse.</t>
         </is>
       </c>
-      <c r="D646" t="inlineStr">
+      <c r="D646" s="0" t="inlineStr">
         <is>
           <t>Jack opened up to his best friend.</t>
         </is>
       </c>
-      <c r="I646" t="inlineStr">
+      <c r="I646" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: open up — Present: opens up — Past: opened up — Past participle: opened up. Intransitive in this sense: open up to someone.</t>
         </is>
       </c>
     </row>
     <row r="647">
-      <c r="A647" t="inlineStr">
+      <c r="A647" s="0" t="inlineStr">
         <is>
           <t>Bottle up</t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
+      <c r="B647" s="0" t="inlineStr">
         <is>
           <t>bótel ap</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
+      <c r="C647" s="0" t="inlineStr">
         <is>
           <t>Keep your feelings inside — Reprimir los sentimientos.</t>
         </is>
       </c>
-      <c r="D647" t="inlineStr">
+      <c r="D647" s="0" t="inlineStr">
         <is>
           <t>Emma bottled up her emotions.</t>
         </is>
       </c>
-      <c r="I647" t="inlineStr">
+      <c r="I647" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: bottle up — Present: bottles up — Past: bottled up — Past participle: bottled up. Separable: bottle something up.</t>
         </is>
       </c>
     </row>
     <row r="648">
-      <c r="A648" t="inlineStr">
+      <c r="A648" s="0" t="inlineStr">
         <is>
           <t>Break down</t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
+      <c r="B648" s="0" t="inlineStr">
         <is>
           <t>bréik daun</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
+      <c r="C648" s="0" t="inlineStr">
         <is>
           <t>Lose control of your emotions — Derrumbarse.</t>
         </is>
       </c>
-      <c r="D648" t="inlineStr">
+      <c r="D648" s="0" t="inlineStr">
         <is>
           <t>Sarah broke down in tears.</t>
         </is>
       </c>
-      <c r="I648" t="inlineStr">
+      <c r="I648" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: break down — Present: breaks down — Past: broke down — Past participle: broken down. Intransitive in this sense; of a machine it means to stop working.</t>
         </is>
       </c>
     </row>
     <row r="649">
-      <c r="A649" t="inlineStr">
+      <c r="A649" s="0" t="inlineStr">
         <is>
           <t>Hold back</t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
+      <c r="B649" s="0" t="inlineStr">
         <is>
           <t>jóuld bak</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
+      <c r="C649" s="0" t="inlineStr">
         <is>
           <t>Stop yourself from showing emotion — Contener.</t>
         </is>
       </c>
-      <c r="D649" t="inlineStr">
+      <c r="D649" s="0" t="inlineStr">
         <is>
           <t>Jack held back his tears.</t>
         </is>
       </c>
-      <c r="I649" t="inlineStr">
+      <c r="I649" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: hold back — Present: holds back — Past: held back — Past participle: held back. Separable: hold something back.</t>
         </is>
       </c>
     </row>
     <row r="650">
-      <c r="A650" t="inlineStr">
+      <c r="A650" s="0" t="inlineStr">
         <is>
           <t>Bring down</t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
+      <c r="B650" s="0" t="inlineStr">
         <is>
           <t>bring dáun</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
+      <c r="C650" s="0" t="inlineStr">
         <is>
           <t>Make someone feel sad — Desanimar.</t>
         </is>
       </c>
-      <c r="D650" t="inlineStr">
+      <c r="D650" s="0" t="inlineStr">
         <is>
           <t>The bad news brought him down.</t>
         </is>
       </c>
-      <c r="I650" t="inlineStr">
+      <c r="I650" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: bring down — Present: brings down — Past: brought down — Past participle: brought down. Separable: bring someone down.</t>
         </is>
       </c>
     </row>
     <row r="651">
-      <c r="A651" t="inlineStr">
+      <c r="A651" s="0" t="inlineStr">
         <is>
           <t>Fall apart</t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
+      <c r="B651" s="0" t="inlineStr">
         <is>
           <t>fol apárt</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr">
+      <c r="C651" s="0" t="inlineStr">
         <is>
           <t>Become emotionally upset — Desmoronarse.</t>
         </is>
       </c>
-      <c r="D651" t="inlineStr">
+      <c r="D651" s="0" t="inlineStr">
         <is>
           <t>Jack fell apart after the loss.</t>
         </is>
       </c>
-      <c r="I651" t="inlineStr">
+      <c r="I651" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: fall apart — Present: falls apart — Past: fell apart — Past participle: fallen apart. Intransitive; also used of things that break into pieces.</t>
         </is>
       </c>
     </row>
     <row r="652">
-      <c r="A652" t="inlineStr">
+      <c r="A652" s="0" t="inlineStr">
         <is>
           <t>Feel up to</t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
+      <c r="B652" s="0" t="inlineStr">
         <is>
           <t>fíl ap tu</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr">
+      <c r="C652" s="0" t="inlineStr">
         <is>
           <t>Feel able to do something — Sentirse capaz de.</t>
         </is>
       </c>
-      <c r="D652" t="inlineStr">
+      <c r="D652" s="0" t="inlineStr">
         <is>
           <t>Tom didn't feel up to going out.</t>
         </is>
       </c>
-      <c r="I652" t="inlineStr">
+      <c r="I652" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: feel up to — Present: feels up to — Past: felt up to — Past participle: felt up to. Not separable. Followed by a noun or by -ing.</t>
         </is>
       </c>
     </row>
     <row r="653">
-      <c r="A653" t="inlineStr">
+      <c r="A653" s="0" t="inlineStr">
         <is>
           <t>Wear down</t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B653" s="0" t="inlineStr">
         <is>
           <t>uér daun</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr">
+      <c r="C653" s="0" t="inlineStr">
         <is>
           <t>Make someone tired or stressed — Desgastar.</t>
         </is>
       </c>
-      <c r="D653" t="inlineStr">
+      <c r="D653" s="0" t="inlineStr">
         <is>
           <t>The long week wore him down.</t>
         </is>
       </c>
-      <c r="I653" t="inlineStr">
+      <c r="I653" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: wear down — Present: wears down — Past: wore down — Past participle: worn down. Separable: wear someone down.</t>
         </is>
       </c>
     </row>
     <row r="654">
-      <c r="A654" t="inlineStr">
+      <c r="A654" s="0" t="inlineStr">
         <is>
           <t>Ease up</t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B654" s="0" t="inlineStr">
         <is>
           <t>ís ap</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr">
+      <c r="C654" s="0" t="inlineStr">
         <is>
           <t>Become less worried or tense — Relajarse.</t>
         </is>
       </c>
-      <c r="D654" t="inlineStr">
+      <c r="D654" s="0" t="inlineStr">
         <is>
           <t>Sarah eased up after the test.</t>
         </is>
       </c>
-      <c r="I654" t="inlineStr">
+      <c r="I654" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: ease up — Present: eases up — Past: eased up — Past participle: eased up. Intransitive. Also said of rain or pressure letting up.</t>
         </is>
       </c>
     </row>
     <row r="655">
-      <c r="A655" t="inlineStr">
+      <c r="A655" s="0" t="inlineStr">
         <is>
           <t>Snap out of</t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B655" s="0" t="inlineStr">
         <is>
           <t>snáp aut of</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
+      <c r="C655" s="0" t="inlineStr">
         <is>
           <t>Stop feeling sad or worried — Salir de un estado de ánimo.</t>
         </is>
       </c>
-      <c r="D655" t="inlineStr">
+      <c r="D655" s="0" t="inlineStr">
         <is>
           <t>Emma snapped out of her bad mood.</t>
         </is>
       </c>
-      <c r="I655" t="inlineStr">
+      <c r="I655" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: snap out of — Present: snaps out of — Past: snapped out of — Past participle: snapped out of. Not separable. Often an imperative: snap out of it.</t>
         </is>
       </c>
     </row>
     <row r="656">
-      <c r="A656" t="inlineStr">
+      <c r="A656" s="0" t="inlineStr">
         <is>
           <t>Lighten up</t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B656" s="0" t="inlineStr">
         <is>
           <t>láiten ap</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr">
+      <c r="C656" s="0" t="inlineStr">
         <is>
           <t>Become less serious or worried — Tomárselo con calma.</t>
         </is>
       </c>
-      <c r="D656" t="inlineStr">
+      <c r="D656" s="0" t="inlineStr">
         <is>
           <t>Jack lightened up after hearing the joke.</t>
         </is>
       </c>
-      <c r="I656" t="inlineStr">
+      <c r="I656" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: lighten up — Present: lightens up — Past: lightened up — Past participle: lightened up. Intransitive, and usually said as an instruction.</t>
         </is>
       </c>
     </row>
     <row r="657">
-      <c r="A657" t="inlineStr">
+      <c r="A657" s="0" t="inlineStr">
         <is>
           <t>Warm up to</t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B657" s="0" t="inlineStr">
         <is>
           <t>uórm ap tu</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr">
+      <c r="C657" s="0" t="inlineStr">
         <is>
           <t>Gradually start liking someone — Agarrar confianza con.</t>
         </is>
       </c>
-      <c r="D657" t="inlineStr">
+      <c r="D657" s="0" t="inlineStr">
         <is>
           <t>Sarah warmed up to her new neighbor.</t>
         </is>
       </c>
-      <c r="I657" t="inlineStr">
+      <c r="I657" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: warm up to — Present: warms up to — Past: warmed up to — Past participle: warmed up to. Not separable.</t>
         </is>
       </c>
     </row>
     <row r="658">
-      <c r="A658" t="inlineStr">
+      <c r="A658" s="0" t="inlineStr">
         <is>
           <t>Lean on</t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B658" s="0" t="inlineStr">
         <is>
           <t>lín on</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr">
+      <c r="C658" s="0" t="inlineStr">
         <is>
           <t>Depend on someone for support — Apoyarse en.</t>
         </is>
       </c>
-      <c r="D658" t="inlineStr">
+      <c r="D658" s="0" t="inlineStr">
         <is>
           <t>Emma leaned on her sister.</t>
         </is>
       </c>
-      <c r="I658" t="inlineStr">
+      <c r="I658" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: lean on — Present: leans on — Past: leaned on — Past participle: leaned on. Not separable. British English also uses leant.</t>
         </is>
       </c>
     </row>
     <row r="659">
-      <c r="A659" t="inlineStr">
+      <c r="A659" s="0" t="inlineStr">
         <is>
           <t>Well up</t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B659" s="0" t="inlineStr">
         <is>
           <t>uél ap</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr">
+      <c r="C659" s="0" t="inlineStr">
         <is>
           <t>Fill with tears or strong emotion — Llenarse de lágrimas.</t>
         </is>
       </c>
-      <c r="D659" t="inlineStr">
+      <c r="D659" s="0" t="inlineStr">
         <is>
           <t>Tears welled up in her eyes.</t>
         </is>
       </c>
-      <c r="I659" t="inlineStr">
+      <c r="I659" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: well up — Present: wells up — Past: welled up — Past participle: welled up. Intransitive. The subject is usually tears or a feeling.</t>
         </is>
       </c>
     </row>
     <row r="660">
-      <c r="A660" t="inlineStr">
+      <c r="A660" s="0" t="inlineStr">
         <is>
           <t>Come around</t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B660" s="0" t="inlineStr">
         <is>
           <t>kam aráund</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr">
+      <c r="C660" s="0" t="inlineStr">
         <is>
           <t>Change your opinion or attitude — Cambiar de opinión.</t>
         </is>
       </c>
-      <c r="D660" t="inlineStr">
+      <c r="D660" s="0" t="inlineStr">
         <is>
           <t>Tom came around after talking to her.</t>
         </is>
       </c>
-      <c r="I660" t="inlineStr">
+      <c r="I660" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: come around — Present: comes around — Past: came around — Past participle: come around. Intransitive. Also means to regain consciousness.</t>
         </is>
       </c>
     </row>
     <row r="661">
-      <c r="A661" t="inlineStr">
+      <c r="A661" s="0" t="inlineStr">
         <is>
           <t>Dwell on</t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B661" s="0" t="inlineStr">
         <is>
           <t>duél on</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C661" s="0" t="inlineStr">
         <is>
           <t>Keep thinking about something upsetting — Darle vueltas a.</t>
         </is>
       </c>
-      <c r="D661" t="inlineStr">
+      <c r="D661" s="0" t="inlineStr">
         <is>
           <t>Emma dwelled on her mistake.</t>
         </is>
       </c>
-      <c r="I661" t="inlineStr">
+      <c r="I661" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: dwell on — Present: dwells on — Past: dwelled on — Past participle: dwelled on. Not separable. British English also uses dwelt.</t>
         </is>
       </c>
     </row>
     <row r="662">
-      <c r="A662" t="inlineStr">
+      <c r="A662" s="0" t="inlineStr">
         <is>
           <t>Shake off</t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B662" s="0" t="inlineStr">
         <is>
           <t>shéik of</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C662" s="0" t="inlineStr">
         <is>
           <t>Stop feeling something unpleasant — Quitarse de encima.</t>
         </is>
       </c>
-      <c r="D662" t="inlineStr">
+      <c r="D662" s="0" t="inlineStr">
         <is>
           <t>Tom shook off his worries.</t>
         </is>
       </c>
-      <c r="I662" t="inlineStr">
+      <c r="I662" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: shake off — Present: shakes off — Past: shook off — Past participle: shaken off. Separable: shake something off.</t>
         </is>
       </c>
     </row>
     <row r="663">
-      <c r="A663" t="inlineStr">
+      <c r="A663" s="0" t="inlineStr">
         <is>
           <t>Hang on to</t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B663" s="0" t="inlineStr">
         <is>
           <t>jáng on tu</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr">
+      <c r="C663" s="0" t="inlineStr">
         <is>
           <t>Keep a feeling or a memory — Aferrarse a.</t>
         </is>
       </c>
-      <c r="D663" t="inlineStr">
+      <c r="D663" s="0" t="inlineStr">
         <is>
           <t>Emma hung on to her childhood memories.</t>
         </is>
       </c>
-      <c r="I663" t="inlineStr">
+      <c r="I663" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: hang on to — Present: hangs on to — Past: hung on to — Past participle: hung on to. Not separable.</t>
         </is>
       </c>
     </row>
     <row r="664">
-      <c r="A664" t="inlineStr">
+      <c r="A664" s="0" t="inlineStr">
         <is>
           <t>Sink in</t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B664" s="0" t="inlineStr">
         <is>
           <t>sínk in</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C664" s="0" t="inlineStr">
         <is>
           <t>Be fully understood — Asimilarse.</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr">
+      <c r="D664" s="0" t="inlineStr">
         <is>
           <t>The news finally sank in.</t>
         </is>
       </c>
-      <c r="I664" t="inlineStr">
+      <c r="I664" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: sink in — Present: sinks in — Past: sank in — Past participle: sunk in. Intransitive. The subject is the news or the fact, not the person.</t>
         </is>
       </c>
     </row>
     <row r="665">
-      <c r="A665" t="inlineStr">
+      <c r="A665" s="0" t="inlineStr">
         <is>
           <t>Live through</t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B665" s="0" t="inlineStr">
         <is>
           <t>lív zru</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C665" s="0" t="inlineStr">
         <is>
           <t>Experience something difficult — Vivir algo difícil.</t>
         </is>
       </c>
-      <c r="D665" t="inlineStr">
+      <c r="D665" s="0" t="inlineStr">
         <is>
           <t>Tom lived through a stressful year.</t>
         </is>
       </c>
-      <c r="I665" t="inlineStr">
+      <c r="I665" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: live through — Present: lives through — Past: lived through — Past participle: lived through. Not separable.</t>
         </is>
       </c>
     </row>
     <row r="666">
-      <c r="A666" t="inlineStr">
+      <c r="A666" s="0" t="inlineStr">
         <is>
           <t>Look down on</t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B666" s="0" t="inlineStr">
         <is>
           <t>lúk daun on</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C666" s="0" t="inlineStr">
         <is>
           <t>Think you are better than someone — Menospreciar.</t>
         </is>
       </c>
-      <c r="D666" t="inlineStr">
+      <c r="D666" s="0" t="inlineStr">
         <is>
           <t>Jack looked down on his classmates.</t>
         </is>
       </c>
-      <c r="I666" t="inlineStr">
+      <c r="I666" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: look down on — Present: looks down on — Past: looked down on — Past participle: looked down on. Not separable.</t>
         </is>
       </c>
     </row>
     <row r="667">
-      <c r="A667" t="inlineStr">
+      <c r="A667" s="0" t="inlineStr">
         <is>
           <t>Beat yourself up</t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B667" s="0" t="inlineStr">
         <is>
           <t>bít yorsélf ap</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C667" s="0" t="inlineStr">
         <is>
           <t>Criticise yourself too much — Culparse demasiado.</t>
         </is>
       </c>
-      <c r="D667" t="inlineStr">
+      <c r="D667" s="0" t="inlineStr">
         <is>
           <t>Emma beat herself up over the mistake.</t>
         </is>
       </c>
-      <c r="I667" t="inlineStr">
+      <c r="I667" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: beat yourself up — Present: beats himself up — Past: beat herself up — Past participle: beaten yourself up. The middle word changes with the person: beat myself up, beat himself up.</t>
         </is>
       </c>
     </row>
     <row r="668">
-      <c r="A668" t="inlineStr">
+      <c r="A668" s="0" t="inlineStr">
         <is>
           <t>Miss out on</t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B668" s="0" t="inlineStr">
         <is>
           <t>mís aut on</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C668" s="0" t="inlineStr">
         <is>
           <t>Lose the chance to experience something — Perderse algo.</t>
         </is>
       </c>
-      <c r="D668" t="inlineStr">
+      <c r="D668" s="0" t="inlineStr">
         <is>
           <t>Tom missed out on the trip.</t>
         </is>
       </c>
-      <c r="I668" t="inlineStr">
+      <c r="I668" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: miss out on — Present: misses out on — Past: missed out on — Past participle: missed out on. Not separable.</t>
         </is>
       </c>
     </row>
     <row r="669">
-      <c r="A669" t="inlineStr">
+      <c r="A669" s="0" t="inlineStr">
         <is>
           <t>Break into</t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B669" s="0" t="inlineStr">
         <is>
           <t>bréik íntu</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C669" s="0" t="inlineStr">
         <is>
           <t>Suddenly show an emotion — Echarse a.</t>
         </is>
       </c>
-      <c r="D669" t="inlineStr">
+      <c r="D669" s="0" t="inlineStr">
         <is>
           <t>Emma broke into laughter.</t>
         </is>
       </c>
-      <c r="I669" t="inlineStr">
+      <c r="I669" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: break into — Present: breaks into — Past: broke into — Past participle: broken into. Not separable. Also means to enter a building by force.</t>
         </is>
       </c>
     </row>
     <row r="670">
-      <c r="A670" t="inlineStr">
+      <c r="A670" s="0" t="inlineStr">
         <is>
           <t>Get carried away</t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B670" s="0" t="inlineStr">
         <is>
           <t>guét kárid auéi</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C670" s="0" t="inlineStr">
         <is>
           <t>Become too excited or emotional — Dejarse llevar.</t>
         </is>
       </c>
-      <c r="D670" t="inlineStr">
+      <c r="D670" s="0" t="inlineStr">
         <is>
           <t>Tom got carried away during the celebration.</t>
         </is>
       </c>
-      <c r="I670" t="inlineStr">
+      <c r="I670" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: get carried away — Present: gets carried away — Past: got carried away — Past participle: gotten carried away. A fixed expression; the three words stay together.</t>
         </is>
       </c>
     </row>
     <row r="671">
-      <c r="A671" t="inlineStr">
+      <c r="A671" s="0" t="inlineStr">
         <is>
           <t>Bottle out</t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B671" s="0" t="inlineStr">
         <is>
           <t>bótel áut</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
+      <c r="C671" s="0" t="inlineStr">
         <is>
           <t>Lose courage and back out — Echarse atrás.</t>
         </is>
       </c>
-      <c r="D671" t="inlineStr">
+      <c r="D671" s="0" t="inlineStr">
         <is>
           <t>Jack bottled out of giving the speech.</t>
         </is>
       </c>
-      <c r="I671" t="inlineStr">
+      <c r="I671" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: bottle out — Present: bottles out — Past: bottled out — Past participle: bottled out. Intransitive. British and informal.</t>
         </is>
       </c>
     </row>
     <row r="672">
-      <c r="A672" t="inlineStr">
+      <c r="A672" s="0" t="inlineStr">
         <is>
           <t>Fight back</t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B672" s="0" t="inlineStr">
         <is>
           <t>fáit bak</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr">
+      <c r="C672" s="0" t="inlineStr">
         <is>
           <t>Stop yourself from showing emotion — Contener.</t>
         </is>
       </c>
-      <c r="D672" t="inlineStr">
+      <c r="D672" s="0" t="inlineStr">
         <is>
           <t>Sarah fought back her tears.</t>
         </is>
       </c>
-      <c r="I672" t="inlineStr">
+      <c r="I672" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: fight back — Present: fights back — Past: fought back — Past participle: fought back. Separable in this sense. On its own it means to defend yourself.</t>
         </is>
       </c>
     </row>
     <row r="673">
-      <c r="A673" t="inlineStr">
+      <c r="A673" s="0" t="inlineStr">
         <is>
           <t>Clam up</t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B673" s="0" t="inlineStr">
         <is>
           <t>klám ap</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C673" s="0" t="inlineStr">
         <is>
           <t>Suddenly stop talking — Quedarse callado.</t>
         </is>
       </c>
-      <c r="D673" t="inlineStr">
+      <c r="D673" s="0" t="inlineStr">
         <is>
           <t>Tom clammed up during the interview.</t>
         </is>
       </c>
-      <c r="I673" t="inlineStr">
+      <c r="I673" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: clam up — Present: clams up — Past: clammed up — Past participle: clammed up. Intransitive and informal.</t>
         </is>
       </c>
     </row>
     <row r="674">
-      <c r="A674" t="inlineStr">
+      <c r="A674" s="0" t="inlineStr">
         <is>
           <t>Bring about</t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B674" s="0" t="inlineStr">
         <is>
           <t>bring abáut</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
+      <c r="C674" s="0" t="inlineStr">
         <is>
           <t>Cause something to happen — Provocar.</t>
         </is>
       </c>
-      <c r="D674" t="inlineStr">
+      <c r="D674" s="0" t="inlineStr">
         <is>
           <t>The new rule brought about positive changes.</t>
         </is>
       </c>
-      <c r="I674" t="inlineStr">
+      <c r="I674" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: bring about — Present: brings about — Past: brought about — Past participle: brought about. Separable, though the object usually follows the whole verb.</t>
         </is>
       </c>
     </row>
     <row r="675">
-      <c r="A675" t="inlineStr">
+      <c r="A675" s="0" t="inlineStr">
         <is>
           <t>Carry out</t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B675" s="0" t="inlineStr">
         <is>
           <t>kári áut</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C675" s="0" t="inlineStr">
         <is>
           <t>Complete a task or a plan — Llevar a cabo.</t>
         </is>
       </c>
-      <c r="D675" t="inlineStr">
+      <c r="D675" s="0" t="inlineStr">
         <is>
           <t>The students carried out the project successfully.</t>
         </is>
       </c>
-      <c r="I675" t="inlineStr">
+      <c r="I675" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: carry out — Present: carries out — Past: carried out — Past participle: carried out. Separable: carry it out.</t>
         </is>
       </c>
     </row>
     <row r="676">
-      <c r="A676" t="inlineStr">
+      <c r="A676" s="0" t="inlineStr">
         <is>
           <t>Come up with</t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B676" s="0" t="inlineStr">
         <is>
           <t>kam ap uith</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C676" s="0" t="inlineStr">
         <is>
           <t>Think of an idea or a solution — Ocurrírsele a uno.</t>
         </is>
       </c>
-      <c r="D676" t="inlineStr">
+      <c r="D676" s="0" t="inlineStr">
         <is>
           <t>Sarah came up with a clever idea.</t>
         </is>
       </c>
-      <c r="I676" t="inlineStr">
+      <c r="I676" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: come up with — Present: comes up with — Past: came up with — Past participle: come up with. Not separable; all three words stay together.</t>
         </is>
       </c>
     </row>
     <row r="677">
-      <c r="A677" t="inlineStr">
+      <c r="A677" s="0" t="inlineStr">
         <is>
           <t>Turn out</t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B677" s="0" t="inlineStr">
         <is>
           <t>tern áut</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
+      <c r="C677" s="0" t="inlineStr">
         <is>
           <t>Happen or develop in a particular way — Resultar.</t>
         </is>
       </c>
-      <c r="D677" t="inlineStr">
+      <c r="D677" s="0" t="inlineStr">
         <is>
           <t>The party turned out great.</t>
         </is>
       </c>
-      <c r="I677" t="inlineStr">
+      <c r="I677" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: turn out — Present: turns out — Past: turned out — Past participle: turned out. Intransitive in this sense. Often: it turned out that...</t>
         </is>
       </c>
     </row>
     <row r="678">
-      <c r="A678" t="inlineStr">
+      <c r="A678" s="0" t="inlineStr">
         <is>
           <t>Get away with</t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B678" s="0" t="inlineStr">
         <is>
           <t>guét auéi uith</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="C678" s="0" t="inlineStr">
         <is>
           <t>Avoid punishment for something — Salirse con la suya.</t>
         </is>
       </c>
-      <c r="D678" t="inlineStr">
+      <c r="D678" s="0" t="inlineStr">
         <is>
           <t>Jack got away with breaking the rules.</t>
         </is>
       </c>
-      <c r="I678" t="inlineStr">
+      <c r="I678" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: get away with — Present: gets away with — Past: got away with — Past participle: gotten away with. Not separable.</t>
         </is>
       </c>
     </row>
     <row r="679">
-      <c r="A679" t="inlineStr">
+      <c r="A679" s="0" t="inlineStr">
         <is>
           <t>Put up with</t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B679" s="0" t="inlineStr">
         <is>
           <t>pút ap uith</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C679" s="0" t="inlineStr">
         <is>
           <t>Tolerate something unpleasant — Aguantar.</t>
         </is>
       </c>
-      <c r="D679" t="inlineStr">
+      <c r="D679" s="0" t="inlineStr">
         <is>
           <t>Sarah put up with the loud noise.</t>
         </is>
       </c>
-      <c r="I679" t="inlineStr">
+      <c r="I679" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: put up with — Present: puts up with — Past: put up with — Past participle: put up with. Not separable. The past looks the same as the base.</t>
         </is>
       </c>
     </row>
     <row r="680">
-      <c r="A680" t="inlineStr">
+      <c r="A680" s="0" t="inlineStr">
         <is>
           <t>Back out</t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B680" s="0" t="inlineStr">
         <is>
           <t>bák áut</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C680" s="0" t="inlineStr">
         <is>
           <t>Withdraw from an agreement or a plan — Echarse atrás.</t>
         </is>
       </c>
-      <c r="D680" t="inlineStr">
+      <c r="D680" s="0" t="inlineStr">
         <is>
           <t>Jack backed out of the deal.</t>
         </is>
       </c>
-      <c r="I680" t="inlineStr">
+      <c r="I680" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: back out — Present: backs out — Past: backed out — Past participle: backed out. Intransitive: back out of something.</t>
         </is>
       </c>
     </row>
     <row r="681">
-      <c r="A681" t="inlineStr">
+      <c r="A681" s="0" t="inlineStr">
         <is>
           <t>Come up against</t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B681" s="0" t="inlineStr">
         <is>
           <t>kam ap aguénst</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr">
+      <c r="C681" s="0" t="inlineStr">
         <is>
           <t>Face a difficulty — Toparse con.</t>
         </is>
       </c>
-      <c r="D681" t="inlineStr">
+      <c r="D681" s="0" t="inlineStr">
         <is>
           <t>The team came up against many problems.</t>
         </is>
       </c>
-      <c r="I681" t="inlineStr">
+      <c r="I681" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: come up against — Present: comes up against — Past: came up against — Past participle: come up against. Not separable.</t>
         </is>
       </c>
     </row>
     <row r="682">
-      <c r="A682" t="inlineStr">
+      <c r="A682" s="0" t="inlineStr">
         <is>
           <t>Drop out</t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B682" s="0" t="inlineStr">
         <is>
           <t>dráp áut</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
+      <c r="C682" s="0" t="inlineStr">
         <is>
           <t>Leave a course before finishing — Abandonar los estudios.</t>
         </is>
       </c>
-      <c r="D682" t="inlineStr">
+      <c r="D682" s="0" t="inlineStr">
         <is>
           <t>Jack dropped out of college.</t>
         </is>
       </c>
-      <c r="I682" t="inlineStr">
+      <c r="I682" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: drop out — Present: drops out — Past: dropped out — Past participle: dropped out. Intransitive: drop out of something.</t>
         </is>
       </c>
     </row>
     <row r="683">
-      <c r="A683" t="inlineStr">
+      <c r="A683" s="0" t="inlineStr">
         <is>
           <t>Get over with</t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B683" s="0" t="inlineStr">
         <is>
           <t>guét óuver uith</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C683" s="0" t="inlineStr">
         <is>
           <t>Finish something unpleasant — Terminar de una vez.</t>
         </is>
       </c>
-      <c r="D683" t="inlineStr">
+      <c r="D683" s="0" t="inlineStr">
         <is>
           <t>Emma got the exam over with quickly.</t>
         </is>
       </c>
-      <c r="I683" t="inlineStr">
+      <c r="I683" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: get over with — Present: gets over with — Past: got over with — Past participle: gotten over with. The object goes in the middle: get it over with.</t>
         </is>
       </c>
     </row>
     <row r="684">
-      <c r="A684" t="inlineStr">
+      <c r="A684" s="0" t="inlineStr">
         <is>
           <t>Pull off</t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B684" s="0" t="inlineStr">
         <is>
           <t>púl of</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr">
+      <c r="C684" s="0" t="inlineStr">
         <is>
           <t>Succeed in doing something difficult — Lograr.</t>
         </is>
       </c>
-      <c r="D684" t="inlineStr">
+      <c r="D684" s="0" t="inlineStr">
         <is>
           <t>Sarah pulled off a great performance.</t>
         </is>
       </c>
-      <c r="I684" t="inlineStr">
+      <c r="I684" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: pull off — Present: pulls off — Past: pulled off — Past participle: pulled off. Separable: pull it off.</t>
         </is>
       </c>
     </row>
     <row r="685">
-      <c r="A685" t="inlineStr">
+      <c r="A685" s="0" t="inlineStr">
         <is>
           <t>Turn down</t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B685" s="0" t="inlineStr">
         <is>
           <t>tern dáun</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C685" s="0" t="inlineStr">
         <is>
           <t>Refuse an offer or a request — Rechazar.</t>
         </is>
       </c>
-      <c r="D685" t="inlineStr">
+      <c r="D685" s="0" t="inlineStr">
         <is>
           <t>Emma turned down the job offer.</t>
         </is>
       </c>
-      <c r="I685" t="inlineStr">
+      <c r="I685" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: turn down — Present: turns down — Past: turned down — Past participle: turned down. Separable: turn it down. Also means to lower the volume.</t>
         </is>
       </c>
     </row>
     <row r="686">
-      <c r="A686" t="inlineStr">
+      <c r="A686" s="0" t="inlineStr">
         <is>
           <t>Turn up</t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B686" s="0" t="inlineStr">
         <is>
           <t>tern ap</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C686" s="0" t="inlineStr">
         <is>
           <t>Appear or be found unexpectedly — Aparecer.</t>
         </is>
       </c>
-      <c r="D686" t="inlineStr">
+      <c r="D686" s="0" t="inlineStr">
         <is>
           <t>My keys turned up yesterday.</t>
         </is>
       </c>
-      <c r="I686" t="inlineStr">
+      <c r="I686" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: turn up — Present: turns up — Past: turned up — Past participle: turned up. Intransitive in this sense. Also means to raise the volume.</t>
         </is>
       </c>
     </row>
     <row r="687">
-      <c r="A687" t="inlineStr">
+      <c r="A687" s="0" t="inlineStr">
         <is>
           <t>Work through</t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B687" s="0" t="inlineStr">
         <is>
           <t>uérk zru</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="C687" s="0" t="inlineStr">
         <is>
           <t>Deal with a problem step by step — Resolver poco a poco.</t>
         </is>
       </c>
-      <c r="D687" t="inlineStr">
+      <c r="D687" s="0" t="inlineStr">
         <is>
           <t>Sarah worked through her difficulties.</t>
         </is>
       </c>
-      <c r="I687" t="inlineStr">
+      <c r="I687" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: work through — Present: works through — Past: worked through — Past participle: worked through. Not separable.</t>
         </is>
       </c>
     </row>
     <row r="688">
-      <c r="A688" t="inlineStr">
+      <c r="A688" s="0" t="inlineStr">
         <is>
           <t>Write off</t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B688" s="0" t="inlineStr">
         <is>
           <t>ráit of</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr">
+      <c r="C688" s="0" t="inlineStr">
         <is>
           <t>Consider something a loss — Dar por perdido.</t>
         </is>
       </c>
-      <c r="D688" t="inlineStr">
+      <c r="D688" s="0" t="inlineStr">
         <is>
           <t>The company wrote off the damaged equipment.</t>
         </is>
       </c>
-      <c r="I688" t="inlineStr">
+      <c r="I688" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: write off — Present: writes off — Past: wrote off — Past participle: written off. Separable: write it off.</t>
         </is>
       </c>
     </row>
     <row r="689">
-      <c r="A689" t="inlineStr">
+      <c r="A689" s="0" t="inlineStr">
         <is>
           <t>Pass up</t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B689" s="0" t="inlineStr">
         <is>
           <t>pás ap</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
+      <c r="C689" s="0" t="inlineStr">
         <is>
           <t>Miss an opportunity by not taking it — Dejar pasar.</t>
         </is>
       </c>
-      <c r="D689" t="inlineStr">
+      <c r="D689" s="0" t="inlineStr">
         <is>
           <t>Tom passed up a great offer.</t>
         </is>
       </c>
-      <c r="I689" t="inlineStr">
+      <c r="I689" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: pass up — Present: passes up — Past: passed up — Past participle: passed up. Separable: pass it up.</t>
         </is>
       </c>
     </row>
     <row r="690">
-      <c r="A690" t="inlineStr">
+      <c r="A690" s="0" t="inlineStr">
         <is>
           <t>Follow through</t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
+      <c r="B690" s="0" t="inlineStr">
         <is>
           <t>fólou zru</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C690" s="0" t="inlineStr">
         <is>
           <t>Complete what you started — Cumplir hasta el final.</t>
         </is>
       </c>
-      <c r="D690" t="inlineStr">
+      <c r="D690" s="0" t="inlineStr">
         <is>
           <t>Emma followed through on her promise.</t>
         </is>
       </c>
-      <c r="I690" t="inlineStr">
+      <c r="I690" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: follow through — Present: follows through — Past: followed through — Past participle: followed through. Not separable; usually follow through on something.</t>
         </is>
       </c>
     </row>
     <row r="691">
-      <c r="A691" t="inlineStr">
+      <c r="A691" s="0" t="inlineStr">
         <is>
           <t>Let down</t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
+      <c r="B691" s="0" t="inlineStr">
         <is>
           <t>lét daun</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C691" s="0" t="inlineStr">
         <is>
           <t>Disappoint someone — Defraudar.</t>
         </is>
       </c>
-      <c r="D691" t="inlineStr">
+      <c r="D691" s="0" t="inlineStr">
         <is>
           <t>Sarah let her team down.</t>
         </is>
       </c>
-      <c r="I691" t="inlineStr">
+      <c r="I691" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: let down — Present: lets down — Past: let down — Past participle: let down. Separable: let someone down. All the forms look the same.</t>
         </is>
       </c>
     </row>
     <row r="692">
-      <c r="A692" t="inlineStr">
+      <c r="A692" s="0" t="inlineStr">
         <is>
           <t>Call for</t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
+      <c r="B692" s="0" t="inlineStr">
         <is>
           <t>kol for</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C692" s="0" t="inlineStr">
         <is>
           <t>Require something — Requerir.</t>
         </is>
       </c>
-      <c r="D692" t="inlineStr">
+      <c r="D692" s="0" t="inlineStr">
         <is>
           <t>The situation called for quick action.</t>
         </is>
       </c>
-      <c r="I692" t="inlineStr">
+      <c r="I692" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: call for — Present: calls for — Past: called for — Past participle: called for. Not separable.</t>
         </is>
       </c>
     </row>
     <row r="693">
-      <c r="A693" t="inlineStr">
+      <c r="A693" s="0" t="inlineStr">
         <is>
           <t>Rule out</t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
+      <c r="B693" s="0" t="inlineStr">
         <is>
           <t>rúl áut</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr">
+      <c r="C693" s="0" t="inlineStr">
         <is>
           <t>Eliminate a possibility — Descartar.</t>
         </is>
       </c>
-      <c r="D693" t="inlineStr">
+      <c r="D693" s="0" t="inlineStr">
         <is>
           <t>The doctor ruled out an infection.</t>
         </is>
       </c>
-      <c r="I693" t="inlineStr">
+      <c r="I693" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: rule out — Present: rules out — Past: ruled out — Past participle: ruled out. Separable: rule it out.</t>
         </is>
       </c>
     </row>
     <row r="694">
-      <c r="A694" t="inlineStr">
+      <c r="A694" s="0" t="inlineStr">
         <is>
           <t>Put down to</t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
+      <c r="B694" s="0" t="inlineStr">
         <is>
           <t>pút daun tu</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr">
+      <c r="C694" s="0" t="inlineStr">
         <is>
           <t>Explain something as caused by — Atribuir a.</t>
         </is>
       </c>
-      <c r="D694" t="inlineStr">
+      <c r="D694" s="0" t="inlineStr">
         <is>
           <t>Tom put his success down to practice.</t>
         </is>
       </c>
-      <c r="I694" t="inlineStr">
+      <c r="I694" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: put down to — Present: puts down to — Past: put down to — Past participle: put down to. The object goes in the middle: put it down to luck.</t>
         </is>
       </c>
     </row>
     <row r="695">
-      <c r="A695" t="inlineStr">
+      <c r="A695" s="0" t="inlineStr">
         <is>
           <t>See through</t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B695" s="0" t="inlineStr">
         <is>
           <t>sí zru</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C695" s="0" t="inlineStr">
         <is>
           <t>Recognise the truth about something — Calar.</t>
         </is>
       </c>
-      <c r="D695" t="inlineStr">
+      <c r="D695" s="0" t="inlineStr">
         <is>
           <t>Emma saw through the excuse.</t>
         </is>
       </c>
-      <c r="I695" t="inlineStr">
+      <c r="I695" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: see through — Present: sees through — Past: saw through — Past participle: seen through. Not separable in this sense.</t>
         </is>
       </c>
     </row>
     <row r="696">
-      <c r="A696" t="inlineStr">
+      <c r="A696" s="0" t="inlineStr">
         <is>
           <t>Stand up for</t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B696" s="0" t="inlineStr">
         <is>
           <t>stand ap for</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C696" s="0" t="inlineStr">
         <is>
           <t>Defend someone or something — Defender.</t>
         </is>
       </c>
-      <c r="D696" t="inlineStr">
+      <c r="D696" s="0" t="inlineStr">
         <is>
           <t>Jack stood up for his friend.</t>
         </is>
       </c>
-      <c r="I696" t="inlineStr">
+      <c r="I696" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: stand up for — Present: stands up for — Past: stood up for — Past participle: stood up for. Not separable.</t>
         </is>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I696"/>
+  <dimension ref="A1:I713"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -24350,6 +24350,505 @@
       <c r="I696" s="0" t="inlineStr">
         <is>
           <t>Irregular verb. Base: stand up for — Present: stands up for — Past: stood up for — Past participle: stood up for. Not separable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="0" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="B697" s="0" t="inlineStr">
+        <is>
+          <t>béi</t>
+        </is>
+      </c>
+      <c r="C697" s="0" t="inlineStr">
+        <is>
+          <t>Body of water partly enclosed by land — Bahía.</t>
+        </is>
+      </c>
+      <c r="D697" s="0" t="inlineStr">
+        <is>
+          <t>We anchored the boat in the bay.</t>
+        </is>
+      </c>
+      <c r="I697" s="0" t="inlineStr">
+        <is>
+          <t>Common in set phrases such as 'bay leaf' (hoja de laurel) and 'loading bay' (muelle de carga).</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="0" t="inlineStr">
+        <is>
+          <t>Sparkling</t>
+        </is>
+      </c>
+      <c r="B698" s="0" t="inlineStr">
+        <is>
+          <t>spárklin</t>
+        </is>
+      </c>
+      <c r="C698" s="0" t="inlineStr">
+        <is>
+          <t>Shining brightly with flashes of light — Brillante, centelleante.</t>
+        </is>
+      </c>
+      <c r="D698" s="0" t="inlineStr">
+        <is>
+          <t>She wore a sparkling diamond necklace.</t>
+        </is>
+      </c>
+      <c r="E698" s="0" t="inlineStr">
+        <is>
+          <t>Containing bubbles of gas — Con gas, espumoso.</t>
+        </is>
+      </c>
+      <c r="F698" s="0" t="inlineStr">
+        <is>
+          <t>I prefer sparkling water to still water.</t>
+        </is>
+      </c>
+      <c r="I698" s="0" t="inlineStr">
+        <is>
+          <t>The opposite of sparkling water (agua con gas) is still water (agua sin gas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="0" t="inlineStr">
+        <is>
+          <t>Timeless</t>
+        </is>
+      </c>
+      <c r="B699" s="0" t="inlineStr">
+        <is>
+          <t>táimles</t>
+        </is>
+      </c>
+      <c r="C699" s="0" t="inlineStr">
+        <is>
+          <t>Classic and unaffected by time — Atemporal.</t>
+        </is>
+      </c>
+      <c r="D699" s="0" t="inlineStr">
+        <is>
+          <t>This book is a timeless classic.</t>
+        </is>
+      </c>
+      <c r="I699" s="0" t="inlineStr">
+        <is>
+          <t>Often used to describe fashion, art, or beauty that never goes out of style.</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="0" t="inlineStr">
+        <is>
+          <t>Coastal</t>
+        </is>
+      </c>
+      <c r="B700" s="0" t="inlineStr">
+        <is>
+          <t>kóustal</t>
+        </is>
+      </c>
+      <c r="C700" s="0" t="inlineStr">
+        <is>
+          <t>Related to the coast — Costero.</t>
+        </is>
+      </c>
+      <c r="D700" s="0" t="inlineStr">
+        <is>
+          <t>We took a scenic drive along the coastal road.</t>
+        </is>
+      </c>
+      <c r="I700" s="0" t="inlineStr">
+        <is>
+          <t>Adjective. Derived from the noun 'coast'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="0" t="inlineStr">
+        <is>
+          <t>Charm</t>
+        </is>
+      </c>
+      <c r="B701" s="0" t="inlineStr">
+        <is>
+          <t>chárm</t>
+        </is>
+      </c>
+      <c r="C701" s="0" t="inlineStr">
+        <is>
+          <t>A pleasing or attractive quality — Encanto.</t>
+        </is>
+      </c>
+      <c r="D701" s="0" t="inlineStr">
+        <is>
+          <t>The historic town has a lot of charm.</t>
+        </is>
+      </c>
+      <c r="E701" s="0" t="inlineStr">
+        <is>
+          <t>To delight or attract someone — Encantar, cautivar.</t>
+        </is>
+      </c>
+      <c r="F701" s="0" t="inlineStr">
+        <is>
+          <t>He managed to charm everyone at the party.</t>
+        </is>
+      </c>
+      <c r="G701" s="0" t="inlineStr">
+        <is>
+          <t>A small ornament on a bracelet or a lucky object — Amuleto, dije.</t>
+        </is>
+      </c>
+      <c r="H701" s="0" t="inlineStr">
+        <is>
+          <t>She wears a gold bracelet with a heart charm.</t>
+        </is>
+      </c>
+      <c r="I701" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: charm — Present: charms — Past: charmed — Past participle: charmed. Also functions as a noun. The common idiom "work like a charm" means to work perfectly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="0" t="inlineStr">
+        <is>
+          <t>Shoreline</t>
+        </is>
+      </c>
+      <c r="B702" s="0" t="inlineStr">
+        <is>
+          <t>shórlain</t>
+        </is>
+      </c>
+      <c r="C702" s="0" t="inlineStr">
+        <is>
+          <t>The edge of a body of water — Orilla, línea costera.</t>
+        </is>
+      </c>
+      <c r="D702" s="0" t="inlineStr">
+        <is>
+          <t>We walked along the shoreline at sunset.</t>
+        </is>
+      </c>
+      <c r="I702" s="0" t="inlineStr">
+        <is>
+          <t>Noun. Refers specifically to the precise line where the water meets the land.</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="0" t="inlineStr">
+        <is>
+          <t>Sunset</t>
+        </is>
+      </c>
+      <c r="B703" s="0" t="inlineStr">
+        <is>
+          <t>sánset</t>
+        </is>
+      </c>
+      <c r="C703" s="0" t="inlineStr">
+        <is>
+          <t>The time in the evening when the sun disappears — Atardecer, puesta de sol.</t>
+        </is>
+      </c>
+      <c r="D703" s="0" t="inlineStr">
+        <is>
+          <t>We sat on the beach to watch the sunset.</t>
+        </is>
+      </c>
+      <c r="I703" s="0" t="inlineStr">
+        <is>
+          <t>Opposite of sunrise (amanecer).</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="0" t="inlineStr">
+        <is>
+          <t>Seaside</t>
+        </is>
+      </c>
+      <c r="B704" s="0" t="inlineStr">
+        <is>
+          <t>sísaid</t>
+        </is>
+      </c>
+      <c r="C704" s="0" t="inlineStr">
+        <is>
+          <t>Area by the sea, especially a holiday resort — Costa, playa, junto al mar.</t>
+        </is>
+      </c>
+      <c r="D704" s="0" t="inlineStr">
+        <is>
+          <t>We spent our summer holidays at the seaside.</t>
+        </is>
+      </c>
+      <c r="I704" s="0" t="inlineStr">
+        <is>
+          <t>Commonly used with the definite article 'the' (at the seaside) to refer to a holiday destination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="0" t="inlineStr">
+        <is>
+          <t>Postcard</t>
+        </is>
+      </c>
+      <c r="B705" s="0" t="inlineStr">
+        <is>
+          <t>póust-card</t>
+        </is>
+      </c>
+      <c r="C705" s="0" t="inlineStr">
+        <is>
+          <t>Card for sending a message by mail without an envelope — Tarjeta postal.</t>
+        </is>
+      </c>
+      <c r="D705" s="0" t="inlineStr">
+        <is>
+          <t>She sent me a postcard from Paris.</t>
+        </is>
+      </c>
+      <c r="I705" s="0" t="inlineStr">
+        <is>
+          <t>Usually has a photo or picture on one side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="0" t="inlineStr">
+        <is>
+          <t>Head off</t>
+        </is>
+      </c>
+      <c r="B706" s="0" t="inlineStr">
+        <is>
+          <t>jed of</t>
+        </is>
+      </c>
+      <c r="C706" s="0" t="inlineStr">
+        <is>
+          <t>Leave or start a journey — Marcharse.</t>
+        </is>
+      </c>
+      <c r="D706" s="0" t="inlineStr">
+        <is>
+          <t>Let's head off down the path.</t>
+        </is>
+      </c>
+      <c r="I706" s="0" t="inlineStr">
+        <is>
+          <t>Phrasal verb. Base: head off — Present: heads off — Past: headed off — Past participle: headed off. Also used to mean prevent something from happening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="0" t="inlineStr">
+        <is>
+          <t>Head off down</t>
+        </is>
+      </c>
+      <c r="B707" s="0" t="inlineStr">
+        <is>
+          <t>jed of daun</t>
+        </is>
+      </c>
+      <c r="C707" s="0" t="inlineStr">
+        <is>
+          <t>Start walking or traveling in a specific direction — Dirigirse hacia, salir hacia.</t>
+        </is>
+      </c>
+      <c r="D707" s="0" t="inlineStr">
+        <is>
+          <t>Let's head off down the road before it rains.</t>
+        </is>
+      </c>
+      <c r="I707" s="0" t="inlineStr">
+        <is>
+          <t>Phrasal verb. Base: head off down — Present: heads off down — Past: headed off down — Past participle: headed off down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="0" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B708" s="0" t="inlineStr">
+        <is>
+          <t>paz</t>
+        </is>
+      </c>
+      <c r="C708" s="0" t="inlineStr">
+        <is>
+          <t>Track or way made by walking — Sendero, camino.</t>
+        </is>
+      </c>
+      <c r="D708" s="0" t="inlineStr">
+        <is>
+          <t>We followed the narrow path through the woods.</t>
+        </is>
+      </c>
+      <c r="E708" s="0" t="inlineStr">
+        <is>
+          <t>Course of action or direction — Camino, trayectoria.</t>
+        </is>
+      </c>
+      <c r="F708" s="0" t="inlineStr">
+        <is>
+          <t>Choosing the right career path is important.</t>
+        </is>
+      </c>
+      <c r="I708" s="0" t="inlineStr">
+        <is>
+          <t>Plural is paths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="0" t="inlineStr">
+        <is>
+          <t>Catch</t>
+        </is>
+      </c>
+      <c r="B709" s="0" t="inlineStr">
+        <is>
+          <t>kach</t>
+        </is>
+      </c>
+      <c r="C709" s="0" t="inlineStr">
+        <is>
+          <t>Capture or trap a moving object or animal — Atrapar o pescar.</t>
+        </is>
+      </c>
+      <c r="D709" s="0" t="inlineStr">
+        <is>
+          <t>Are you ready to see what we can catch?</t>
+        </is>
+      </c>
+      <c r="I709" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: catch — Present: catches — Past: caught — Past participle: caught.</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="0" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="B710" s="0" t="inlineStr">
+        <is>
+          <t>lid</t>
+        </is>
+      </c>
+      <c r="C710" s="0" t="inlineStr">
+        <is>
+          <t>Show the way by going in front — Guiar.</t>
+        </is>
+      </c>
+      <c r="D710" s="0" t="inlineStr">
+        <is>
+          <t>Lead the way through the cul-de-sac.</t>
+        </is>
+      </c>
+      <c r="I710" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: lead — Present: leads — Past: led — Past participle: led. Do not confuse with the noun meaning the metal, which is pronounced 'led'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="0" t="inlineStr">
+        <is>
+          <t>Straight on the hook</t>
+        </is>
+      </c>
+      <c r="B711" s="0" t="inlineStr">
+        <is>
+          <t>streit on the juk</t>
+        </is>
+      </c>
+      <c r="C711" s="0" t="inlineStr">
+        <is>
+          <t>Immediately available or ready — Directamente listo.</t>
+        </is>
+      </c>
+      <c r="D711" s="0" t="inlineStr">
+        <is>
+          <t>The taxi is waiting straight on the hook.</t>
+        </is>
+      </c>
+      <c r="I711" s="0" t="inlineStr">
+        <is>
+          <t>Idiomatic phrase used to indicate that something or someone is instantly ready for action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="0" t="inlineStr">
+        <is>
+          <t>Pull around</t>
+        </is>
+      </c>
+      <c r="B712" s="0" t="inlineStr">
+        <is>
+          <t>pul araund</t>
+        </is>
+      </c>
+      <c r="C712" s="0" t="inlineStr">
+        <is>
+          <t>Drive a vehicle to the next designated spot — Avanzar con el vehículo.</t>
+        </is>
+      </c>
+      <c r="D712" s="0" t="inlineStr">
+        <is>
+          <t>Please pull around to the second window.</t>
+        </is>
+      </c>
+      <c r="I712" s="0" t="inlineStr">
+        <is>
+          <t>Phrasal verb. Base: pull around — Present: pulls around — Past: pulled around — Past participle: pulled around. Often used in drive-thrus to direct cars forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Drive on up</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>draiv on ap</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Move a vehicle closer by driving — Acercarse en vehículo.</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Drive on up to the window.</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>Phrasal verb. Base: drive on up — Present: drives on up — Past: drove on up — Past participle: driven on up.</t>
         </is>
       </c>
     </row>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I713"/>
+  <dimension ref="A1:I714"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -24826,29 +24826,51 @@
       </c>
     </row>
     <row r="713">
-      <c r="A713" t="inlineStr">
+      <c r="A713" s="0" t="inlineStr">
         <is>
           <t>Drive on up</t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
+      <c r="B713" s="0" t="inlineStr">
         <is>
           <t>draiv on ap</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
+      <c r="C713" s="0" t="inlineStr">
         <is>
           <t>Move a vehicle closer by driving — Acercarse en vehículo.</t>
         </is>
       </c>
-      <c r="D713" t="inlineStr">
+      <c r="D713" s="0" t="inlineStr">
         <is>
           <t>Drive on up to the window.</t>
         </is>
       </c>
-      <c r="I713" t="inlineStr">
+      <c r="I713" s="0" t="inlineStr">
         <is>
           <t>Phrasal verb. Base: drive on up — Present: drives on up — Past: drove on up — Past participle: driven on up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Equator</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>ekuator</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Imaginary line around the middle of the Earth — Ecuador.</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>The equator divides the Earth into the Northern and Southern Hemispheres.</t>
         </is>
       </c>
     </row>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I714"/>
+  <dimension ref="A1:I717"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -24853,24 +24853,115 @@
       </c>
     </row>
     <row r="714">
-      <c r="A714" t="inlineStr">
+      <c r="A714" s="0" t="inlineStr">
         <is>
           <t>Equator</t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
+      <c r="B714" s="0" t="inlineStr">
         <is>
           <t>ekuator</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr">
+      <c r="C714" s="0" t="inlineStr">
         <is>
           <t>Imaginary line around the middle of the Earth — Ecuador.</t>
         </is>
       </c>
-      <c r="D714" t="inlineStr">
+      <c r="D714" s="0" t="inlineStr">
         <is>
           <t>The equator divides the Earth into the Northern and Southern Hemispheres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="0" t="inlineStr">
+        <is>
+          <t>Gear</t>
+        </is>
+      </c>
+      <c r="B715" s="0" t="inlineStr">
+        <is>
+          <t>guer</t>
+        </is>
+      </c>
+      <c r="C715" s="0" t="inlineStr">
+        <is>
+          <t>Equipment or clothing needed for a particular activity — Equipo.</t>
+        </is>
+      </c>
+      <c r="D715" s="0" t="inlineStr">
+        <is>
+          <t>Did you get all the camping gear you need?</t>
+        </is>
+      </c>
+      <c r="E715" s="0" t="inlineStr">
+        <is>
+          <t>Toothed wheel in a machine that transmits power — Engranaje.</t>
+        </is>
+      </c>
+      <c r="F715" s="0" t="inlineStr">
+        <is>
+          <t>Shift into a lower gear to climb the hill.</t>
+        </is>
+      </c>
+      <c r="I715" s="0" t="inlineStr">
+        <is>
+          <t>Uncountable noun in the first meaning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="0" t="inlineStr">
+        <is>
+          <t>Tricky</t>
+        </is>
+      </c>
+      <c r="B716" s="0" t="inlineStr">
+        <is>
+          <t>triki</t>
+        </is>
+      </c>
+      <c r="C716" s="0" t="inlineStr">
+        <is>
+          <t>Difficult to deal with or accomplish — Difícil.</t>
+        </is>
+      </c>
+      <c r="D716" s="0" t="inlineStr">
+        <is>
+          <t>The math problem was really tricky.</t>
+        </is>
+      </c>
+      <c r="I716" s="0" t="inlineStr">
+        <is>
+          <t>Adjective. Often used to describe situations, problems, or tasks that require care and skill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Shelves</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>ʃelvz</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Horizontal boards for storage — Estantes.</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>The books are on the top shelves.</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Plural of shelf.</t>
         </is>
       </c>
     </row>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I717"/>
+  <dimension ref="A1:I728"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -24939,29 +24939,336 @@
       </c>
     </row>
     <row r="717">
-      <c r="A717" t="inlineStr">
+      <c r="A717" s="0" t="inlineStr">
         <is>
           <t>Shelves</t>
         </is>
       </c>
-      <c r="B717" t="inlineStr">
+      <c r="B717" s="0" t="inlineStr">
         <is>
           <t>ʃelvz</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr">
+      <c r="C717" s="0" t="inlineStr">
         <is>
           <t>Horizontal boards for storage — Estantes.</t>
         </is>
       </c>
-      <c r="D717" t="inlineStr">
+      <c r="D717" s="0" t="inlineStr">
         <is>
           <t>The books are on the top shelves.</t>
         </is>
       </c>
-      <c r="I717" t="inlineStr">
+      <c r="I717" s="0" t="inlineStr">
         <is>
           <t>Plural of shelf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="0" t="inlineStr">
+        <is>
+          <t>Plenty</t>
+        </is>
+      </c>
+      <c r="B718" s="0" t="inlineStr">
+        <is>
+          <t>plenti</t>
+        </is>
+      </c>
+      <c r="C718" s="0" t="inlineStr">
+        <is>
+          <t>A large amount or quantity; more than enough — Abundancia, mucho.</t>
+        </is>
+      </c>
+      <c r="D718" s="0" t="inlineStr">
+        <is>
+          <t>We have plenty of food for the party.</t>
+        </is>
+      </c>
+      <c r="I718" s="0" t="inlineStr">
+        <is>
+          <t>Often followed by 'of'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="0" t="inlineStr">
+        <is>
+          <t>Shelf</t>
+        </is>
+      </c>
+      <c r="B719" s="0" t="inlineStr">
+        <is>
+          <t>chelf</t>
+        </is>
+      </c>
+      <c r="C719" s="0" t="inlineStr">
+        <is>
+          <t>A flat board fixed to a wall or inside a cupboard for holding things — Estante.</t>
+        </is>
+      </c>
+      <c r="D719" s="0" t="inlineStr">
+        <is>
+          <t>The book was on the top shelf.</t>
+        </is>
+      </c>
+      <c r="I719" s="0" t="inlineStr">
+        <is>
+          <t>Plural: shelves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="0" t="inlineStr">
+        <is>
+          <t>Trout</t>
+        </is>
+      </c>
+      <c r="B720" s="0" t="inlineStr">
+        <is>
+          <t>traut</t>
+        </is>
+      </c>
+      <c r="C720" s="0" t="inlineStr">
+        <is>
+          <t>Freshwater fish with a speckled body — Trucha.</t>
+        </is>
+      </c>
+      <c r="D720" s="0" t="inlineStr">
+        <is>
+          <t>We caught a big trout in the river.</t>
+        </is>
+      </c>
+      <c r="I720" s="0" t="inlineStr">
+        <is>
+          <t>Plural is usually trout, though trouts is sometimes used for different species.</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="0" t="inlineStr">
+        <is>
+          <t>Proudly</t>
+        </is>
+      </c>
+      <c r="B721" s="0" t="inlineStr">
+        <is>
+          <t>praudli</t>
+        </is>
+      </c>
+      <c r="C721" s="0" t="inlineStr">
+        <is>
+          <t>With pride — Con orgullo.</t>
+        </is>
+      </c>
+      <c r="D721" s="0" t="inlineStr">
+        <is>
+          <t>She proudly displayed her diploma.</t>
+        </is>
+      </c>
+      <c r="I721" s="0" t="inlineStr">
+        <is>
+          <t>Adverb formed from the adjective proud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="0" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="B722" s="0" t="inlineStr">
+        <is>
+          <t>kleim</t>
+        </is>
+      </c>
+      <c r="C722" s="0" t="inlineStr">
+        <is>
+          <t>State that something is the case, typically without providing evidence — Afirmar, asegurar.</t>
+        </is>
+      </c>
+      <c r="D722" s="0" t="inlineStr">
+        <is>
+          <t>He claims that he saw the ghost.</t>
+        </is>
+      </c>
+      <c r="E722" s="0" t="inlineStr">
+        <is>
+          <t>Formally request or demand something because you believe you have a right to it — Reclamar, exigir.</t>
+        </is>
+      </c>
+      <c r="F722" s="0" t="inlineStr">
+        <is>
+          <t>You can claim your money back.</t>
+        </is>
+      </c>
+      <c r="I722" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: claim — Present: claims — Past: claimed — Past participle: claimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="0" t="inlineStr">
+        <is>
+          <t>Shimmering</t>
+        </is>
+      </c>
+      <c r="B723" s="0" t="inlineStr">
+        <is>
+          <t>shímering</t>
+        </is>
+      </c>
+      <c r="C723" s="0" t="inlineStr">
+        <is>
+          <t>Reflecting a soft, tremulous light — Brillante o trémulo.</t>
+        </is>
+      </c>
+      <c r="D723" s="0" t="inlineStr">
+        <is>
+          <t>The shimmering surface of the lake looked magical.</t>
+        </is>
+      </c>
+      <c r="I723" s="0" t="inlineStr">
+        <is>
+          <t>Present participle/adjective formed from the verb shimmer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="0" t="inlineStr">
+        <is>
+          <t>Stretches</t>
+        </is>
+      </c>
+      <c r="B724" s="0" t="inlineStr">
+        <is>
+          <t>stréchis</t>
+        </is>
+      </c>
+      <c r="C724" s="0" t="inlineStr">
+        <is>
+          <t>Extends or pulls something so that it becomes longer or wider — Estira.</t>
+        </is>
+      </c>
+      <c r="D724" s="0" t="inlineStr">
+        <is>
+          <t>She stretches her legs before running.</t>
+        </is>
+      </c>
+      <c r="I724" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: stretch — Present: stretches — Past: stretched — Past participle: stretched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="0" t="inlineStr">
+        <is>
+          <t>Joggers</t>
+        </is>
+      </c>
+      <c r="B725" s="0" t="inlineStr">
+        <is>
+          <t>yóguers</t>
+        </is>
+      </c>
+      <c r="C725" s="0" t="inlineStr">
+        <is>
+          <t>Soft, loose trousers worn for exercise or relaxing — Pantalones de chándal.</t>
+        </is>
+      </c>
+      <c r="D725" s="0" t="inlineStr">
+        <is>
+          <t>He put on a t-shirt and joggers.</t>
+        </is>
+      </c>
+      <c r="I725" s="0" t="inlineStr">
+        <is>
+          <t>Plural noun. Always used in the plural for this meaning (singular 'jogger' refers to a person who runs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="0" t="inlineStr">
+        <is>
+          <t>Jogger</t>
+        </is>
+      </c>
+      <c r="B726" s="0" t="inlineStr">
+        <is>
+          <t>yóguer</t>
+        </is>
+      </c>
+      <c r="C726" s="0" t="inlineStr">
+        <is>
+          <t>Person who runs for exercise — Corredor (que hace footing).</t>
+        </is>
+      </c>
+      <c r="D726" s="0" t="inlineStr">
+        <is>
+          <t>A jogger ran past our house.</t>
+        </is>
+      </c>
+      <c r="I726" s="0" t="inlineStr">
+        <is>
+          <t>Usually refers to recreational runners rather than competitive ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="0" t="inlineStr">
+        <is>
+          <t>Effortless</t>
+        </is>
+      </c>
+      <c r="B727" s="0" t="inlineStr">
+        <is>
+          <t>éf-ort-les</t>
+        </is>
+      </c>
+      <c r="C727" s="0" t="inlineStr">
+        <is>
+          <t>Requiring no physical or mental exertion — Sin esfuerzo.</t>
+        </is>
+      </c>
+      <c r="D727" s="0" t="inlineStr">
+        <is>
+          <t>Her performance on the piano looked completely effortless.</t>
+        </is>
+      </c>
+      <c r="I727" s="0" t="inlineStr">
+        <is>
+          <t>Adjective. Often used to describe skills, beauty, or movement that seems natural and easy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Beauty</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>biuti</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>The quality of being pleasing or attractive — Belleza.</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>She admires the natural beauty of the mountains.</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>Countable noun when referring to a beautiful person or thing (e.g., 'She was a beauty in her youth').</t>
         </is>
       </c>
     </row>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -25246,27 +25246,27 @@
       </c>
     </row>
     <row r="728">
-      <c r="A728" t="inlineStr">
+      <c r="A728" s="0" t="inlineStr">
         <is>
           <t>Beauty</t>
         </is>
       </c>
-      <c r="B728" t="inlineStr">
+      <c r="B728" s="0" t="inlineStr">
         <is>
           <t>biuti</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr">
+      <c r="C728" s="0" t="inlineStr">
         <is>
           <t>The quality of being pleasing or attractive — Belleza.</t>
         </is>
       </c>
-      <c r="D728" t="inlineStr">
+      <c r="D728" s="0" t="inlineStr">
         <is>
           <t>She admires the natural beauty of the mountains.</t>
         </is>
       </c>
-      <c r="I728" t="inlineStr">
+      <c r="I728" s="0" t="inlineStr">
         <is>
           <t>Countable noun when referring to a beautiful person or thing (e.g., 'She was a beauty in her youth').</t>
         </is>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I728"/>
+  <dimension ref="A1:I730"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -25269,6 +25269,60 @@
       <c r="I728" s="0" t="inlineStr">
         <is>
           <t>Countable noun when referring to a beautiful person or thing (e.g., 'She was a beauty in her youth').</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="0" t="inlineStr">
+        <is>
+          <t>Detached</t>
+        </is>
+      </c>
+      <c r="B729" s="0" t="inlineStr">
+        <is>
+          <t>ditácht</t>
+        </is>
+      </c>
+      <c r="C729" s="0" t="inlineStr">
+        <is>
+          <t>Not connected or separate — Separado / independiente.</t>
+        </is>
+      </c>
+      <c r="D729" s="0" t="inlineStr">
+        <is>
+          <t>The house has a detached garage.</t>
+        </is>
+      </c>
+      <c r="I729" s="0" t="inlineStr">
+        <is>
+          <t>Often used to describe houses that are not joined to another property, or a person who is emotionally removed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Handle</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>jándel</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Part of something designed to be held or opened by — Manija / mango / tirador.</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>The handle of the suitcase broke.</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: handle — Present: handles — Past: handled — Past participle: handled. Also used as a noun.</t>
         </is>
       </c>
     </row>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I730"/>
+  <dimension ref="A1:I764"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -25300,29 +25300,972 @@
       </c>
     </row>
     <row r="730">
-      <c r="A730" t="inlineStr">
+      <c r="A730" s="0" t="inlineStr">
         <is>
           <t>Handle</t>
         </is>
       </c>
-      <c r="B730" t="inlineStr">
+      <c r="B730" s="0" t="inlineStr">
         <is>
           <t>jándel</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C730" s="0" t="inlineStr">
         <is>
           <t>Part of something designed to be held or opened by — Manija / mango / tirador.</t>
         </is>
       </c>
-      <c r="D730" t="inlineStr">
+      <c r="D730" s="0" t="inlineStr">
         <is>
           <t>The handle of the suitcase broke.</t>
         </is>
       </c>
-      <c r="I730" t="inlineStr">
+      <c r="I730" s="0" t="inlineStr">
         <is>
           <t>Regular verb. Base: handle — Present: handles — Past: handled — Past participle: handled. Also used as a noun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="0" t="inlineStr">
+        <is>
+          <t>Rocky</t>
+        </is>
+      </c>
+      <c r="B731" s="0" t="inlineStr">
+        <is>
+          <t>roki</t>
+        </is>
+      </c>
+      <c r="C731" s="0" t="inlineStr">
+        <is>
+          <t>Full of rocks — Rocoso.</t>
+        </is>
+      </c>
+      <c r="D731" s="0" t="inlineStr">
+        <is>
+          <t>They crossed a rocky plateau.</t>
+        </is>
+      </c>
+      <c r="E731" s="0" t="inlineStr">
+        <is>
+          <t>Unstable or difficult — Inseguro.</t>
+        </is>
+      </c>
+      <c r="F731" s="0" t="inlineStr">
+        <is>
+          <t>They had a rocky start to their relationship.</t>
+        </is>
+      </c>
+      <c r="I731" s="0" t="inlineStr">
+        <is>
+          <t>Adjective. Comparative: rockier — Superlative: rockiest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="0" t="inlineStr">
+        <is>
+          <t>Makeover</t>
+        </is>
+      </c>
+      <c r="B732" s="0" t="inlineStr">
+        <is>
+          <t>méik-ou-ver</t>
+        </is>
+      </c>
+      <c r="C732" s="0" t="inlineStr">
+        <is>
+          <t>A thorough renovation or improvement of something — Cambio de imagen o renovación.</t>
+        </is>
+      </c>
+      <c r="D732" s="0" t="inlineStr">
+        <is>
+          <t>The kitchen is getting a complete makeover.</t>
+        </is>
+      </c>
+      <c r="I732" s="0" t="inlineStr">
+        <is>
+          <t>Often used for rooms, websites, or people's appearances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="0" t="inlineStr">
+        <is>
+          <t>Figures</t>
+        </is>
+      </c>
+      <c r="B733" s="0" t="inlineStr">
+        <is>
+          <t>figiers</t>
+        </is>
+      </c>
+      <c r="C733" s="0" t="inlineStr">
+        <is>
+          <t>Numbers or amount expressed in numbers — Cifras.</t>
+        </is>
+      </c>
+      <c r="D733" s="0" t="inlineStr">
+        <is>
+          <t>Take a look at these figures and let me know what you think.</t>
+        </is>
+      </c>
+      <c r="I733" s="0" t="inlineStr">
+        <is>
+          <t>Plural noun. Usually refers to statistical data or numerical amounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="0" t="inlineStr">
+        <is>
+          <t>Tiles</t>
+        </is>
+      </c>
+      <c r="B734" s="0" t="inlineStr">
+        <is>
+          <t>táils</t>
+        </is>
+      </c>
+      <c r="C734" s="0" t="inlineStr">
+        <is>
+          <t>Flat pieces of baked clay, stone, or other material used for covering roofs, floors, or walls — Azulejos o baldosas.</t>
+        </is>
+      </c>
+      <c r="D734" s="0" t="inlineStr">
+        <is>
+          <t>We need to buy new tiles for the bathroom floor.</t>
+        </is>
+      </c>
+      <c r="I734" s="0" t="inlineStr">
+        <is>
+          <t>Plural of tile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="0" t="inlineStr">
+        <is>
+          <t>Picked</t>
+        </is>
+      </c>
+      <c r="B735" s="0" t="inlineStr">
+        <is>
+          <t>pikt</t>
+        </is>
+      </c>
+      <c r="C735" s="0" t="inlineStr">
+        <is>
+          <t>Selected or chosen from a group — Elegido, escogido.</t>
+        </is>
+      </c>
+      <c r="D735" s="0" t="inlineStr">
+        <is>
+          <t>The tiles you picked might be a bit tricky to fit.</t>
+        </is>
+      </c>
+      <c r="I735" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: pick — Present: picks — Past: picked — Past participle: picked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="0" t="inlineStr">
+        <is>
+          <t>Stick with</t>
+        </is>
+      </c>
+      <c r="B736" s="0" t="inlineStr">
+        <is>
+          <t>stik uiz</t>
+        </is>
+      </c>
+      <c r="C736" s="0" t="inlineStr">
+        <is>
+          <t>Continue using, doing, or believing in something — Mantenerse fiel a, seguir con.</t>
+        </is>
+      </c>
+      <c r="D736" s="0" t="inlineStr">
+        <is>
+          <t>Do you want to stick with that plan?</t>
+        </is>
+      </c>
+      <c r="I736" s="0" t="inlineStr">
+        <is>
+          <t>Irregular phrasal verb. Base: stick with — Present: sticks with — Past: stuck with — Past participle: stuck with.</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="0" t="inlineStr">
+        <is>
+          <t>Push up</t>
+        </is>
+      </c>
+      <c r="B737" s="0" t="inlineStr">
+        <is>
+          <t>push ap</t>
+        </is>
+      </c>
+      <c r="C737" s="0" t="inlineStr">
+        <is>
+          <t>Exercise where you lift your body from the floor using your arms — Flexión.</t>
+        </is>
+      </c>
+      <c r="D737" s="0" t="inlineStr">
+        <is>
+          <t>He can do fifty push-ups without stopping.</t>
+        </is>
+      </c>
+      <c r="I737" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb (phrasal verb). Base: push up — Present: pushes up — Past: pushed up — Past participle: pushed up. Can also mean to increase the price or level of something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="0" t="inlineStr">
+        <is>
+          <t>Fair enough</t>
+        </is>
+      </c>
+      <c r="B738" s="0" t="inlineStr">
+        <is>
+          <t>fér inaf</t>
+        </is>
+      </c>
+      <c r="C738" s="0" t="inlineStr">
+        <is>
+          <t>An expression used to admit that something is reasonable or acceptable — De acuerdo.</t>
+        </is>
+      </c>
+      <c r="D738" s="0" t="inlineStr">
+        <is>
+          <t>You don't want to work overtime? Fair enough.</t>
+        </is>
+      </c>
+      <c r="I738" s="0" t="inlineStr">
+        <is>
+          <t>Used to acknowledge and accept another person's point of view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="0" t="inlineStr">
+        <is>
+          <t>They're up</t>
+        </is>
+      </c>
+      <c r="B739" s="0" t="inlineStr">
+        <is>
+          <t>deir ap</t>
+        </is>
+      </c>
+      <c r="C739" s="0" t="inlineStr">
+        <is>
+          <t>Installed and in position — Instalados y colocados.</t>
+        </is>
+      </c>
+      <c r="D739" s="0" t="inlineStr">
+        <is>
+          <t>The new kitchen cabinets are up.</t>
+        </is>
+      </c>
+      <c r="I739" s="0" t="inlineStr">
+        <is>
+          <t>Contraction of 'they are' combined with the adverb 'up'. Used for structures, tiles, wallpaper, or posters that have been put in place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="0" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="B740" s="0" t="inlineStr">
+        <is>
+          <t>jit</t>
+        </is>
+      </c>
+      <c r="C740" s="0" t="inlineStr">
+        <is>
+          <t>Reach a barrier or obstacle — Encontrarse con un obstáculo.</t>
+        </is>
+      </c>
+      <c r="D740" s="0" t="inlineStr">
+        <is>
+          <t>We hit a bit of a wall during the project.</t>
+        </is>
+      </c>
+      <c r="I740" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb. Base: hit — Present: hits — Past: hit — Past participle: hit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="0" t="inlineStr">
+        <is>
+          <t>Hit a wall</t>
+        </is>
+      </c>
+      <c r="B741" s="0" t="inlineStr">
+        <is>
+          <t>jit a uol</t>
+        </is>
+      </c>
+      <c r="C741" s="0" t="inlineStr">
+        <is>
+          <t>Reach a barrier or stop making progress — Topar con pared.</t>
+        </is>
+      </c>
+      <c r="D741" s="0" t="inlineStr">
+        <is>
+          <t>I tried to solve the puzzle for hours before I hit a wall.</t>
+        </is>
+      </c>
+      <c r="I741" s="0" t="inlineStr">
+        <is>
+          <t>Irregular verb phrase. Base: hit a wall — Present: hits a wall — Past: hit a wall — Past participle: hit a wall. Usually used figuratively.</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="0" t="inlineStr">
+        <is>
+          <t>From here on out</t>
+        </is>
+      </c>
+      <c r="B742" s="0" t="inlineStr">
+        <is>
+          <t>from jier on aut</t>
+        </is>
+      </c>
+      <c r="C742" s="0" t="inlineStr">
+        <is>
+          <t>From this time forward, in the future — De ahora en adelante.</t>
+        </is>
+      </c>
+      <c r="D742" s="0" t="inlineStr">
+        <is>
+          <t>We'll definitely be extra careful from here on out.</t>
+        </is>
+      </c>
+      <c r="I742" s="0" t="inlineStr">
+        <is>
+          <t>Synonym: from now on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="0" t="inlineStr">
+        <is>
+          <t>Sign off</t>
+        </is>
+      </c>
+      <c r="B743" s="0" t="inlineStr">
+        <is>
+          <t>sain of</t>
+        </is>
+      </c>
+      <c r="C743" s="0" t="inlineStr">
+        <is>
+          <t>Approve formally — Aprobar oficialmente.</t>
+        </is>
+      </c>
+      <c r="D743" s="0" t="inlineStr">
+        <is>
+          <t>I need you to sign off on the new timeline.</t>
+        </is>
+      </c>
+      <c r="I743" s="0" t="inlineStr">
+        <is>
+          <t>Phrasal verb. Base: sign off — Present: signs off — Past: signed off — Past participle: signed off. Usually followed by 'on'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="0" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="B744" s="0" t="inlineStr">
+        <is>
+          <t>táin-lain</t>
+        </is>
+      </c>
+      <c r="C744" s="0" t="inlineStr">
+        <is>
+          <t>A schedule of events — Cronograma.</t>
+        </is>
+      </c>
+      <c r="D744" s="0" t="inlineStr">
+        <is>
+          <t>We need to approve the new timeline for the project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="0" t="inlineStr">
+        <is>
+          <t>Paperwork</t>
+        </is>
+      </c>
+      <c r="B745" s="0" t="inlineStr">
+        <is>
+          <t>péiper-uerk</t>
+        </is>
+      </c>
+      <c r="C745" s="0" t="inlineStr">
+        <is>
+          <t>Routine administrative work involving documents — Papeleo.</t>
+        </is>
+      </c>
+      <c r="D745" s="0" t="inlineStr">
+        <is>
+          <t>I hate doing paperwork.</t>
+        </is>
+      </c>
+      <c r="I745" s="0" t="inlineStr">
+        <is>
+          <t>Uncountable noun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="0" t="inlineStr">
+        <is>
+          <t>Toss</t>
+        </is>
+      </c>
+      <c r="B746" s="0" t="inlineStr">
+        <is>
+          <t>tos</t>
+        </is>
+      </c>
+      <c r="C746" s="0" t="inlineStr">
+        <is>
+          <t>Throw away or discard something — Botar, tirar.</t>
+        </is>
+      </c>
+      <c r="D746" s="0" t="inlineStr">
+        <is>
+          <t>I'll toss those old cabinets right away.</t>
+        </is>
+      </c>
+      <c r="I746" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: toss — Present: tosses — Past: tossed — Past participle: tossed. Often used with 'away' or 'out' when discarding things.</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="0" t="inlineStr">
+        <is>
+          <t>Falls behind</t>
+        </is>
+      </c>
+      <c r="B747" s="0" t="inlineStr">
+        <is>
+          <t>fols bijáind</t>
+        </is>
+      </c>
+      <c r="C747" s="0" t="inlineStr">
+        <is>
+          <t>Fail to maintain a schedule or standard — Retrasarse.</t>
+        </is>
+      </c>
+      <c r="D747" s="0" t="inlineStr">
+        <is>
+          <t>If we work slowly, the project falls behind.</t>
+        </is>
+      </c>
+      <c r="I747" s="0" t="inlineStr">
+        <is>
+          <t>Phrasal verb. Base: fall behind — Present: falls behind — Past: fell behind — Past participle: fallen behind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="0" t="inlineStr">
+        <is>
+          <t>Ring</t>
+        </is>
+      </c>
+      <c r="B748" s="0" t="inlineStr">
+        <is>
+          <t>ring</t>
+        </is>
+      </c>
+      <c r="C748" s="0" t="inlineStr">
+        <is>
+          <t>Telephone call — Llamada telefónica.</t>
+        </is>
+      </c>
+      <c r="D748" s="0" t="inlineStr">
+        <is>
+          <t>I'll give you a ring later today.</t>
+        </is>
+      </c>
+      <c r="I748" s="0" t="inlineStr">
+        <is>
+          <t>Often used in the phrase 'give someone a ring'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="0" t="inlineStr">
+        <is>
+          <t>Pops up</t>
+        </is>
+      </c>
+      <c r="B749" s="0" t="inlineStr">
+        <is>
+          <t>pops ap</t>
+        </is>
+      </c>
+      <c r="C749" s="0" t="inlineStr">
+        <is>
+          <t>Appear unexpectedly — Aparecer de la nada.</t>
+        </is>
+      </c>
+      <c r="D749" s="0" t="inlineStr">
+        <is>
+          <t>A new problem always pops up.</t>
+        </is>
+      </c>
+      <c r="I749" s="0" t="inlineStr">
+        <is>
+          <t>Phrasal verb. Base: pop up — Present: pops up — Past: popped up — Past participle: popped up. Intransitive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="0" t="inlineStr">
+        <is>
+          <t>Punch list</t>
+        </is>
+      </c>
+      <c r="B750" s="0" t="inlineStr">
+        <is>
+          <t>panch list</t>
+        </is>
+      </c>
+      <c r="C750" s="0" t="inlineStr">
+        <is>
+          <t>A list of remaining tasks needed to finish a project — Lista de tareas pendientes.</t>
+        </is>
+      </c>
+      <c r="D750" s="0" t="inlineStr">
+        <is>
+          <t>We reviewed the punch list before the final inspection.</t>
+        </is>
+      </c>
+      <c r="I750" s="0" t="inlineStr">
+        <is>
+          <t>Often used in construction, software development, and project management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="0" t="inlineStr">
+        <is>
+          <t>Firm date</t>
+        </is>
+      </c>
+      <c r="B751" s="0" t="inlineStr">
+        <is>
+          <t>ferm deit</t>
+        </is>
+      </c>
+      <c r="C751" s="0" t="inlineStr">
+        <is>
+          <t>Definite or fixed date — Fecha fija.</t>
+        </is>
+      </c>
+      <c r="D751" s="0" t="inlineStr">
+        <is>
+          <t>We need to set a firm date for the meeting.</t>
+        </is>
+      </c>
+      <c r="I751" s="0" t="inlineStr">
+        <is>
+          <t>Often used in business and project management when schedules need to be locked in rather than left tentative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="0" t="inlineStr">
+        <is>
+          <t>Mess on-site</t>
+        </is>
+      </c>
+      <c r="B752" s="0" t="inlineStr">
+        <is>
+          <t>mes on sait</t>
+        </is>
+      </c>
+      <c r="C752" s="0" t="inlineStr">
+        <is>
+          <t>Untidy or dirty condition at a workplace or construction area — Desorden o suciedad en el lugar de trabajo o la obra.</t>
+        </is>
+      </c>
+      <c r="D752" s="0" t="inlineStr">
+        <is>
+          <t>We need to clean up the mess on-site before the client arrives.</t>
+        </is>
+      </c>
+      <c r="I752" s="0" t="inlineStr">
+        <is>
+          <t>Often used in construction and project management to refer to disorganization at the physical location of a project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="0" t="inlineStr">
+        <is>
+          <t>Out of the way</t>
+        </is>
+      </c>
+      <c r="B753" s="0" t="inlineStr">
+        <is>
+          <t>aut ov de wei</t>
+        </is>
+      </c>
+      <c r="C753" s="0" t="inlineStr">
+        <is>
+          <t>Finished or dealt with — Terminado, fuera del camino.</t>
+        </is>
+      </c>
+      <c r="D753" s="0" t="inlineStr">
+        <is>
+          <t>Let's get this paperwork out of the way first.</t>
+        </is>
+      </c>
+      <c r="I753" s="0" t="inlineStr">
+        <is>
+          <t>Often used with verbs like 'get' or 'be'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="0" t="inlineStr">
+        <is>
+          <t>Financial plateau</t>
+        </is>
+      </c>
+      <c r="B754" s="0" t="inlineStr">
+        <is>
+          <t>faináncial plató</t>
+        </is>
+      </c>
+      <c r="C754" s="0" t="inlineStr">
+        <is>
+          <t>A state of little or no financial growth following a period of activity or progress — Estancamiento financiero.</t>
+        </is>
+      </c>
+      <c r="D754" s="0" t="inlineStr">
+        <is>
+          <t>The company has been stuck on a financial plateau for months.</t>
+        </is>
+      </c>
+      <c r="I754" s="0" t="inlineStr">
+        <is>
+          <t>Plateau is of French origin, pronounced with a silent 't' at the end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="0" t="inlineStr">
+        <is>
+          <t>Tackle</t>
+        </is>
+      </c>
+      <c r="B755" s="0" t="inlineStr">
+        <is>
+          <t>tákl</t>
+        </is>
+      </c>
+      <c r="C755" s="0" t="inlineStr">
+        <is>
+          <t>Deal with a problem or task — Abordar, lidiar con.</t>
+        </is>
+      </c>
+      <c r="D755" s="0" t="inlineStr">
+        <is>
+          <t>We need to tackle this issue immediately.</t>
+        </is>
+      </c>
+      <c r="E755" s="0" t="inlineStr">
+        <is>
+          <t>Try to take the ball from an opponent in sport — Quitar el balón, taclear.</t>
+        </is>
+      </c>
+      <c r="F755" s="0" t="inlineStr">
+        <is>
+          <t>He made a great tackle near the goal.</t>
+        </is>
+      </c>
+      <c r="I755" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: tackle — Present: tackles — Past: tackled — Past participle: tackled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="0" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="B756" s="0" t="inlineStr">
+        <is>
+          <t>ekspensiz</t>
+        </is>
+      </c>
+      <c r="C756" s="0" t="inlineStr">
+        <is>
+          <t>The money spent on something; costs — Gastos.</t>
+        </is>
+      </c>
+      <c r="D756" s="0" t="inlineStr">
+        <is>
+          <t>We need to cut down our monthly expenses.</t>
+        </is>
+      </c>
+      <c r="I756" s="0" t="inlineStr">
+        <is>
+          <t>Usually used in the plural form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="0" t="inlineStr">
+        <is>
+          <t>Smuggler</t>
+        </is>
+      </c>
+      <c r="B757" s="0" t="inlineStr">
+        <is>
+          <t>smá-glor</t>
+        </is>
+      </c>
+      <c r="C757" s="0" t="inlineStr">
+        <is>
+          <t>Person who illegally moves goods across a border — Contrabandista.</t>
+        </is>
+      </c>
+      <c r="D757" s="0" t="inlineStr">
+        <is>
+          <t>The police caught the smuggler at the border.</t>
+        </is>
+      </c>
+      <c r="I757" s="0" t="inlineStr">
+        <is>
+          <t>Related verb: to smuggle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="0" t="inlineStr">
+        <is>
+          <t>Seized</t>
+        </is>
+      </c>
+      <c r="B758" s="0" t="inlineStr">
+        <is>
+          <t>siizd</t>
+        </is>
+      </c>
+      <c r="C758" s="0" t="inlineStr">
+        <is>
+          <t>Take hold of suddenly and forcibly — Apoderarse de, agarrar.</t>
+        </is>
+      </c>
+      <c r="D758" s="0" t="inlineStr">
+        <is>
+          <t>She seized the rope to avoid falling.</t>
+        </is>
+      </c>
+      <c r="E758" s="0" t="inlineStr">
+        <is>
+          <t>Confiscate or take illegal items — Incautar, decomisar.</t>
+        </is>
+      </c>
+      <c r="F758" s="0" t="inlineStr">
+        <is>
+          <t>The police seized the smuggled goods.</t>
+        </is>
+      </c>
+      <c r="I758" s="0" t="inlineStr">
+        <is>
+          <t>Regular verb. Base: seize — Present: seizes — Past: seized — Past participle: seized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="0" t="inlineStr">
+        <is>
+          <t>Final number</t>
+        </is>
+      </c>
+      <c r="B759" s="0" t="inlineStr">
+        <is>
+          <t>fáinal námber</t>
+        </is>
+      </c>
+      <c r="C759" s="0" t="inlineStr">
+        <is>
+          <t>Total amount or final figure — Cifra final.</t>
+        </is>
+      </c>
+      <c r="D759" s="0" t="inlineStr">
+        <is>
+          <t>What's the final number on the invoice?</t>
+        </is>
+      </c>
+      <c r="I759" s="0" t="inlineStr">
+        <is>
+          <t>Used in informal business contexts to ask for a final total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="0" t="inlineStr">
+        <is>
+          <t>Looking like</t>
+        </is>
+      </c>
+      <c r="B760" s="0" t="inlineStr">
+        <is>
+          <t>luking laik</t>
+        </is>
+      </c>
+      <c r="C760" s="0" t="inlineStr">
+        <is>
+          <t>Appearing to be, or taking on a certain shape or projection — Aparentando, teniendo pinta de.</t>
+        </is>
+      </c>
+      <c r="D760" s="0" t="inlineStr">
+        <is>
+          <t>What's the final number looking like?</t>
+        </is>
+      </c>
+      <c r="I760" s="0" t="inlineStr">
+        <is>
+          <t>Used informally to ask about the current status or appearance of something, often progress or a numerical total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="0" t="inlineStr">
+        <is>
+          <t>Quite a bit</t>
+        </is>
+      </c>
+      <c r="B761" s="0" t="inlineStr">
+        <is>
+          <t>kuait a bit</t>
+        </is>
+      </c>
+      <c r="C761" s="0" t="inlineStr">
+        <is>
+          <t>A lot, a considerable amount — Bastante, un buen cacho.</t>
+        </is>
+      </c>
+      <c r="D761" s="0" t="inlineStr">
+        <is>
+          <t>It costs quite a bit more than I expected.</t>
+        </is>
+      </c>
+      <c r="I761" s="0" t="inlineStr">
+        <is>
+          <t>Used as an adverbial phrase to modify verbs, adjectives, or comparative forms. More informal than 'quite a lot'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="0" t="inlineStr">
+        <is>
+          <t>Agreed on</t>
+        </is>
+      </c>
+      <c r="B762" s="0" t="inlineStr">
+        <is>
+          <t>agrid on</t>
+        </is>
+      </c>
+      <c r="C762" s="0" t="inlineStr">
+        <is>
+          <t>Have the same opinion about a particular thing or come to a mutual decision — Estar de acuerdo en, acordar.</t>
+        </is>
+      </c>
+      <c r="D762" s="0" t="inlineStr">
+        <is>
+          <t>Fifteen thousand is quite a bit more than we agreed on.</t>
+        </is>
+      </c>
+      <c r="I762" s="0" t="inlineStr">
+        <is>
+          <t>Phrasal verb. Base: agree on — Present: agrees on — Past: agreed on — Past participle: agreed on. Often used with a preposition at the end when referring to a specific topic or amount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="0" t="inlineStr">
+        <is>
+          <t>Itemized</t>
+        </is>
+      </c>
+      <c r="B763" s="0" t="inlineStr">
+        <is>
+          <t>ái-tomaist</t>
+        </is>
+      </c>
+      <c r="C763" s="0" t="inlineStr">
+        <is>
+          <t>Divided into individual parts or details — Desglosado.</t>
+        </is>
+      </c>
+      <c r="D763" s="0" t="inlineStr">
+        <is>
+          <t>Look, I need an itemized list of those extra expenses on my desk by tomorrow morning.</t>
+        </is>
+      </c>
+      <c r="I763" s="0" t="inlineStr">
+        <is>
+          <t>Past participle used as an adjective. Base verb: itemize.</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>Forward</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>fórward</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Proceed or progress with an action or plan — Seguir adelante.</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Are we good to move forward with that plan?</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>Often used with verbs like 'move', 'go', or 'press'.</t>
         </is>
       </c>
     </row>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I764"/>
+  <dimension ref="A1:I765"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -26243,29 +26243,56 @@
       </c>
     </row>
     <row r="764">
-      <c r="A764" t="inlineStr">
+      <c r="A764" s="0" t="inlineStr">
         <is>
           <t>Forward</t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B764" s="0" t="inlineStr">
         <is>
           <t>fórward</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C764" s="0" t="inlineStr">
         <is>
           <t>Proceed or progress with an action or plan — Seguir adelante.</t>
         </is>
       </c>
-      <c r="D764" t="inlineStr">
+      <c r="D764" s="0" t="inlineStr">
         <is>
           <t>Are we good to move forward with that plan?</t>
         </is>
       </c>
-      <c r="I764" t="inlineStr">
+      <c r="I764" s="0" t="inlineStr">
         <is>
           <t>Often used with verbs like 'move', 'go', or 'press'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>How are you keeping</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>jau ar yu ki-ping</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>How are you? — ¿Cómo estás? o ¿Cómo te va?</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Hello, John! How are you keeping?</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>Informal greeting used mainly in British English to ask about someone's health or general well-being over a period of time.</t>
         </is>
       </c>
     </row>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I765"/>
+  <dimension ref="A1:I767"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -26270,29 +26270,93 @@
       </c>
     </row>
     <row r="765">
-      <c r="A765" t="inlineStr">
+      <c r="A765" s="0" t="inlineStr">
         <is>
           <t>How are you keeping</t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B765" s="0" t="inlineStr">
         <is>
           <t>jau ar yu ki-ping</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
+      <c r="C765" s="0" t="inlineStr">
         <is>
           <t>How are you? — ¿Cómo estás? o ¿Cómo te va?</t>
         </is>
       </c>
-      <c r="D765" t="inlineStr">
+      <c r="D765" s="0" t="inlineStr">
         <is>
           <t>Hello, John! How are you keeping?</t>
         </is>
       </c>
-      <c r="I765" t="inlineStr">
+      <c r="I765" s="0" t="inlineStr">
         <is>
           <t>Informal greeting used mainly in British English to ask about someone's health or general well-being over a period of time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="0" t="inlineStr">
+        <is>
+          <t>Definitely</t>
+        </is>
+      </c>
+      <c r="B766" s="0" t="inlineStr">
+        <is>
+          <t>dé-finitli</t>
+        </is>
+      </c>
+      <c r="C766" s="0" t="inlineStr">
+        <is>
+          <t>Without doubt or certainly — Ciertamente / sin duda.</t>
+        </is>
+      </c>
+      <c r="D766" s="0" t="inlineStr">
+        <is>
+          <t>I will definitely be there.</t>
+        </is>
+      </c>
+      <c r="E766" s="0" t="inlineStr">
+        <is>
+          <t>Used to agree politely — Claro que sí.</t>
+        </is>
+      </c>
+      <c r="F766" s="0" t="inlineStr">
+        <is>
+          <t>—Can you help me? —Definitely.</t>
+        </is>
+      </c>
+      <c r="I766" s="0" t="inlineStr">
+        <is>
+          <t>Often misspelled as 'definitely' (avoid spelling it with 'a').</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>Adulthood</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>aduljud</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>The state or condition of being a adult — Edad adulta.</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>He reached adulthood at eighteen.</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>Noun.</t>
         </is>
       </c>
     </row>

--- a/ENGLISH SCHOOL.xlsx
+++ b/ENGLISH SCHOOL.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I767"/>
+  <dimension ref="A1:I768"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -26334,29 +26334,56 @@
       </c>
     </row>
     <row r="767">
-      <c r="A767" t="inlineStr">
+      <c r="A767" s="0" t="inlineStr">
         <is>
           <t>Adulthood</t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B767" s="0" t="inlineStr">
         <is>
           <t>aduljud</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C767" s="0" t="inlineStr">
         <is>
           <t>The state or condition of being a adult — Edad adulta.</t>
         </is>
       </c>
-      <c r="D767" t="inlineStr">
+      <c r="D767" s="0" t="inlineStr">
         <is>
           <t>He reached adulthood at eighteen.</t>
         </is>
       </c>
-      <c r="I767" t="inlineStr">
+      <c r="I767" s="0" t="inlineStr">
         <is>
           <t>Noun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>Thoughtfully</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>zótfuli</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>In a quiet, deep, or considerate way — Pensativamente / Con consideración.</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>He looked at the painting thoughtfully before speaking.</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>Adverb. Derived from the adjective 'thoughtful'.</t>
         </is>
       </c>
     </row>
